--- a/extraction/synacor.xlsx
+++ b/extraction/synacor.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
-    <numFmt numFmtId="166" formatCode="0.00##"/>
+    <numFmt numFmtId="166" formatCode="$0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -69,10 +69,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,31 +440,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,7 +585,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>by 01/10/2018</t>
+          <t>before 01/10/2018</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -609,8 +609,8 @@
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -621,7 +621,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Company A (private investment firm) approached first, expressing interest in acquiring the Company before signing an NDA. Bidder-led first contact; date of approach not given.</t>
+          <t>Company A, a private investment firm, expressed interest in exploring an acquisition of the Company before signing its NDA; bidder-led first contact in process 1. Exact date not given.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="4" t="n">
+      <c r="T2" s="3" t="n">
         <v>43110</v>
       </c>
-      <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="3" t="n">
         <v>43110</v>
       </c>
     </row>
@@ -669,8 +669,8 @@
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
@@ -681,7 +681,7 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Mutual NDA with standstill for the Company’s benefit. Entry of Company A.</t>
+          <t>Mutual NDA including a standstill for the Company's benefit; Company A's entry to process 1.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -691,13 +691,13 @@
       </c>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
-      <c r="T3" s="4" t="n">
+      <c r="T3" s="3" t="n">
         <v>43110</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="3" t="n">
         <v>43110</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="3" t="n">
         <v>43110</v>
       </c>
     </row>
@@ -731,8 +731,8 @@
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -755,7 +755,7 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Non-binding IOI for the whole company; price and terms not disclosed. No conditions reported. Unsolicited, before any outreach (round 0).</t>
+          <t>No condition or financing reported; price not disclosed. Non-binding indication of interest to acquire the Company, unsolicited (before any target outreach), so round 0.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -765,13 +765,13 @@
       </c>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="3" t="n">
         <v>43137</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="3" t="n">
         <v>43137</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="3" t="n">
         <v>43137</v>
       </c>
     </row>
@@ -805,8 +805,8 @@
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -829,7 +829,7 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Updated non-binding IOI after discussion between the parties; revises #3. Price and changes not disclosed; no conditions reported.</t>
+          <t>No condition or financing reported; price not disclosed. Updated non-binding IOI after discussion between the parties; revises #3. Its value is what Company A later could not support (#8).</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -839,13 +839,13 @@
       </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
-      <c r="T5" s="4" t="n">
+      <c r="T5" s="3" t="n">
         <v>43215</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="3" t="n">
         <v>43215</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="V5" s="3" t="n">
         <v>43215</v>
       </c>
     </row>
@@ -875,8 +875,8 @@
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
@@ -885,7 +885,7 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Target’s financial adviser, engaged to evaluate strategic opportunities; engagement letter had a stated termination date of 12/31/2018 (no termination reported).</t>
+          <t>Target's financial adviser, engaged to evaluate potential strategic opportunities; engagement letter had a stated termination date of 12/31/2018. No other end of the relationship is reported.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -895,13 +895,13 @@
       </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
-      <c r="T6" s="4" t="n">
+      <c r="T6" s="3" t="n">
         <v>43228</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="3" t="n">
         <v>43228</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="3" t="n">
         <v>43228</v>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>after 05/08/2018</t>
+          <t>after 05/08/2018 (undated)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -931,8 +931,8 @@
       <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
@@ -941,12 +941,12 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Round 1 opens with Liontree’s outreach to about 12 strategic and financial parties (#7). Start not dated beyond “then”, after the 05/08/2018 engagement. Company A’s IOI still standing. No due date reported.</t>
+          <t>Liontree's outreach to about 12 strategic and financial companies is process 1's first outreach wave; its start is undated, so it is dated from the engagement it carried out (#5). No bid due date stated. Company A carried in from round 0.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“Liontree then reached out to approximately 12 potential strategic and financial companies to evaluate their interest in an acquisition of the Company.” (p. 30)</t>
+          <t>“Liontree then reached out to approximately 12 potential strategic and financial companies to evaluate their interest in an acquisition of the Company” (p. 30)</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="S7" s="2" t="n"/>
-      <c r="T7" s="4" t="n">
+      <c r="T7" s="3" t="n">
         <v>43228</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="3" t="n">
         <v>43228</v>
       </c>
-      <c r="V7" s="4" t="n"/>
+      <c r="V7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -969,12 +969,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>after 05/08/2018</t>
+          <t>after 05/08/2018 (undated)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>About 12 strategic and financial parties (Liontree outreach)</t>
+          <t>Approximately 12 strategic and financial companies (Liontree outreach)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -993,8 +993,8 @@
       <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
@@ -1003,7 +1003,7 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated outreach by Liontree. Count: approximately 12; strategic/financial split not given. No NDAs reported; none led to an IOI.</t>
+          <t>Count: approximately 12. Target-initiated contacts by Liontree; strategic/financial split not given. None is reported to have signed an NDA or submitted an IOI, so none entered.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1013,13 +1013,13 @@
       </c>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="3" t="n">
         <v>43228</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="3" t="n">
         <v>43228</v>
       </c>
-      <c r="V8" s="4" t="n"/>
+      <c r="V8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1051,8 +1051,8 @@
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
@@ -1067,23 +1067,23 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Company A said it could not support a deal at the value in its own IOI (#4), revealing a valuation below its earlier offer. Process 1 then lapsed; no termination reported.</t>
+          <t>Company A told the Company it could not support a deal at the value in its non-binding IOI (#4, price undisclosed): its value is below its earlier offer. No bidder remains live in process 1.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“On June 20, 2018, Company A informed the Company that they were unable to support the transaction at the proposed value set forth in the non-binding indication of interest.” (p. 30)</t>
+          <t>“Company A informed the Company that they were unable to support the transaction at the proposed value set forth in the non-binding indication of interest” (p. 30)</t>
         </is>
       </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
-      <c r="T9" s="4" t="n">
+      <c r="T9" s="3" t="n">
         <v>43271</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="3" t="n">
         <v>43271</v>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="V9" s="3" t="n">
         <v>43271</v>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -1113,8 +1113,8 @@
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Inferred restart at the Company C NDA (#10). Process 1 lapsed: last reported acquirer contact Company A, 06/20/2018 (Liontree outreach contacts undated, possibly later). No process-1 participants remain to close. Company B merger-of-equals talks (Oct 2018–Mar 2019) not treated as a sale (Q2).</t>
+          <t>Inferred restart. Process 1 lapsed after Company A's 06/20/2018 withdrawal (last dated acquirer contact; Liontree outreach undated). Fresh start: NDA with Company C (#10). No participation open from process 1. Company B 'merger of equals' talks not treated as a sale (Q2).</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
-      <c r="T10" s="4" t="n">
+      <c r="T10" s="3" t="n">
         <v>43540</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="U10" s="3" t="n">
         <v>43525</v>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="V10" s="3" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -1181,8 +1181,8 @@
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
@@ -1193,23 +1193,23 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Mutual NDA with standstill, to explore a business combination. Company C is a publicly traded software company. Entry of Company C; direction of first contact not stated.</t>
+          <t>Mutual NDA with standstill for the Company's benefit, 'to explore a potential business combination'. Company C is a publicly-traded software company; who initiated contact is not stated. Company C's entry to process 2.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“In March 2019, the Company and a publicly-traded software company (“Company C”) entered into a mutual non-disclosure agreement, which included a standstill provision for the benefit of the Company” (p. 30)</t>
+          <t>“entered into a mutual non-disclosure agreement, which included a standstill provision for the benefit of the Company, to explore a potential business combination” (p. 30)</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="3" t="n">
         <v>43540</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="3" t="n">
         <v>43525</v>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="V11" s="3" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -1219,57 +1219,63 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Q3 2019 (by 07/30/2019)</t>
+          <t>07/30/2019</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
+          <t>Company E</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
+      <c r="M12" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Round 1 opens with management outreach to about five companies while the board weighed divesting the portal and advertising business (#12). Narrated as preceding the 07/30/2019 Company E NDA. Canaccord’s whole-company outreach (#17) followed within this round. No due date.</t>
+          <t>Mutual NDA with standstill. Company E (investment subsidiary of a publicly-traded financial services company) had expressed interest in acquiring only the portal and advertising business, within management's divestiture effort. Entry as a segment buyer (Q3).</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“The Company’s management engaged in outreach to approximately five companies” (p. 31)</t>
+          <t>“on July 30, 2019, the Company entered into a mutual non-disclosure agreement, which included a standstill provision for the benefit of the Company” (p. 31)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S12" s="2" t="n"/>
-      <c r="T12" s="4" t="n">
-        <v>43661</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>43647</v>
-      </c>
-      <c r="V12" s="4" t="n">
+      <c r="T12" s="3" t="n">
+        <v>43676</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>43676</v>
+      </c>
+      <c r="V12" s="3" t="n">
         <v>43676</v>
       </c>
     </row>
@@ -1279,58 +1285,72 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Q3 2019 (by 07/30/2019)</t>
+          <t>08/13/2019</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>About five companies (portal and advertising business outreach)</t>
+          <t>Company C</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated management outreach about buying the portal and advertising business only. Count: approximately 5. Whether Company E or F was among them is not stated.</t>
+          <t>No condition or financing reported; price not disclosed. Non-binding LOI to acquire the Company for cash and stock. Arrived before the banker outreach, so round 0; Canaccord was engaged on 08/25/2019 partly to evaluate it.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“the Company Board was evaluating divesting its portal and advertising business so as to convert the Company into a pure-play software company” (p. 31)</t>
+          <t>“On August 13, 2019, Company C submitted a non-binding letter of intent proposing an acquisition of the Company with consideration in the form of cash and stock” (p. 30)</t>
         </is>
       </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
-      <c r="T13" s="4" t="n">
-        <v>43661</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>43647</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>43676</v>
+      <c r="T13" s="3" t="n">
+        <v>43690</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>43690</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>43690</v>
       </c>
     </row>
     <row r="14">
@@ -1339,60 +1359,62 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>07/30/2019</t>
+          <t>third quarter of 2019</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Approximately five companies (portal and advertising divestiture outreach)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Mutual NDA with standstill; Company E (investment subsidiary of a public financial services company) had expressed interest in the portal and advertising business only. Entry of Company E in process 2.</t>
+          <t>Count: approximately 5. Management outreach to sell only the portal and advertising business (segment divestiture, not a whole-company sale). Company E and Company F may be among them; the filing does not say.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“on July 30, 2019, the Company entered into a mutual non-disclosure agreement, which included a standstill provision for the benefit of the Company, with an investment subsidiary” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="n"/>
+          <t>“The Company’s management engaged in outreach to approximately five companies” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S14" s="2" t="n"/>
-      <c r="T14" s="4" t="n">
-        <v>43676</v>
-      </c>
-      <c r="U14" s="4" t="n">
-        <v>43676</v>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>43676</v>
+      <c r="T14" s="3" t="n">
+        <v>43692</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>43647</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>43738</v>
       </c>
     </row>
     <row r="15">
@@ -1401,60 +1423,54 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Q3 2019</t>
+          <t>08/25/2019</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Company F</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Canaccord Genuity LLC</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Company F (information and technology services company) expressed interest in the portal and advertising business. Its existing May 2018 NDA from a commercial relationship is treated as reused, so this row is its entry. Dated only by the third-quarter 2019 paragraph and before its 09/15/2019 IOI.</t>
+          <t>Target's financial adviser, engaged to evaluate Company C's proposal and review other strategic and financial opportunities; stated termination 01/15/2020. Separately engaged 01/02/2020 for the target's own Company D acquisition (not a sale).</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“with whom the Company already had a valid non-disclosure agreement from May 2018 from a prior commercial relationship, also expressed interest in acquiring the Company’s portal and advertising business” (p. 31)</t>
+          <t>“On August 25, 2019, the Company engaged Canaccord Genuity to act as the Company’s financial advisor for purposes of evaluating the proposal from Company C” (p. 31)</t>
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
-      <c r="T15" s="4" t="n">
-        <v>43684</v>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>43647</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>43723</v>
+      <c r="T15" s="3" t="n">
+        <v>43702</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>43702</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>43702</v>
       </c>
     </row>
     <row r="16">
@@ -1463,73 +1479,57 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>08/13/2019</t>
+          <t>after 08/25/2019 (undated)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Company C</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Non-binding LOI to acquire the whole company for cash and stock; price not disclosed. No conditions reported. Came from bilateral talks begun in March, not from the outreach (round 0; C listed in round 1).</t>
+          <t>Canaccord's outreach to 18 additional parties, at the Board's direction under the 08/25/2019 engagement, is the first whole-company outreach wave; start undated. No bid due date stated. Company C carried in from round 0.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“On August 13, 2019, Company C submitted a non-binding letter of intent proposing an acquisition of the Company with consideration in the form of cash and stock.” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="n"/>
+          <t>“Pursuant to this engagement, at the direction of the Company Board, Canaccord Genuity reached out to an additional 18 parties” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="n"/>
-      <c r="T16" s="4" t="n">
-        <v>43690</v>
-      </c>
-      <c r="U16" s="4" t="n">
-        <v>43690</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>43690</v>
-      </c>
+      <c r="T16" s="3" t="n">
+        <v>43702</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>43702</v>
+      </c>
+      <c r="V16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1537,18 +1537,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>08/25/2019</t>
+          <t>after 08/25/2019 (undated)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Canaccord Genuity LLC</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
+          <t>18 additional parties (Canaccord outreach)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1557,35 +1561,35 @@
       <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
+      <c r="M17" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Target’s financial adviser, engaged to evaluate Company C’s proposal and other strategic and financial opportunities; letter’s stated termination 01/15/2020.</t>
+          <t>Target-initiated contacts; types not given. None led to an indication of interest and none is reported to have signed an NDA, so none entered.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“On August 25, 2019, the Company engaged Canaccord Genuity to act as the Company’s financial advisor for purposes of evaluating the proposal from Company C” (p. 31)</t>
+          <t>“none of the outreach attempts to these 18 additional parties led to an indication of interest from any of these parties” (p. 31)</t>
         </is>
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
-      <c r="T17" s="4" t="n">
+      <c r="T17" s="3" t="n">
         <v>43702</v>
       </c>
-      <c r="U17" s="4" t="n">
+      <c r="U17" s="3" t="n">
         <v>43702</v>
       </c>
-      <c r="V17" s="4" t="n">
-        <v>43702</v>
-      </c>
+      <c r="V17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1593,60 +1597,76 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>after 08/25/2019</t>
+          <t>09/15/2019</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18 parties (Canaccord outreach)</t>
+          <t>Company F</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated outreach by Canaccord at the board’s direction about a whole-company transaction, made under the engagement ending 01/15/2020. Type split not given. None led to an IOI; no NDAs reported.</t>
+          <t>No condition or financing reported; price not disclosed. Non-binding IOI for the portal and advertising business only. Company F (information and technology services) held a valid May 2018 NDA from a commercial relationship; reuse not stated. Answers management's divestiture outreach (Q3).</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“Canaccord Genuity reached out to an additional 18 parties to determine whether such parties would be interested in exploring a potential strategic transaction with the Company at that time” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="n"/>
+          <t>“Company F submitted a non-binding indication of interest to the Company on September 15, 2019” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="n"/>
-      <c r="T18" s="4" t="n">
-        <v>43702</v>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>43702</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>43845</v>
+      <c r="T18" s="3" t="n">
+        <v>43723</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>43723</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>43723</v>
       </c>
     </row>
     <row r="19">
@@ -1655,7 +1675,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>09/15/2019</t>
+          <t>after 09/15/2019 (undated)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1670,62 +1690,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="2" t="n"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Terms or process</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Non-binding IOI; price not disclosed. Scope not restated, taken as the portal and advertising business in which F expressed interest (#14). No conditions reported.</t>
+          <t>The parties 'were ultimately unable to agree on terms'; who ended talks and when are not stated. Withdrew is a convention for this mutual ending (Q4). No upper date bound is established.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“Company F submitted a non-binding indication of interest to the Company on September 15, 2019.” (p. 31)</t>
+          <t>“Company F submitted a non-binding indication of interest to the Company on September 15, 2019. However, the parties were ultimately unable to agree on terms for the transaction.” (p. 31)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q3; Q4</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
-      <c r="T19" s="4" t="n">
-        <v>43723</v>
-      </c>
-      <c r="U19" s="4" t="n">
-        <v>43723</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>43723</v>
-      </c>
+      <c r="T19" s="3" t="n">
+        <v>43724</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>43724</v>
+      </c>
+      <c r="V19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1733,12 +1743,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>after 09/15/2019</t>
+          <t>October 2019</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Company F</t>
+          <t>Company C</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1757,8 +1767,8 @@
       <c r="G20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
@@ -1767,29 +1777,35 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Terms or process</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Talks ended because the parties could not agree on terms; the filing does not say which side ended them. Undated.</t>
+          <t>The Company and Company C 'mutually agreed' not to pursue a transaction, after further discussion and Canaccord's engagement; no reason given. Recorded as Withdrew for a mutual ending (Q4). Leaves only Company E's portal NDA open.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“However, the parties were ultimately unable to agree on terms for the transaction.” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="n"/>
+          <t>“the Company and Company C mutually agreed in October 2019 not to pursue a transaction” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
-      <c r="T20" s="4" t="n">
-        <v>43723</v>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>43723</v>
-      </c>
-      <c r="V20" s="4" t="n"/>
+      <c r="T20" s="3" t="n">
+        <v>43754</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>43739</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>43769</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1797,64 +1813,64 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>October 2019</t>
+          <t>07/13/2020</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Company C</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Process restarted</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Mutual decision by the Company and Company C not to pursue a deal, after further talks and Canaccord’s evaluation. Label reflects a joint decision; no reason stated. Process 2 then lapsed.</t>
+          <t>Inferred restart. Last acquirer contact before the gap: Company C talks ended October 2019 (Company F's end undated). Fresh start: Company E's approach taken up and outreach launched. Closes Company E's open process-2 participation (portal NDA, #11).</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“the Company and Company C mutually agreed in October 2019 not to pursue a transaction” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="n"/>
+          <t>“As a result of this outreach, the Company directed Canaccord Genuity to reach out to Company E for further information about a potential strategic transaction” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q2</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="n"/>
-      <c r="T21" s="4" t="n">
-        <v>43754</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>43739</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>43769</v>
+      <c r="T21" s="3" t="n">
+        <v>44025</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>44025</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>44025</v>
       </c>
     </row>
     <row r="22">
@@ -1868,13 +1884,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
+          <t>Company E</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Process restarted</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1883,8 +1903,8 @@
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
@@ -1892,34 +1912,26 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Inferred restart at Company E’s new approach (#22). Process 2 lapsed: last reported acquirer contact October 2019 (Company C); F’s end and Canaccord’s 18 contacts undated (engagement to 01/15/2020). Company D deal (Jan–Jun 2020) excluded (Q2). Closes Company E’s process-2 participation (#13).</t>
+          <t>Director Kevin Rendino relayed Company E's interest in acquiring the whole Company; Rendino had invested alongside E through affiliated entities. Bidder-led first contact in process 3; the Company then had Canaccord contact E.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Kevin Rendino, informed the Company’s management of potential interest that Company E had in a potential acquisition of the Company.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q2</t>
-        </is>
-      </c>
+          <t>“Mr. Kevin Rendino, informed the Company’s management of potential interest that Company E had in a potential acquisition of the Company” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
-      <c r="T22" s="4" t="n">
+      <c r="T22" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="U22" s="4" t="n">
+      <c r="U22" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="V22" s="4" t="n">
+      <c r="V22" s="3" t="n">
         <v>44025</v>
       </c>
     </row>
@@ -1934,17 +1946,13 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Canaccord Genuity LLC</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1953,35 +1961,33 @@
       <c r="G23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Company E’s interest in acquiring the whole company relayed by director Kevin Rendino, who had co-invested with E. Company directed Canaccord to contact E. Bidder-led first contact in process 3.</t>
+          <t>Target's financial adviser, acting in process 3 from 07/13/2020; engagement letter amended 07/30/2020 (term to 01/31/2021) and 01/25/2021 (to 06/30/2021). Gave the $2.20 fairness opinion on 02/10/2021.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“informed the Company’s management of potential interest that Company E had in a potential acquisition of the Company” (p. 32)</t>
+          <t>“the Company directed Canaccord Genuity to reach out to Company E for further information about a potential strategic transaction” (p. 32)</t>
         </is>
       </c>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
-      <c r="T23" s="4" t="n">
+      <c r="T23" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="U23" s="4" t="n">
+      <c r="U23" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="V23" s="4" t="n">
+      <c r="V23" s="3" t="n">
         <v>44025</v>
       </c>
     </row>
@@ -2015,8 +2021,8 @@
       <c r="G24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
@@ -2027,7 +2033,7 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Amendment to E’s 07/30/2019 NDA (#13), extending the standstill to 07/30/2021. Row records the agreement’s application to this process on this day, not its original execution. Entry of Company E in process 3.</t>
+          <t>Amendment to E's 07/30/2019 mutual NDA extending the standstill (no proposals without invitation) to 07/30/2021. A newly executed instrument, so E's entry to process 3.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2035,19 +2041,15 @@
           <t>“on July 13, 2020, the Company and Company E entered into an amendment to their non-disclosure agreement entered into on July 30, 2019” (p. 32)</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+      <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
-      <c r="T24" s="4" t="n">
+      <c r="T24" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="U24" s="4" t="n">
+      <c r="U24" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="V24" s="4" t="n">
+      <c r="V24" s="3" t="n">
         <v>44025</v>
       </c>
     </row>
@@ -2057,18 +2059,18 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/13/2020</t>
+          <t>after 07/13/2020 (undated)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Canaccord Genuity LLC</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2077,8 +2079,8 @@
       <c r="G25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
@@ -2087,24 +2089,24 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Target’s financial adviser, first seen acting in process 3 (directed to contact E). Re-engaged 01/02/2020 for the Company D deal; letter amended 07/30/2020 (term to 01/31/2021) and 01/25/2021 (to 06/30/2021). Gave the 02/10/2021 fairness opinion.</t>
+          <t>The Company directed Canaccord to begin outreach on an acquisition of the whole Company and/or its software and services business; no Board meeting is reported. Window: after E's 07/13 approach, before outreach began in mid-July.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“the Company directed Canaccord Genuity to reach out to Company E for further information about a potential strategic transaction” (p. 32)</t>
+          <t>“The Company also then directed Canaccord Genuity to commence outreach to various parties to consider an acquisition of the Company and/or its software and services business” (p. 32)</t>
         </is>
       </c>
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
-      <c r="T25" s="4" t="n">
+      <c r="T25" s="3" t="n">
+        <v>44028</v>
+      </c>
+      <c r="U25" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="U25" s="4" t="n">
-        <v>44025</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>44025</v>
+      <c r="V25" s="3" t="n">
+        <v>44031</v>
       </c>
     </row>
     <row r="26">
@@ -2118,23 +2120,23 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
@@ -2143,23 +2145,27 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Company directed Canaccord to begin outreach about an acquisition of the whole company and/or only its software and services business. Follows the 07/13/2020 E contact.</t>
+          <t>Canaccord's outreach wave from mid-July (#26). Parties still involved were asked for non-binding IOIs by 09/17/2020; when that request was made is not stated, so no separate Deadline set row. Company E carried in from round 0.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“The Company also then directed Canaccord Genuity to commence outreach to various parties to consider an acquisition of the Company and/or its software and services business.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="n"/>
+          <t>“Parties that remained involved in the process were requested to submit a non-binding indication of interest by September 17, 2020” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="4" t="n">
+      <c r="T26" s="3" t="n">
         <v>44028</v>
       </c>
-      <c r="U26" s="4" t="n">
+      <c r="U26" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="V26" s="4" t="n">
+      <c r="V26" s="3" t="n">
         <v>44031</v>
       </c>
     </row>
@@ -2169,18 +2175,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>mid-July 2020</t>
+          <t>mid-July to mid-September 2020</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n"/>
+          <t>37 parties (Canaccord outreach, other than Companies A-D)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2189,17 +2199,19 @@
       <c r="G27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="n"/>
+      <c r="M27" s="2" t="n">
+        <v>37</v>
+      </c>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Round 1 opens with Canaccord’s outreach (#27), plus management outreach on the portal business (#28). NDA signers got confidential information; remaining parties asked for non-binding IOIs by 09/17/2020 (#30).</t>
+          <t>Target-initiated contacts about the whole Company and/or its software and services business; types not given. Company H is established as one of them (#35); CLP and Company G may be. Of the 37, 14 signed NDAs (#28).</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -2207,20 +2219,16 @@
           <t>“From the middle of July 2020 to the middle of September 2020, Canaccord Genuity reached out to 37 parties (other than Companies A-D)” (p. 32)</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
-      <c r="T27" s="4" t="n">
-        <v>44028</v>
-      </c>
-      <c r="U27" s="4" t="n">
+      <c r="T27" s="3" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="V27" s="4" t="n">
-        <v>44031</v>
+      <c r="V27" s="3" t="n">
+        <v>44093</v>
       </c>
     </row>
     <row r="28">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>37 parties (Canaccord outreach), incl. CLP, Company G, Company H</t>
+          <t>8 parties (portal and advertising business, management outreach)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2253,39 +2261,39 @@
       <c r="G28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated outreach. Excludes Companies A–D; E, which approached first, is treated as outside the 37 (Q4). CLP, G and H are members: the filing counts IOIs “described below” as coming from this outreach (CLP, G), and H’s interest arose from it. Type split not given.</t>
+          <t>At the same time as #26, management contacted 8 parties about buying only the portal and advertising business (segment). None is reported to have signed an NDA or bid in this window.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“Other than as described below, none of the outreach attempts to these 37 parties ultimately led to an indication of interest” (p. 32)</t>
+          <t>“the Company’s management reached out to 8 parties to determine whether such parties would be interested in exploring a potential acquisition of the portal and advertising business” (p. 32)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S28" s="2" t="n"/>
-      <c r="T28" s="4" t="n">
-        <v>44028</v>
-      </c>
-      <c r="U28" s="4" t="n">
+      <c r="T28" s="3" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U28" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="V28" s="4" t="n">
+      <c r="V28" s="3" t="n">
         <v>44093</v>
       </c>
     </row>
@@ -2300,7 +2308,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8 parties (portal and advertising business outreach)</t>
+          <t>NDA signers from Canaccord outreach (14 stated; 13-14 besides CLP)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2310,7 +2318,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2319,37 +2327,37 @@
       <c r="G29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Target management outreach about buying the portal and advertising business only, alongside Canaccord’s outreach. Type split not given.</t>
+          <t>Count: 13-14. Filing: 14 of the 37 contacted signed NDAs and received confidential information. CLP's 09/08/2020 agreement (#29) may be one of the 14; Company G and Company H may also be members (Q5). Execution dates not given.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“the Company’s management reached out to 8 parties to determine whether such parties would be interested in exploring a potential acquisition of the portal and advertising business.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="n"/>
+          <t>“Of the parties contacted, 14 parties executed non-disclosure agreements with the Company and were provided access to confidential information relating to the Company’s business and prospects” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="n"/>
-      <c r="T29" s="4" t="n">
-        <v>44028</v>
-      </c>
-      <c r="U29" s="4" t="n">
+      <c r="T29" s="3" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>44025</v>
       </c>
-      <c r="V29" s="4" t="n">
-        <v>44093</v>
-      </c>
+      <c r="V29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2357,17 +2365,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>mid-July to mid-September 2020</t>
+          <t>09/08/2020</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13 other NDA signers from Canaccord outreach</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2381,40 +2389,40 @@
       <c r="G30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Residual of the 14 parties that signed NDAs and got confidential information: 14 − CLP (#31) = 13. Signing dates not given. Could include Company G or H; neither is shown to have signed (Q4).</t>
+          <t>Confidentiality Agreement with a standstill (12 months or earlier significant event). CLP is a private-equity manager; Parent is controlled by its fund CLP Fund V. Whether CLP came through Canaccord's outreach and is one of the 14 signers is not stated (Q5).</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“Of the parties contacted, 14 parties executed non-disclosure agreements with the Company and were provided access to confidential information” (p. 32)</t>
+          <t>“On September 8, 2020, Centre Lane Partners, LLC (“CLP”) entered into the Confidentiality Agreement (as defined herein) with the Company, which included a standstill provision” (p. 32)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S30" s="2" t="n"/>
-      <c r="T30" s="4" t="n">
-        <v>44028</v>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>44025</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>44093</v>
+      <c r="T30" s="3" t="n">
+        <v>44082</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>44082</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>44082</v>
       </c>
     </row>
     <row r="31">
@@ -2423,18 +2431,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>undated, before 09/17/2020</t>
+          <t>09/10/2020</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
+          <t>Company E</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2443,38 +2455,52 @@
       <c r="G31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
+      <c r="H31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Parties still in the process asked for non-binding IOIs by 09/17/2020. Communication day not reported; window runs from the start of outreach to the day before the due date.</t>
+          <t>No condition or financing source reported; E's diligence began only after 09/23 (#46). Non-binding LOI, all cash, for 100% of equity and equity awards at $2.00; 180 Degree (Rendino affiliate) to roll over its stake. Before the 09/17 due date.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“Parties that remained involved in the process were requested to submit a non-binding indication of interest by September 17, 2020.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“for an all-cash transaction to acquire 100% of the Company’s outstanding equity and equity awards at a per Share price of $2.00” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
-      <c r="T31" s="4" t="n">
-        <v>44057</v>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>44025</v>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>44090</v>
+      <c r="T31" s="3" t="n">
+        <v>44084</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>44084</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>44084</v>
       </c>
     </row>
     <row r="32">
@@ -2483,22 +2509,18 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>09/08/2020</t>
+          <t>09/13/2020</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Gunderson Dettmer</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2507,36 +2529,34 @@
       <c r="G32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality Agreement with standstill; CLP is a private-fund manager, buyer vehicle backed by CLP Fund V (p. 28). One of the 14 NDA signers. Filing (p. 27) says Synacor gave CLP certain internal projections; undated, so no separate row. Entry of CLP.</t>
+          <t>Target's outside corporate counsel; first shown acting at the 09/13/2020 Board meeting.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“On September 8, 2020, Centre Lane Partners, LLC (“CLP”) entered into the Confidentiality Agreement (as defined herein) with the Company, which included a standstill provision” (p. 32)</t>
+          <t>“the Company’s outside corporate counsel, Gunderson Dettmer (“Gunderson”)” (p. 32)</t>
         </is>
       </c>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
-      <c r="T32" s="4" t="n">
-        <v>44082</v>
-      </c>
-      <c r="U32" s="4" t="n">
-        <v>44082</v>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>44082</v>
+      <c r="T32" s="3" t="n">
+        <v>44087</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>44087</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>44087</v>
       </c>
     </row>
     <row r="33">
@@ -2545,22 +2565,18 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>09/10/2020</t>
+          <t>09/13/2020</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2569,52 +2585,34 @@
       <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: diligence began only after the 09/23 LOI. Non-binding LOI, $2.00 cash per share for 100% of equity and awards; 180 Degree (director Rendino’s affiliate) to roll over its stake.</t>
+          <t>Board forms a Special Committee (Bhise, Kau, Donohue, Fawaz, Montgomery) to lead negotiations with Company E because director Rendino had invested alongside E; Rendino recuses from E matters. The Board also reviewed E's LOI and outreach feedback.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“an all-cash transaction to acquire 100% of the Company’s outstanding equity and equity awards at a per Share price of $2.00” (p. 32)</t>
+          <t>“The Company Special Committee was authorized to lead the negotiations with Company E on behalf of the Company” (p. 32)</t>
         </is>
       </c>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
-      <c r="T33" s="4" t="n">
-        <v>44084</v>
-      </c>
-      <c r="U33" s="4" t="n">
-        <v>44084</v>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>44084</v>
+      <c r="T33" s="3" t="n">
+        <v>44087</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>44087</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>44087</v>
       </c>
     </row>
     <row r="34">
@@ -2623,18 +2621,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/13/2020</t>
+          <t>09/14/2020</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Gunderson Dettmer</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t>Company G</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2643,34 +2645,52 @@
       <c r="G34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Target’s outside corporate (legal) counsel; first seen acting at the 09/13/2020 board meeting.</t>
+          <t>Financing: equity plus third-party debt, commitment status not stated. Non-binding IOI for only the software and services business; valuation 'a fraction' of E's implied value, no per-share price. G regularly invests in enterprise software. Entry by bid; no NDA reported (Q3).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“the Company’s outside corporate counsel, Gunderson Dettmer (“Gunderson”)” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="n"/>
+          <t>“Company G proposed paying cash for the purchase price, but Company G indicated that it would utilize equity and third party debt financing to finance the transaction” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S34" s="2" t="n"/>
-      <c r="T34" s="4" t="n">
-        <v>44087</v>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>44087</v>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>44087</v>
+      <c r="T34" s="3" t="n">
+        <v>44088</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>44088</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>44088</v>
       </c>
     </row>
     <row r="35">
@@ -2679,12 +2699,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/13/2020</t>
+          <t>09/14/2020</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
+          <t>180 Degree Capital Corp.</t>
         </is>
       </c>
       <c r="D35" s="2" t="n"/>
@@ -2699,8 +2719,8 @@
       <c r="G35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
@@ -2709,24 +2729,24 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Board formed a Special Committee of the five other directors to lead negotiations with E, because of Rendino’s past co-investments with E; Rendino recused himself.</t>
+          <t>Rollover support: 180 Degree (affiliate of director Rendino; later a Tender and Support Agreement signatory) told Gunderson it supported rolling its equity into E's proposed deal, subject to due diligence. Supports E; not a bidding group (E4).</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“The Company Special Committee was authorized to lead the negotiations with Company E on behalf of the Company.” (p. 32)</t>
+          <t>“180 Degree, an affiliate of Mr. Rendino, confirmed to Gunderson that it was supportive of rolling over its existing equity position in the Company as part of the proposed transaction” (p. 33)</t>
         </is>
       </c>
       <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
-      <c r="T35" s="4" t="n">
-        <v>44087</v>
-      </c>
-      <c r="U35" s="4" t="n">
-        <v>44087</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>44087</v>
+      <c r="T35" s="3" t="n">
+        <v>44088</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>44088</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>44088</v>
       </c>
     </row>
     <row r="36">
@@ -2735,22 +2755,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>09/14/2020</t>
+          <t>09/16/2020</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Company G</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2759,23 +2779,11 @@
       <c r="G36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n">
         <v>1</v>
       </c>
@@ -2783,28 +2791,24 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Non-binding IOI for the software and services business only. Valued only as a “fraction” of E’s implied value on an enterprise-value basis; no per-share price. Cash, financed with equity and third-party debt (commitment not stated). Entry of Company G.</t>
+          <t>Canaccord reports that Company H, a public-company software acquirer reached in its outreach, has 'more serious interest' but cannot yet submit an LOI. No NDA or bid is reported for H, so no entry. Committee also met E's representatives.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“proposed acquiring only the Company’s software and services business” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q4</t>
-        </is>
-      </c>
+          <t>“had also expressed more serious interest in an acquisition of the Company, but was not yet in a position to submit a letter of intent” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
-      <c r="T36" s="4" t="n">
-        <v>44088</v>
-      </c>
-      <c r="U36" s="4" t="n">
-        <v>44088</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>44088</v>
+      <c r="T36" s="3" t="n">
+        <v>44090</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>44090</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>44090</v>
       </c>
     </row>
     <row r="37">
@@ -2813,12 +2817,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>09/14/2020</t>
+          <t>09/17/2020</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>180 Degree Capital (affiliate of director Rendino)</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D37" s="2" t="n"/>
@@ -2833,8 +2837,8 @@
       <c r="G37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
@@ -2843,24 +2847,28 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Rollover relationship formed: shareholder 180 Degree confirmed to Gunderson it supports rolling over its equity in E’s deal (#32), subject to diligence. Not a bidding group (C4). Became moot when E dropped its 100% offer (#57).</t>
+          <t>Price request: the Company sent Company E a revised LOI asking for its best offer on price, and Canaccord repeated it by phone. Treated as bargaining within round 1, not a best-and-final round (Q6).</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“180 Degree, an affiliate of Mr. Rendino, confirmed to Gunderson that it was supportive of rolling over its existing equity position in the Company” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="n"/>
+          <t>“the Company submitted a revised letter of intent to Company E, which included a request for Company E to provide its best offer on purchase price” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="n"/>
-      <c r="T37" s="4" t="n">
-        <v>44088</v>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>44088</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>44088</v>
+      <c r="T37" s="3" t="n">
+        <v>44091</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>44091</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>44091</v>
       </c>
     </row>
     <row r="38">
@@ -2874,13 +2882,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n"/>
+          <t>CLP (Centre Lane Partners, LLC)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -2889,37 +2901,51 @@
       <c r="G38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
+      <c r="H38" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Target sent E a revised LOI asking for its best price; Canaccord later relayed the request by phone. Not treated as a final-round solicitation (Q6).</t>
+          <t>Financing from committed capital of CLP's private equity vehicles, but diligence still open (#44 is 'subject to further diligence'). Non-binding IOI for 100% of equity and equity awards at $1.35-$1.41 cash, on the due date. CLP's first bid.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“the Company submitted a revised letter of intent to Company E, which included a request for Company E to provide its best offer on purchase price” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q6</t>
-        </is>
-      </c>
+          <t>“contemplated a purchase price of $1.35 to $1.41 per Share. CLP proposed paying cash for the purchase price by utilizing committed capital from its private equity vehicles” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
-      <c r="T38" s="4" t="n">
+      <c r="T38" s="3" t="n">
         <v>44091</v>
       </c>
-      <c r="U38" s="4" t="n">
+      <c r="U38" s="3" t="n">
         <v>44091</v>
       </c>
-      <c r="V38" s="4" t="n">
+      <c r="V38" s="3" t="n">
         <v>44091</v>
       </c>
     </row>
@@ -2934,17 +2960,13 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -2953,51 +2975,37 @@
       <c r="G39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: CLP’s 09/22 signal was “subject to further diligence”. Non-binding IOI for 100% at $1.35–$1.41 per share, cash from committed capital in CLP’s private equity vehicles.</t>
+          <t>Due date for round-1 non-binding IOIs. Received by then: Company E (#30), Company G (#33, segment only) and CLP (#37). The target then acted on these bids (outcome, Q7).</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“from CLP for an acquisition of 100% of the Company’s outstanding equity and equity awards and contemplated a purchase price of $1.35 to $1.41 per Share” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="n"/>
+          <t>“requested to submit a non-binding indication of interest by September 17, 2020” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="n"/>
-      <c r="T39" s="4" t="n">
+      <c r="T39" s="3" t="n">
         <v>44091</v>
       </c>
-      <c r="U39" s="4" t="n">
+      <c r="U39" s="3" t="n">
         <v>44091</v>
       </c>
-      <c r="V39" s="4" t="n">
+      <c r="V39" s="3" t="n">
         <v>44091</v>
       </c>
     </row>
@@ -3007,18 +3015,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>09/17/2020</t>
+          <t>by 09/17/2020</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
+          <t>Outreach NDA signers without an IOI</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -3027,22 +3039,30 @@
       <c r="G40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>IOI due date reached. By then: E (#32), G (#35) and CLP (#38) had submitted; H had not. No extension. Next steps on bids in hand: price-improvement requests, then exclusivity with E on 09/23 (Q5).</t>
+          <t>Count: 12-14. 14 NDA signers minus submitters among them (CLP, Company G; membership not stated) = 12-14. Filing: no other outreach party produced an IOI. Some were 'still conducting diligence' on 09/16 and may have lasted until talks ended 09/23 (#47).</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“Parties that remained involved in the process were requested to submit a non-binding indication of interest by September 17, 2020.” (p. 32)</t>
+          <t>“Other than as described below, none of the outreach attempts to these 37 parties ultimately led to an indication of interest from any of these parties” (p. 32)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -3051,13 +3071,11 @@
         </is>
       </c>
       <c r="S40" s="2" t="n"/>
-      <c r="T40" s="4" t="n">
+      <c r="T40" s="3" t="n">
         <v>44091</v>
       </c>
-      <c r="U40" s="4" t="n">
-        <v>44091</v>
-      </c>
-      <c r="V40" s="4" t="n">
+      <c r="U40" s="2" t="n"/>
+      <c r="V40" s="3" t="n">
         <v>44091</v>
       </c>
     </row>
@@ -3067,22 +3085,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>by 09/17/2020</t>
+          <t>09/18/2020</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>13 other NDA signers from Canaccord outreach</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -3091,46 +3109,56 @@
       <c r="G41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
+      <c r="H41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Inferred: 14 NDA signers − CLP = 13 with no IOI; the filing says no other outreach party produced an IOI. Some were still in diligence on 09/16. Any still active had talks ended at E exclusivity on 09/23 (#47). Count assumes G and H are not among them (Q4).</t>
+          <t>Heavy: asks for exclusivity until 10/23/2020 (about five weeks) for diligence and documents. Revised LOI answering #36, 're-affirming' E would only pay $2.00 cash for 100%; 180 Degree rollover kept.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“Other than as described below, none of the outreach attempts to these 37 parties ultimately led to an indication of interest from any of these parties” (p. 32)</t>
+          <t>“it would only pay $2.00 per Share in connection with its acquisition of the Company, and requesting that the Company enter into exclusivity with it until October 23, 2020” (p. 33)</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S41" s="2" t="n"/>
-      <c r="T41" s="4" t="n">
-        <v>44091</v>
-      </c>
-      <c r="U41" s="4" t="n"/>
-      <c r="V41" s="4" t="n">
-        <v>44091</v>
+      <c r="T41" s="3" t="n">
+        <v>44092</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>44092</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>44092</v>
       </c>
     </row>
     <row r="42">
@@ -3154,7 +3182,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -3163,27 +3191,11 @@
       <c r="G42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n">
         <v>1</v>
       </c>
@@ -3191,27 +3203,23 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Asked for exclusivity to 10/23/2020 (about five weeks) before starting diligence; 180 Degree rollover still subject to its diligence. Revised LOI reaffirms $2.00 per share in reply to the best-offer request (#37); price carried from #32.</t>
+          <t>Requested: Company E's revised LOI asks the Company to enter exclusivity with it until 10/23/2020.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“Company E provided a revised letter of intent to the Company, re-affirming that it would only pay $2.00 per Share” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“requesting that the Company enter into exclusivity with it until October 23, 2020” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
-      <c r="T42" s="4" t="n">
+      <c r="T42" s="3" t="n">
         <v>44092</v>
       </c>
-      <c r="U42" s="4" t="n">
+      <c r="U42" s="3" t="n">
         <v>44092</v>
       </c>
-      <c r="V42" s="4" t="n">
+      <c r="V42" s="3" t="n">
         <v>44092</v>
       </c>
     </row>
@@ -3226,7 +3234,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D43" s="2" t="n"/>
@@ -3241,8 +3249,8 @@
       <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
@@ -3251,7 +3259,7 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Special Committee told Canaccord to seek higher prices from G (software segment) and CLP (100%).</t>
+          <t>Price requests: the Special Committee directs Canaccord to ask Company G to raise its software-and-services price and CLP to raise its whole-company price. It also reviewed E's revised LOI.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -3261,13 +3269,13 @@
       </c>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
-      <c r="T43" s="4" t="n">
+      <c r="T43" s="3" t="n">
         <v>44095</v>
       </c>
-      <c r="U43" s="4" t="n">
+      <c r="U43" s="3" t="n">
         <v>44095</v>
       </c>
-      <c r="V43" s="4" t="n">
+      <c r="V43" s="3" t="n">
         <v>44095</v>
       </c>
     </row>
@@ -3282,7 +3290,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
+          <t>Company G</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3301,8 +3309,8 @@
       <c r="G44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
@@ -3313,27 +3321,23 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Price signal without an offer: CLP said verbally it would consider raising its price 10–25% per share over #38, subject to further diligence. Not recorded as a Bid (Q7). G said the same day it could not raise its price.</t>
+          <t>Asked to improve (#42), Company G says it cannot raise its software-and-services price; its IOI (#33) stands.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“CLP provided a verbal indication that, subject to further diligence, it would consider increasing its purchase price by 10% to 25% per Share” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
+          <t>“Company G was unable to increase its purchase price” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
-      <c r="T44" s="4" t="n">
+      <c r="T44" s="3" t="n">
         <v>44096</v>
       </c>
-      <c r="U44" s="4" t="n">
+      <c r="U44" s="3" t="n">
         <v>44096</v>
       </c>
-      <c r="V44" s="4" t="n">
+      <c r="V44" s="3" t="n">
         <v>44096</v>
       </c>
     </row>
@@ -3348,17 +3352,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3367,11 +3371,23 @@
       <c r="G45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="n">
         <v>1</v>
       </c>
@@ -3379,27 +3395,27 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Target invited a bid: CEO Himesh Bhise urged public-company software acquirer H to submit a whole-company proposal. H had shown “more serious interest” through the outreach (09/16) but had no LOI. Treated as H’s admission and entry (Q4, Q8).</t>
+          <t>Heavy: 'subject to further diligence'. Verbal: CLP 'would consider' raising its $1.35-$1.41 IOI (#37) by 10%-25% per share. No per-share figure stated (arithmetic implies about $1.49-$1.76), so price cells blank (Q8).</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“encourage it to submit a proposal relating to a potential acquisition of 100% of the Company’s outstanding equity and equity awards” (p. 34)</t>
+          <t>“CLP provided a verbal indication that, subject to further diligence, it would consider increasing its purchase price by 10% to 25% per Share” (p. 33)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q8</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S45" s="2" t="n"/>
-      <c r="T45" s="4" t="n">
+      <c r="T45" s="3" t="n">
         <v>44096</v>
       </c>
-      <c r="U45" s="4" t="n">
+      <c r="U45" s="3" t="n">
         <v>44096</v>
       </c>
-      <c r="V45" s="4" t="n">
+      <c r="V45" s="3" t="n">
         <v>44096</v>
       </c>
     </row>
@@ -3414,17 +3430,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Other potential portal-business buyers (Bhise outreach)</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3433,33 +3449,39 @@
       <c r="G46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
+      <c r="M46" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated: CEO Bhise contacted other companies that might buy the portal and advertising business; none would propose in the near term. Count: unknown; may overlap the 8 in #28.</t>
+          <t>After the 09/17 due date, CEO Bhise urged Company H to submit a whole-company proposal and also contacted possible portal buyers. None said it would propose in the near term.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Bhise also reached out to other companies which the Company believed may have an interest in acquiring the Company’s portal and advertising business.” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="n"/>
+          <t>“None of these parties indicated that they would be submitting a potential proposal in the near term” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="n"/>
-      <c r="T46" s="4" t="n">
+      <c r="T46" s="3" t="n">
         <v>44096</v>
       </c>
-      <c r="U46" s="4" t="n">
+      <c r="U46" s="3" t="n">
         <v>44096</v>
       </c>
-      <c r="V46" s="4" t="n">
+      <c r="V46" s="3" t="n">
         <v>44096</v>
       </c>
     </row>
@@ -3474,13 +3496,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n"/>
+          <t>Company E</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3489,17 +3515,19 @@
       <c r="G47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
+      <c r="M47" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Round 2 opens as the target moves to exclusive diligence and definitive-agreement negotiation with E alone (#47).</t>
+          <t>Executed: the Company entered Company E's LOI, with exclusivity to 10/23/2020, and began diligence and documentation. The Company and Canaccord ended other active discussions.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -3507,19 +3535,15 @@
           <t>“On September 23, 2020, the Company and Company E entered into Company E’s letter of intent, and began coordination to commence diligence and prepare documentation” (p. 34)</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
-      <c r="T47" s="4" t="n">
+      <c r="T47" s="3" t="n">
         <v>44097</v>
       </c>
-      <c r="U47" s="4" t="n">
+      <c r="U47" s="3" t="n">
         <v>44097</v>
       </c>
-      <c r="V47" s="4" t="n">
+      <c r="V47" s="3" t="n">
         <v>44097</v>
       </c>
     </row>
@@ -3534,17 +3558,13 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3553,19 +3573,17 @@
       <c r="G48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity executed with E through 10/23/2020 via the signed $2.00 LOI (#41). The Company and Canaccord ended other active discussions.</t>
+          <t>Move to exclusive definitive negotiation with Company E after a non-final round; E (1 financial bidder) admitted and given diligence from September through December. No due date set.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -3573,15 +3591,19 @@
           <t>“As a result of the exclusivity provisions in the letter of intent, the Company and Canaccord Genuity also terminated other active discussions with other parties” (p. 34)</t>
         </is>
       </c>
-      <c r="R48" s="2" t="n"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="n"/>
-      <c r="T48" s="4" t="n">
+      <c r="T48" s="3" t="n">
         <v>44097</v>
       </c>
-      <c r="U48" s="4" t="n">
+      <c r="U48" s="3" t="n">
         <v>44097</v>
       </c>
-      <c r="V48" s="4" t="n">
+      <c r="V48" s="3" t="n">
         <v>44097</v>
       </c>
     </row>
@@ -3596,7 +3618,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3615,8 +3637,8 @@
       <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
       <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
@@ -3631,7 +3653,7 @@
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Talks ended because of E’s exclusivity. CLP’s standing IOI $1.35–$1.41 (#38) against E’s $2.00.</t>
+          <t>Reported: other active discussions ended because of E's exclusivity; CLP was in active price talks (#44). CLP's $1.35-$1.41 was below E's $2.00, but the filing gives exclusivity, not price, as the reason.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -3641,13 +3663,13 @@
       </c>
       <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
-      <c r="T49" s="4" t="n">
+      <c r="T49" s="3" t="n">
         <v>44097</v>
       </c>
-      <c r="U49" s="4" t="n">
+      <c r="U49" s="3" t="n">
         <v>44097</v>
       </c>
-      <c r="V49" s="4" t="n">
+      <c r="V49" s="3" t="n">
         <v>44097</v>
       </c>
     </row>
@@ -3681,8 +3703,8 @@
       <c r="G50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
@@ -3691,13 +3713,13 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Terms or process</t>
+          <t>Would not improve earlier offer</t>
         </is>
       </c>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Talks ended because of E’s exclusivity. On 09/22 G said it could not raise its segment price (#35). In Dec 2020 G again declined to go higher and did not re-enter.</t>
+          <t>Other active discussions ended for E's exclusivity. G had just declined to raise its price when asked (#43), so E14 gives 'Would not improve earlier offer'. Segment bidder (Q3).</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -3705,15 +3727,19 @@
           <t>“the Company and Canaccord Genuity also terminated other active discussions with other parties relating to a proposed transaction at such time” (p. 34)</t>
         </is>
       </c>
-      <c r="R50" s="2" t="n"/>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S50" s="2" t="n"/>
-      <c r="T50" s="4" t="n">
+      <c r="T50" s="3" t="n">
         <v>44097</v>
       </c>
-      <c r="U50" s="4" t="n">
+      <c r="U50" s="3" t="n">
         <v>44097</v>
       </c>
-      <c r="V50" s="4" t="n">
+      <c r="V50" s="3" t="n">
         <v>44097</v>
       </c>
     </row>
@@ -3723,64 +3749,60 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>09/23/2020</t>
+          <t>10/23/2020</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
+      <c r="N51" s="2" t="n"/>
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Talks ended because of E’s exclusivity; H had not submitted a proposal.</t>
+          <t>Ended: Company E's exclusivity expired under the LOI's terms; negotiation with E continued without exclusivity.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“the Company and Canaccord Genuity also terminated other active discussions with other parties relating to a proposed transaction at such time” (p. 34)</t>
+          <t>“On October 23, 2020, the exclusivity period that the Company had agreed upon with Company E expired in accordance with the terms of the executed letter of intent” (p. 34)</t>
         </is>
       </c>
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
-      <c r="T51" s="4" t="n">
-        <v>44097</v>
-      </c>
-      <c r="U51" s="4" t="n">
-        <v>44097</v>
-      </c>
-      <c r="V51" s="4" t="n">
-        <v>44097</v>
+      <c r="T51" s="3" t="n">
+        <v>44127</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>44127</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>44127</v>
       </c>
     </row>
     <row r="52">
@@ -3789,22 +3811,18 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>10/23/2020</t>
+          <t>10/27/2020</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -3813,36 +3831,38 @@
       <c r="G52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>E’s exclusivity expired under the LOI without a definitive agreement; negotiations with E continued without exclusivity.</t>
+          <t>With talks with Company E slowing, the Special Committee asks Canaccord to re-initiate outreach to parties that had shown interest, while E negotiations continue. Reopens competition inside round 2 (alternative round boundary, Q1).</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“On October 23, 2020, the exclusivity period that the Company had agreed upon with Company E expired in accordance with the terms of the executed letter of intent” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="n"/>
+          <t>“requested that Canaccord Genuity re-initiate outreach to various parties which had previously expressed some interest in a transaction with the Company” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S52" s="2" t="n"/>
-      <c r="T52" s="4" t="n">
-        <v>44127</v>
-      </c>
-      <c r="U52" s="4" t="n">
-        <v>44127</v>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>44127</v>
+      <c r="T52" s="3" t="n">
+        <v>44131</v>
+      </c>
+      <c r="U52" s="3" t="n">
+        <v>44131</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>44131</v>
       </c>
     </row>
     <row r="53">
@@ -3856,52 +3876,54 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
+          <t>Company H</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
+      <c r="M53" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Round 3 opens: as E’s pace slowed, the Special Committee asked Canaccord to restart outreach to parties that had shown interest. E’s non-exclusive negotiation continued. No due date.</t>
+          <t>Bhise re-contacts Company H; H remains interested and asks for updated financial information on the Company (whether provided is not stated).</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“requested that Canaccord Genuity re-initiate outreach to various parties which had previously expressed some interest in a transaction with the Company” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Company H indicated that it remained interested and requested updated financial information for the Company” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
-      <c r="T53" s="4" t="n">
+      <c r="T53" s="3" t="n">
         <v>44131</v>
       </c>
-      <c r="U53" s="4" t="n">
+      <c r="U53" s="3" t="n">
         <v>44131</v>
       </c>
-      <c r="V53" s="4" t="n">
+      <c r="V53" s="3" t="n">
         <v>44131</v>
       </c>
     </row>
@@ -3911,7 +3933,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>10/27/2020</t>
+          <t>11/02/2020</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3926,17 +3948,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
@@ -3947,28 +3969,24 @@
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #50: Bhise contacted H again; H said it remained interested and asked for updated financial information (whether it got it is not stated).</t>
+          <t>Company H will not submit a proposal 'at that time' while the Company is still pursuing another party (E), though still interested. Not an exit: H had not entered.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>“Company H indicated that it remained interested and requested updated financial information for the Company” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
+          <t>“it was unable to submit a proposal at that time given that the Company was separately still pursuing a strategic transaction with another third party” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
-      <c r="T54" s="4" t="n">
-        <v>44131</v>
-      </c>
-      <c r="U54" s="4" t="n">
-        <v>44131</v>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>44131</v>
+      <c r="T54" s="3" t="n">
+        <v>44137</v>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>44137</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>44137</v>
       </c>
     </row>
     <row r="55">
@@ -3977,12 +3995,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/02/2020</t>
+          <t>11/19/2020</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>Company I</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3992,53 +4010,49 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
+      <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>H stopped “at that time”: still interested but would not propose while the Company pursued a deal with another party (E) (Q8).</t>
+          <t>Mutual NDA with standstills for both sides with Company I, a publicly-traded media company interested in the portal and advertising business; I then began diligence. Entry as a segment buyer (Q3).</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>“it was unable to submit a proposal at that time given that the Company was separately still pursuing a strategic transaction with another third party” (p. 34)</t>
+          <t>“On November 19, 2020, the Company entered into a mutual non-disclosure agreement with a publicly-traded media company” (p. 34)</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S55" s="2" t="n"/>
-      <c r="T55" s="4" t="n">
-        <v>44137</v>
-      </c>
-      <c r="U55" s="4" t="n">
-        <v>44137</v>
-      </c>
-      <c r="V55" s="4" t="n">
-        <v>44137</v>
+      <c r="T55" s="3" t="n">
+        <v>44154</v>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>44154</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>44154</v>
       </c>
     </row>
     <row r="56">
@@ -4047,7 +4061,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>11/19/2020</t>
+          <t>12/08/2020</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4062,20 +4076,32 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="n">
         <v>1</v>
       </c>
@@ -4083,24 +4109,28 @@
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Mutual NDA with mutual standstill; Company I (publicly traded media company) had shown interest in the portal and advertising business only. Began diligence afterwards. Entry of Company I.</t>
+          <t>No condition, financing or price reported. Non-binding LOI for solely the portal and advertising business. Bhise then re-canvassed other portal buyers; none could propose in the near term.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>“the Company entered into a mutual non-disclosure agreement with a publicly-traded media company (“Company I”), which had expressed potential interest in the Company’s portal and advertising business” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="n"/>
+          <t>“On December 8, 2020, Company I submitted a non-binding letter of intent to acquire solely the Company’s portal and advertising business” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S56" s="2" t="n"/>
-      <c r="T56" s="4" t="n">
-        <v>44154</v>
-      </c>
-      <c r="U56" s="4" t="n">
-        <v>44154</v>
-      </c>
-      <c r="V56" s="4" t="n">
-        <v>44154</v>
+      <c r="T56" s="3" t="n">
+        <v>44173</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>44173</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>44173</v>
       </c>
     </row>
     <row r="57">
@@ -4109,17 +4139,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>12/08/2020</t>
+          <t>12/14/2020</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Company I</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4131,10 +4161,14 @@
         <v>3</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -4147,7 +4181,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
@@ -4157,24 +4191,24 @@
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Non-binding LOI for the portal and advertising business only; price not disclosed; no conditions reported. Bhise then contacted other possible portal buyers again; none could propose soon.</t>
+          <t>Heavy: needs standstill waiver, new CEO (E's nominee) and CFO, three Board seats and a poison pill. Tender offer for 35% of shares at $2.00 per share (minority stake); cash not stated.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>“On December 8, 2020, Company I submitted a non-binding letter of intent to acquire solely the Company’s portal and advertising business.” (p. 34)</t>
+          <t>“so that Company E could commence a tender offer at a purchase price of $2.00 per Share for 35% of the outstanding Shares” (p. 34)</t>
         </is>
       </c>
       <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n"/>
-      <c r="T57" s="4" t="n">
-        <v>44173</v>
-      </c>
-      <c r="U57" s="4" t="n">
-        <v>44173</v>
-      </c>
-      <c r="V57" s="4" t="n">
-        <v>44173</v>
+      <c r="T57" s="3" t="n">
+        <v>44179</v>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>44179</v>
+      </c>
+      <c r="V57" s="3" t="n">
+        <v>44179</v>
       </c>
     </row>
     <row r="58">
@@ -4198,36 +4232,20 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n">
         <v>1</v>
       </c>
@@ -4235,27 +4253,23 @@
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Conditions: standstill waiver, new CEO (E’s pick) and CFO, three E board seats, NOL poison pill. Tender offer at $2.00 per share for 35% of shares only. E dropped its 100% offer (#41), mooting the rollover (#36). $2.00 is per share tendered, not a whole-company price (Q3).</t>
+          <t>Company E drops its $2.00 whole-company proposal (#40) but stays in with the partial tender (#56). Not an exit: E's participation continues to 01/04/2021 (#66).</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>“so that Company E could commence a tender offer at a purchase price of $2.00 per Share for 35% of the outstanding Shares” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“Company E advised the Company that it no longer had interest in its prior proposed transaction structure which included a purchase price of $2.00 per Share for 100%” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="n"/>
       <c r="S58" s="2" t="n"/>
-      <c r="T58" s="4" t="n">
+      <c r="T58" s="3" t="n">
         <v>44179</v>
       </c>
-      <c r="U58" s="4" t="n">
+      <c r="U58" s="3" t="n">
         <v>44179</v>
       </c>
-      <c r="V58" s="4" t="n">
+      <c r="V58" s="3" t="n">
         <v>44179</v>
       </c>
     </row>
@@ -4265,59 +4279,53 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>12/18/2020–12/21/2020</t>
+          <t>12/18/2020-12/21/2020</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
       <c r="J59" s="2" t="n"/>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M59" s="2" t="n"/>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #48: when Canaccord reached out, CLP said it might re-engage, then sped up its diligence through late December and January. In the same outreach G declined to go higher.</t>
+          <t>Canaccord re-contacts CLP, Company G and Company H, which had shown 'more serious interest'. CLP and H may re-engage; G not interested above its earlier software-and-services price, so G does not return.</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>“Each of CLP and Company H preliminarily indicated they may have continuing interest and would consider re-engaging on a proposed transaction.” (p. 35)</t>
+          <t>“Each of CLP and Company H preliminarily indicated they may have continuing interest and would consider re-engaging on a proposed transaction” (p. 35)</t>
         </is>
       </c>
       <c r="R59" s="2" t="n"/>
       <c r="S59" s="2" t="n"/>
-      <c r="T59" s="4" t="n">
+      <c r="T59" s="3" t="n">
         <v>44184</v>
       </c>
-      <c r="U59" s="4" t="n">
+      <c r="U59" s="3" t="n">
         <v>44183</v>
       </c>
-      <c r="V59" s="4" t="n">
+      <c r="V59" s="3" t="n">
         <v>44186</v>
       </c>
     </row>
@@ -4327,17 +4335,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/18/2020–12/21/2020</t>
+          <t>12/18/2020-12/21/2020</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4349,10 +4357,10 @@
         <v>3</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
@@ -4363,27 +4371,23 @@
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #54: when Canaccord reached out, H preliminarily said it might have continuing interest and would consider re-engaging.</t>
+          <t>CLP returns after its 09/23 drop (#48) and 'increased the pace of its diligence review' into January while E's proposal was pending: diligence access for CLP during E's negotiation.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>“Each of CLP and Company H preliminarily indicated they may have continuing interest and would consider re-engaging on a proposed transaction.” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
+          <t>“Following such time, CLP increased the pace of its diligence review through the end of December and into January” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
-      <c r="T60" s="4" t="n">
+      <c r="T60" s="3" t="n">
         <v>44184</v>
       </c>
-      <c r="U60" s="4" t="n">
+      <c r="U60" s="3" t="n">
         <v>44183</v>
       </c>
-      <c r="V60" s="4" t="n">
+      <c r="V60" s="3" t="n">
         <v>44186</v>
       </c>
     </row>
@@ -4415,10 +4419,10 @@
         <v>3</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -4441,23 +4445,27 @@
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>I reaffirmed interest in the portal business. Its price was only a fraction of CLP’s and partly contingent on the business’s recent performance (amount not given). The filing does not say whether it differs from #56.</t>
+          <t>Contingent pricing: part of the consideration depends on the business's recent performance; no other condition stated. Company I reaffirms interest in the portal business at pricing 'only a fraction' of CLP's; no per-share figure.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>“Company I re-affirmed its interest in a potential acquisition of the Company’s portal and advertising business, but its pricing reflected only a fraction of that being offered” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="n"/>
+          <t>“re-affirmed its interest in a potential acquisition of the Company’s portal and advertising business, but its pricing reflected only a fraction of that being offered pursuant to CLP’s offer” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S61" s="2" t="n"/>
-      <c r="T61" s="4" t="n">
+      <c r="T61" s="3" t="n">
         <v>44194</v>
       </c>
-      <c r="U61" s="4" t="n">
+      <c r="U61" s="3" t="n">
         <v>44194</v>
       </c>
-      <c r="V61" s="4" t="n">
+      <c r="V61" s="3" t="n">
         <v>44194</v>
       </c>
     </row>
@@ -4489,12 +4497,12 @@
         <v>3</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I62" s="3" t="n">
+      <c r="H62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4519,27 +4527,23 @@
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Conditions added: 20% minimum tender and a public board recommendation, on top of #57’s governance demands. Revises #57: 35% tender at $2.00 per share. Offer to expire by 01/04/2021.</t>
+          <t>Heavy: adds 20% minimum tender condition and a required public Board recommendation to #56's governance demands. Still a 35% tender at $2.00 per share; E says the proposal expires by 01/04/2021.</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>“Company E sent a letter further detailing the terms of its proposed tender offer to specify a minimum tender condition of 20%” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“further detailing the terms of its proposed tender offer to specify a minimum tender condition of 20% and to also require that the Company Board publicly recommend” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
-      <c r="T62" s="4" t="n">
+      <c r="T62" s="3" t="n">
         <v>44194</v>
       </c>
-      <c r="U62" s="4" t="n">
+      <c r="U62" s="3" t="n">
         <v>44194</v>
       </c>
-      <c r="V62" s="4" t="n">
+      <c r="V62" s="3" t="n">
         <v>44194</v>
       </c>
     </row>
@@ -4554,23 +4558,23 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
@@ -4579,7 +4583,7 @@
       <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Round 4 opens: Special Committee let E’s partial-tender offer lapse and chose to keep engaging with CLP, H and I, seeking non-binding LOIs from them. G had said it would not raise its price. No due date.</t>
+          <t>Special Committee lets Company E's partial tender offer lapse (control transfer without a premium for all holders) and continues with CLP, Company H and Company I. Rejection, not an exit: E is asked again on 01/04 (#65).</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -4587,19 +4591,15 @@
           <t>“the Company Special Committee determined to let Company E’s offer expire and to continue to engage with CLP, Company H and Company I” (p. 36)</t>
         </is>
       </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+      <c r="R63" s="2" t="n"/>
       <c r="S63" s="2" t="n"/>
-      <c r="T63" s="4" t="n">
+      <c r="T63" s="3" t="n">
         <v>44195</v>
       </c>
-      <c r="U63" s="4" t="n">
+      <c r="U63" s="3" t="n">
         <v>44195</v>
       </c>
-      <c r="V63" s="4" t="n">
+      <c r="V63" s="3" t="n">
         <v>44195</v>
       </c>
     </row>
@@ -4609,76 +4609,58 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>12/30/2020</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="n"/>
       <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: kick-off diligence call only after the 01/07 LOI. Not contingent on third-party debt; CLP would fund it all by equity commitment if needed. Non-binding LOI: two-step tender offer and merger for 100% at $1.88 per share cash.</t>
+          <t>Committee selects CLP, Company H and Company I (I for the portal business only) and has Canaccord and management seek non-binding LOIs; no due date. H enters by this admission. E stays outside, still being received.</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>“with a purchase price of $1.88 per Share in cash” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="n"/>
+          <t>“directing Canaccord Genuity and the Company’s management to continue to seek non-binding letters of intent from such parties” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q9</t>
+        </is>
+      </c>
       <c r="S64" s="2" t="n"/>
-      <c r="T64" s="4" t="n">
-        <v>44200</v>
-      </c>
-      <c r="U64" s="4" t="n">
-        <v>44200</v>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>44200</v>
+      <c r="T64" s="3" t="n">
+        <v>44195</v>
+      </c>
+      <c r="U64" s="3" t="n">
+        <v>44195</v>
+      </c>
+      <c r="V64" s="3" t="n">
+        <v>44195</v>
       </c>
     </row>
     <row r="65">
@@ -4687,71 +4669,75 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>by 01/04/2021</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Company I</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="3" t="n"/>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Inferred: at the 01/04 committee meeting Canaccord said only E and H remained as other interested parties, leaving out I (still engaged on 12/30). Who ended it not stated (Q8).</t>
+          <t>Not contingent on third-party debt and CLP would fund it all with equity if needed, but diligence still open (stepped up into January). Non-binding LOI: tender offer then merger for 100% at $1.88 cash; answers #63.</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>“only Company E (with respect to its proposed partial tender offer proposal) and Company H remained as other parties interested in engaging on a transaction” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
+          <t>“with a purchase price of $1.88 per Share in cash” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="n"/>
       <c r="S65" s="2" t="n"/>
-      <c r="T65" s="4" t="n">
+      <c r="T65" s="3" t="n">
         <v>44200</v>
       </c>
-      <c r="U65" s="4" t="n">
-        <v>44195</v>
-      </c>
-      <c r="V65" s="4" t="n">
+      <c r="U65" s="3" t="n">
+        <v>44200</v>
+      </c>
+      <c r="V65" s="3" t="n">
         <v>44200</v>
       </c>
     </row>
@@ -4766,58 +4752,48 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
       <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Asked by Canaccord (committee told it to maximize E’s offer) to return to a 100% acquisition, E declined; its partial-tender proposal lapsed after 01/04 (#61).</t>
+          <t>Price requests: the Committee has Canaccord seek higher offers from CLP and Company E and a written offer from Company H; Canaccord reports only E (partial offer) and H remain besides CLP. On 01/05 the Company told CLP price was still open.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>“Company E declined to do so and indicated that its tender offer proposal would no longer be available following January 4, 2021.” (p. 36)</t>
+          <t>“directed Canaccord Genuity to engage in outreach to seek to maximize offers from each of CLP and Company E and to receive a written offer from Company H” (p. 36)</t>
         </is>
       </c>
       <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
-      <c r="T66" s="4" t="n">
+      <c r="T66" s="3" t="n">
         <v>44200</v>
       </c>
-      <c r="U66" s="4" t="n">
+      <c r="U66" s="3" t="n">
         <v>44200</v>
       </c>
-      <c r="V66" s="4" t="n">
+      <c r="V66" s="3" t="n">
         <v>44200</v>
       </c>
     </row>
@@ -4827,54 +4803,64 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2021</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n"/>
+          <t>Company E</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
       <c r="J67" s="2" t="n"/>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="n"/>
-      <c r="N67" s="2" t="n"/>
+      <c r="M67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Value below earlier offer</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="n"/>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Target pressed for a higher price: Canaccord told CLP the committee wanted more, and the Company sent CLP a revised LOI leaving price open and requiring customary public-company terms.</t>
+          <t>Asked to re-engage on 100% of the Company, E declined and its partial tender offer lapsed after 01/04/2021. Having dropped its $2.00 whole-company price (#57), E values 100% below $2.00.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>“the Company sent a revised letter of intent to CLP, noting that the price per Share to be paid in the transaction was still an open issue” (p. 36)</t>
+          <t>“Company E declined to do so and indicated that its tender offer proposal would no longer be available following January 4, 2021” (p. 36)</t>
         </is>
       </c>
       <c r="R67" s="2" t="n"/>
       <c r="S67" s="2" t="n"/>
-      <c r="T67" s="4" t="n">
-        <v>44201</v>
-      </c>
-      <c r="U67" s="4" t="n">
-        <v>44201</v>
-      </c>
-      <c r="V67" s="4" t="n">
-        <v>44201</v>
+      <c r="T67" s="3" t="n">
+        <v>44200</v>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>44200</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="68">
@@ -4888,7 +4874,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4905,12 +4891,12 @@
         <v>3</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H68" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I68" s="3" t="n">
+      <c r="I68" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4935,7 +4921,7 @@
       <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Requested 30-day exclusivity, with diligence and definitive negotiation still to begin. Raises #63 to $2.00 per share; terms otherwise from the 01/04 LOI (cash). Reported by Canaccord at the 01/06 meeting.</t>
+          <t>Heavy: CLP asks for a 30-day exclusivity period. Raises #64 to $2.00 cash after the 01/05 request for a higher price; reported at the 01/06 Committee meeting. Equity-funded per #64.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -4943,19 +4929,15 @@
           <t>“Canaccord Genuity reported that CLP agreed to increase its offer to $2.00 per Share and had also requested a 30-day period of exclusivity” (p. 36)</t>
         </is>
       </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+      <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
-      <c r="T68" s="4" t="n">
+      <c r="T68" s="3" t="n">
         <v>44201</v>
       </c>
-      <c r="U68" s="4" t="n">
+      <c r="U68" s="3" t="n">
         <v>44201</v>
       </c>
-      <c r="V68" s="4" t="n">
+      <c r="V68" s="3" t="n">
         <v>44202</v>
       </c>
     </row>
@@ -4970,66 +4952,54 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
       <c r="J69" s="2" t="n"/>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>Inferred: on 01/06 the committee chose to sign an LOI and negotiate a definitive agreement with CLP alone. H still gave no sign if or when it would submit an LOI, and is not mentioned again (Q8).</t>
+          <t>Requested: CLP asks for 30 days of exclusivity. Execution is not reported; the LOI signed 01/07 (#72) is not said to include it.</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>“Company H continued to provide no indication if or when it would be willing to submit a formal letter of intent” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
+          <t>“had also requested a 30-day period of exclusivity” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="n"/>
       <c r="S69" s="2" t="n"/>
-      <c r="T69" s="4" t="n">
-        <v>44202</v>
-      </c>
-      <c r="U69" s="4" t="n">
-        <v>44200</v>
-      </c>
-      <c r="V69" s="4" t="n">
+      <c r="T69" s="3" t="n">
+        <v>44201</v>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>44201</v>
+      </c>
+      <c r="V69" s="3" t="n">
         <v>44202</v>
       </c>
     </row>
@@ -5039,12 +5009,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/06/2021</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D70" s="2" t="n"/>
@@ -5057,10 +5027,10 @@
         <v>3</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="3" t="n"/>
-      <c r="I70" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
@@ -5069,12 +5039,12 @@
       <c r="O70" s="2" t="n"/>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Round 5 opens: after the committee’s 01/06 decision, the Company and CLP signed the non-binding $2.00 LOI and began diligence and definitive-agreement negotiation. Whether CLP’s 30-day exclusivity was granted is not stated.</t>
+          <t>Committee unanimously decides to sign a non-binding LOI with CLP and begin diligence and definitive-agreement negotiation: definitive negotiation with the selected bidder after a non-final round. CLP (1 financial bidder) admitted.</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>“On January 7, 2021, the Company and CLP executed the non-binding letter of intent.” (p. 36)</t>
+          <t>“it unanimously determined to enter into the non-binding letter of intent with CLP and commence diligence and negotiation of a definitive agreement” (p. 36)</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -5083,14 +5053,14 @@
         </is>
       </c>
       <c r="S70" s="2" t="n"/>
-      <c r="T70" s="4" t="n">
-        <v>44203</v>
-      </c>
-      <c r="U70" s="4" t="n">
-        <v>44203</v>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>44203</v>
+      <c r="T70" s="3" t="n">
+        <v>44202</v>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>44202</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>44202</v>
       </c>
     </row>
     <row r="71">
@@ -5099,42 +5069,56 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>01/21/2021</t>
+          <t>by 01/06/2021</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Thompson Hine LLP</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="n"/>
+          <t>Company H</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H71" s="3" t="n"/>
-      <c r="I71" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
       <c r="J71" s="2" t="n"/>
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
-      <c r="M71" s="2" t="n"/>
-      <c r="N71" s="2" t="n"/>
-      <c r="O71" s="2" t="n"/>
+      <c r="M71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>CLP’s outside legal counsel; first seen acting when it sent the buyer’s first draft of the Merger Agreement to Gunderson. That draft is not a bid.</t>
+          <t>Inferred: the complete advancing set on 01/06 is CLP alone. Company H had given 'no indication if or when' it would submit a formal LOI. H entered by admission on 12/30 (#63).</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>“outside counsel to CLP, Thompson Hine LLP (“Thompson”), delivered an initial draft of the Merger Agreement to Gunderson” (p. 37)</t>
+          <t>“Company H continued to provide no indication if or when it would be willing to submit a formal letter of intent” (p. 36)</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr">
@@ -5143,14 +5127,12 @@
         </is>
       </c>
       <c r="S71" s="2" t="n"/>
-      <c r="T71" s="4" t="n">
-        <v>44217</v>
-      </c>
-      <c r="U71" s="4" t="n">
-        <v>44217</v>
-      </c>
-      <c r="V71" s="4" t="n">
-        <v>44217</v>
+      <c r="T71" s="3" t="n">
+        <v>44202</v>
+      </c>
+      <c r="U71" s="2" t="n"/>
+      <c r="V71" s="3" t="n">
+        <v>44202</v>
       </c>
     </row>
     <row r="72">
@@ -5159,80 +5141,70 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>late January 2021 (after 01/27/2021)</t>
+          <t>by 01/06/2021</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
+          <t>Company I</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N72" s="2" t="n"/>
-      <c r="O72" s="2" t="n"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: diligence continued into February. Reaffirmed by returned draft: after Gunderson’s 01/27 revision, CLP and Thompson swapped drafts with the Company for the rest of January. Price carried from #67. First CLP draft return undated (Q9).</t>
+          <t>Inferred: only CLP advanced on 01/06. Company I (portal only) was last reported interested on 12/30; on 01/04 Canaccord named only E and H as other interested parties, so I may have lapsed earlier or been outside that count.</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>“Throughout the remainder of January and into February, the Company, CLP, Gunderson and Thompson continued to negotiate the terms of the Merger Agreement and exchange drafts thereof.” (p. 37)</t>
+          <t>“only Company E (with respect to its proposed partial tender offer proposal) and Company H remained as other parties interested in engaging on a transaction” (p. 36)</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q3; Q9</t>
         </is>
       </c>
       <c r="S72" s="2" t="n"/>
-      <c r="T72" s="4" t="n">
-        <v>44225</v>
-      </c>
-      <c r="U72" s="4" t="n">
-        <v>44224</v>
-      </c>
-      <c r="V72" s="4" t="n">
-        <v>44227</v>
+      <c r="T72" s="3" t="n">
+        <v>44202</v>
+      </c>
+      <c r="U72" s="2" t="n"/>
+      <c r="V72" s="3" t="n">
+        <v>44202</v>
       </c>
     </row>
     <row r="73">
@@ -5241,15 +5213,19 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/08/2021</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n"/>
+          <t>CLP (Centre Lane Partners, LLC)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -5259,36 +5235,38 @@
         <v>3</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
       <c r="J73" s="2" t="n"/>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
-      <c r="M73" s="2" t="n"/>
+      <c r="M73" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N73" s="2" t="n"/>
       <c r="O73" s="2" t="n"/>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>Target price requirement: after Canaccord’s premium analysis (stock up from $1.49 on 01/07), board said it needed $2.20 per share to consider approval. Canaccord relayed it; CLP took it to its investment committee.</t>
+          <t>The Company and CLP execute the non-binding LOI for 100% at $2.00 per share (confirmed 01/08 to Rendino); exclusivity terms not stated. A kick-off diligence call and weeks of diligence followed; Rendino stayed recused.</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>“instructed Canaccord Genuity to relay the need for an increase in purchase price to $2.20 per Share to consider approving the proposed Transaction” (p. 37)</t>
+          <t>“On January 7, 2021, the Company and CLP executed the non-binding letter of intent” (p. 36)</t>
         </is>
       </c>
       <c r="R73" s="2" t="n"/>
       <c r="S73" s="2" t="n"/>
-      <c r="T73" s="4" t="n">
-        <v>44235</v>
-      </c>
-      <c r="U73" s="4" t="n">
-        <v>44235</v>
-      </c>
-      <c r="V73" s="4" t="n">
-        <v>44235</v>
+      <c r="T73" s="3" t="n">
+        <v>44203</v>
+      </c>
+      <c r="U73" s="3" t="n">
+        <v>44203</v>
+      </c>
+      <c r="V73" s="3" t="n">
+        <v>44203</v>
       </c>
     </row>
     <row r="74">
@@ -5297,80 +5275,54 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>02/10/2021</t>
+          <t>01/21/2021</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Thompson Hine LLP</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="n"/>
       <c r="N74" s="2" t="n"/>
       <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Conditioned on signing the Merger Agreement that day and announcing before the 02/11 open; termination fee raised $3.0m→$3.5m; support agreements required; equity commitment from CLP Fund V. Raises #71 to $2.20 cash. Ref: $1.95 close 02/10/2021 (p. 4).</t>
+          <t>CLP's outside counsel; delivered CLP's initial draft Merger Agreement to Gunderson.</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>“CLP indicated that it would increase the purchase price per Share from $2.00 per Share to $2.20 per Share” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R74" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+          <t>“On January 21, 2021, outside counsel to CLP, Thompson Hine LLP” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
-      <c r="T74" s="4" t="n">
-        <v>44237</v>
-      </c>
-      <c r="U74" s="4" t="n">
-        <v>44237</v>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>44237</v>
+      <c r="T74" s="3" t="n">
+        <v>44217</v>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>44217</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>44217</v>
       </c>
     </row>
     <row r="75">
@@ -5379,12 +5331,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>02/10/2021</t>
+          <t>01/21/2021</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Centre Lane Partners (CLP)</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5394,20 +5346,36 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Bid reaffirmed</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
-      <c r="J75" s="2" t="n"/>
-      <c r="K75" s="2" t="n"/>
-      <c r="L75" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M75" s="2" t="n">
         <v>1</v>
       </c>
@@ -5415,24 +5383,28 @@
       <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>$2.20 per share cash via two-step tender offer and §251(h) merger. Tender and Support Agreements with Pacven Walden funds and 180 Degree (about 17.4%, p. 61) and CLP Fund V equity commitment signed. $3.5m target termination fee; no reverse fee. Canaccord gave fairness opinion.</t>
+          <t>Diligence still ongoing, no stated condition. CLP's counsel delivers CLP's own initial draft Merger Agreement, supporting its standing $2.00 cash price (carried from #67) after the target moved to finalize with it (Q10).</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>“Later that day, the parties executed the Merger Agreement and the Tender and Support Agreements, and CLP Fund V, Parent and Purchaser executed the Equity Commitment Letter.” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R75" s="2" t="n"/>
+          <t>“delivered an initial draft of the Merger Agreement to Gunderson” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
       <c r="S75" s="2" t="n"/>
-      <c r="T75" s="4" t="n">
-        <v>44237</v>
-      </c>
-      <c r="U75" s="4" t="n">
-        <v>44237</v>
-      </c>
-      <c r="V75" s="4" t="n">
-        <v>44237</v>
+      <c r="T75" s="3" t="n">
+        <v>44217</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>44217</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>44217</v>
       </c>
     </row>
     <row r="76">
@@ -5441,30 +5413,28 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>02/11/2021</t>
+          <t>02/08/2021</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Synacor</t>
+          <t>Synacor (target)</t>
         </is>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
+      <c r="G76" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
       <c r="J76" s="2" t="n"/>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
@@ -5473,28 +5443,226 @@
       <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Press release and Form 8-K before trading opened. No go-shop; no later competing proposals reported through the 03/03/2021 filing.</t>
+          <t>Price requirement: after the share price rose (Ref: $1.49 close 01/07/2021) and Canaccord's premium advice, the Board requires $2.20 per share to consider approval; Canaccord relays it and CLP will consult its investment committee.</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>“Before the opening of trading on the public markets on February 11, 2021, the Company issued a press release announcing entry into the Merger Agreement” (p. 38)</t>
+          <t>“instructed Canaccord Genuity to relay the need for an increase in purchase price to $2.20 per Share to consider approving the proposed Transaction” (p. 37)</t>
         </is>
       </c>
       <c r="R76" s="2" t="n"/>
       <c r="S76" s="2" t="n"/>
-      <c r="T76" s="4" t="n">
+      <c r="T76" s="3" t="n">
+        <v>44235</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>44235</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>44235</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>02/10/2021</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>CLP (Centre Lane Partners, LLC)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="2" t="n"/>
+      <c r="O77" s="2" t="n"/>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Ready to sign: raise conditioned on signing that day and announcing before the 02/11 open; CLP Fund V equity commitment, no financing condition. $2.20 cash; termination fee up from $3.0m to $3.5m; no reverse fee; support agreements required.</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>“CLP indicated that it would increase the purchase price per Share from $2.00 per Share to $2.20 per Share” (p. 38)</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="n"/>
+      <c r="S77" s="2" t="n"/>
+      <c r="T77" s="3" t="n">
+        <v>44237</v>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>44237</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>44237</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/10/2021</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>CLP (Centre Lane Partners, LLC)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Merger agreement signed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>Agreed $2.20 per share in cash: tender offer then DGCL 251(h) merger; $3.5m termination fee; CLP Fund V equity commitment; Tender and Support Agreements with Pacven Walden funds and 180 Degree (about 17.4% of shares). Canaccord fairness opinion.</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>“Later that day, the parties executed the Merger Agreement and the Tender and Support Agreements” (p. 38)</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="n"/>
+      <c r="S78" s="2" t="n"/>
+      <c r="T78" s="3" t="n">
+        <v>44237</v>
+      </c>
+      <c r="U78" s="3" t="n">
+        <v>44237</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>44237</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/11/2021</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Synacor (target)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="2" t="n"/>
+      <c r="M79" s="2" t="n"/>
+      <c r="N79" s="2" t="n"/>
+      <c r="O79" s="2" t="n"/>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>Press release before market open and Form 8-K. Ref: $1.95 close 02/10/2021, last trading day before announcement (p. 4). No go-shop; no-solicitation covenant from signing.</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>“Before the opening of trading on the public markets on February 11, 2021, the Company issued a press release announcing entry into the Merger Agreement” (p. 38)</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="n"/>
+      <c r="S79" s="2" t="n"/>
+      <c r="T79" s="3" t="n">
         <v>44238</v>
       </c>
-      <c r="U76" s="4" t="n">
+      <c r="U79" s="3" t="n">
         <v>44238</v>
       </c>
-      <c r="V76" s="4" t="n">
+      <c r="V79" s="3" t="n">
         <v>44238</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V76"/>
+  <autoFilter ref="A1:V79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5505,19 +5673,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5579,17 +5747,17 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="3" t="n">
         <v>43228</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Liontree began outreach to about 12 strategic and financial parties after its 05/08/2018 engagement</t>
+          <t>Liontree engaged 05/08/2018; outreach to approximately 12 strategic and financial companies (undated start) (#6)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1 financial: Company A (round-0 IOIs still standing). Outreach contacts did not enter.</t>
+          <t>1 financial: Company A (carried from round 0, NDA 01/10/2018). About 12 contacted parties, none reported to enter.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -5609,12 +5777,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>0 in the round (A’s IOIs of 02/06 and 04/25/2018 were round 0)</t>
+          <t>0 in the round (Company A's two IOIs, #3-#4, preceded the outreach and are round 0)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>A withdrew 06/20/2018; the outreach produced no IOIs; the attempt lapsed</t>
+          <t>Company A withdrew 06/20/2018 (#8); outreach produced no IOI; attempt lapsed (Liontree engagement's stated end 12/31/2018).</t>
         </is>
       </c>
     </row>
@@ -5625,17 +5793,17 @@
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>43661</v>
+      <c r="C3" s="3" t="n">
+        <v>43702</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Management outreach to about 5 companies on selling the portal and advertising business (Q3 2019); Canaccord added whole-company outreach to 18 from 08/25/2019</t>
+          <t>Canaccord engaged 08/25/2019; outreach to 18 additional parties at the Board's direction (undated start) (#15)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>3: Company C (strategic; round-0 LOI of 08/13/2019), Company E (financial; portal-only NDA), Company F (strategic; portal; May 2018 NDA reused)</t>
+          <t>1 strategic: Company C (carried from round 0, NDA March 2019). 18 contacted parties, none entered. Segment buyers in management's portal divestiture, not admitted: Company E (NDA), Company F (IOI, round 0).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -5655,12 +5823,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>1: Company F (portal, other-scope) 09/15/2019</t>
+          <t>0 whole-company bids in the round (Company C's LOI #12 preceded it; Company F's portal IOI #17 answered management's divestiture outreach)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>F failed to agree on terms; C dropped by mutual agreement Oct 2019; the 18 contacts gave no IOIs; lapsed. E never closed here, so it is closed at the P3 restart</t>
+          <t>Company C and the Company mutually dropped talks October 2019 (#19); Company F talks failed, undated (#18); lapsed; Company E's NDA closed by process 3 restart (#20).</t>
         </is>
       </c>
     </row>
@@ -5671,17 +5839,17 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>44028</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Canaccord outreach to 37 parties (plus management outreach to 8 on the portal business); NDA signers asked for IOIs by 09/17</t>
+          <t>Canaccord outreach to 37 parties from mid-July 2020, with IOIs requested by 09/17/2020 (#25); management separately contacted 8 portal buyers</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17 units: 3 financial (Company E, CLP, Company G [software segment]); 1 strategic (Company H, invited 09/22); 13 other NDA signers of unknown type</t>
+          <t>15-17 bidder units entered: Company E (financial, NDA amendment 07/13/2020); CLP (financial, NDA 09/08/2020); 13-14 other outreach NDA signers (type unknown; CLP may be one of the 14); Company G (financial) by its segment bid, possibly also an NDA signer. Company H contacted, not entered.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -5701,12 +5869,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3: Company E ($2.00 on 09/10, reaffirmed 09/18), Company G (software segment, 09/14), CLP ($1.35–$1.41 on 09/17)</t>
+          <t>3 bidders: Company E ($2.00, #30; revised #40), CLP ($1.35-$1.41, #37; verbal #44), Company G (software and services only, #33)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Exclusive LOI with E on 09/23; CLP, G and H dropped; 13 NDA signers did not submit</t>
+          <t>Company E selected for exclusive negotiation 09/23/2020; CLP and Company G dropped 09/23 (#48-#49); 12-14 NDA signers did not submit (#39).</t>
         </is>
       </c>
     </row>
@@ -5717,17 +5885,17 @@
       <c r="B5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Exclusive LOI signed with E; diligence and definitive-agreement negotiation</t>
+          <t>Company E's LOI with exclusivity to 10/23/2020 executed; definitive negotiation with E (#47)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1 financial: Company E</t>
+          <t>1 financial: Company E. Still being received, not admitted: Company I (portal only; NDA 11/19/2020, LOIs #55, #60); CLP (re-entered 12/18-12/21/2020, #59). Company H contacted, not entered.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5747,12 +5915,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2 bidders: Company E (35% partial tender at $2.00, #56, revised #61; dropped whole-company $2.00, #57); Company I (portal only, #55, #60)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity expired 10/23/2020 with no agreement; target reopened outreach 10/27 while E talks went on without exclusivity</t>
+          <t>Exclusivity lapsed 10/23/2020; outreach reopened 10/27; E dropped its whole-company offer 12/14; on 12/30 the Committee let E's partial offer lapse and turned to CLP, H and I (#62).</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5931,17 @@
       <c r="B6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>44131</v>
+      <c r="C6" s="3" t="n">
+        <v>44195</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Special Committee had Canaccord restart outreach to parties that had shown interest, as E talks slowed</t>
+          <t>Special Committee selects CLP, Company H and Company I and seeks non-binding LOIs (#63)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Company E (financial; continuing); Company H (strategic; re-entered 10/27, withdrew 11/02, re-entered Dec 18–21); Company I (strategic, portal only; NDA 11/19); CLP (financial; re-entered Dec 18–21)</t>
+          <t>3 admitted: CLP (financial), Company H (strategic), Company I (strategic, portal only). Still being received, not admitted: Company E (asked 01/04/2021 to re-engage on 100%).</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5793,12 +5961,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2: Company I (portal; 12/08 and 12/29), Company E (35% tender; 12/14 and 12/29)</t>
+          <t>1 bidder: CLP ($1.88 on 01/04/2021, #64; $2.00 by 01/06/2021, #67). Company E declined (#66); H and I did not bid.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>On 12/30 the committee let E’s partial offer lapse and asked CLP, H and I for LOIs</t>
+          <t>CLP selected 01/06/2021 for LOI and definitive negotiation; Company E withdrew 01/04 (#66); Company H and Company I dropped, inferred, by 01/06 (#70-#71).</t>
         </is>
       </c>
     </row>
@@ -5809,17 +5977,17 @@
       <c r="B7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>44195</v>
+      <c r="C7" s="3" t="n">
+        <v>44202</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Committee let E’s offer lapse and sought non-binding LOIs from CLP, H and I</t>
+          <t>Committee decides to sign an LOI with CLP and begin diligence and definitive negotiation (#69); LOI executed 01/07/2021</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3 admitted: CLP (financial), Company H (strategic), Company I (strategic, portal only). Company E (financial): still being received, not admitted (asked 01/04 to return to a 100% offer)</t>
+          <t>1 financial: CLP.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -5834,68 +6002,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Not final</t>
+          <t>Inferred final</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1: CLP ($1.88 on 01/04; $2.00 by 01/06)</t>
+          <t>1 bidder: CLP ($2.00 reaffirmed with its draft Merger Agreement 01/21/2021, #74; $2.20 on 02/10/2021, #76)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>E withdrew 01/04; I out by 01/04; committee chose CLP 01/06 (H dropped); LOI signed 01/07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>44203</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Non-binding $2.00 LOI signed with CLP; diligence and definitive-agreement negotiation</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1 financial: CLP</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>none stated</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>No deadline stated</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Inferred final</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1: CLP (reaffirmed $2.00 by returned draft in late January; $2.20 on 02/10)</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>signing 02/10/2021</t>
+          <t>Signing 02/10/2021 at $2.20 per share in cash (#77); announced 02/11/2021.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5906,16 +6028,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5963,27 +6085,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Is the map of three processes and 1/1/5 rounds right?</t>
+          <t>Is the map right: three processes (2018, 2019, 2020-21), one round in each of processes 1-2, and four rounds in process 3?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. P1: 2018 Company A attempt, with Liontree’s outreach as round 1. P2: 2019 Company C / portal-divestiture attempt, with outreach as round 1. P3 (Jul 2020–Feb 2021) has five rounds: IOIs; exclusive E negotiation; renewed outreach; LOIs sought from CLP/H/I; definitive negotiation with CLP.</t>
+          <t>Yes. P3: R1 IOI outreach due 09/17/2020; R2 exclusive negotiation with Company E from 09/23; R3 LOI requests to CLP, H and I from 12/30; R4 definitive negotiation with CLP from 01/06/2021.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Gaps with no contact of about two months or more: 02/06/2018–04/25/2018 (A; undated “discussion” in between) (p. 30); 06/20/2018 (sure; Liontree contacts undated, maybe later) to March 2019 (month only), about 8.5 months (pp. 30–31); October 2019 (month only; F’s end and the 18 contacts undated, engagement to 01/15/2020) to 07/13/2020, about 9 months (pp. 31–32). C7 tests for P2: (a) met, as A withdrew and no one was carried forward; (b) met, but uncertain because of the undated Liontree contacts; (c) met with the C NDA and later the Canaccord mandate. For P3: (a) met, as C and F had ended and E was not kept in view; (b) met, at least about 6 months even if contacts ran to 01/15/2020; (c) met through E’s approach and the new outreach.</t>
+          <t>E5 tests (pp. 30-32). P1 to P2: (a) met, no offer open after Company A withdrew 06/20/2018 (Liontree outreach undated); (b) met; (c) met, Company C NDA March 2019. P2 to P3: (a) met, but Company F's end undated; (b) met, about 8.5-9.5 months with no reported sale contact (October 2019 to 07/13/2020); (c) met, E approach taken up. Gaps of two months or more with no dated acquirer contact: 02/06/2018-04/25/2018 (undated discussions between); 06/20/2018-October 2018 (Company B) or March 2019 (Company C); March 2019-07/30/2019; October 2019-07/13/2020.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#6, #9, #11, #21, #26, #37, #46, #52, #62, #69</t>
+          <t>#6, #9, #15, #20, #25, #47, #51, #63, #69</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Merging P1 and P2 (if Liontree’s contacts or the Company B talks bridged 2018) would drop #9 and renumber #10–#20 as process 1. Splitting P3 round 1 at 09/17 (best-offer requests) would move #37–#50 into a new round 2. Folding round 3 into round 2 (E talks continued) would remove #52.</t>
+          <t>Most plausible alternative: round 3 opens 10/27/2020, when outreach is re-initiated (#51), moving #52-#62 (H contacts, Company I's NDA and LOIs, E's partial offers, CLP's re-entry) from round 2 to round 3. Merging processes has no supported basis given the gaps.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -5996,27 +6118,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Should the Company B and Company D combinations be excluded as not sales of Synacor?</t>
+          <t>Should the Company B 'merger of equals' (Oct 2018-Mar 2019) and the Company D deal (IOI 07/01/2019; merger agreement 02/11/2020; terminated 06/29/2020) be treated as sale processes?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes. Both are recorded only in Deal facts.</t>
+          <t>No. Synacor was the proposer in both: it delivered the MOE letter to Company B and proposed to acquire Company D. E1 excludes a target's attempt to buy another company. Both are recorded only in Deal facts.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>B was a “merger of equals” that Synacor itself proposed (Oct 2018–Mar 2019). D began as Synacor’s own bid to buy D (07/01/2019). The Jan 2020 LOI and the 02/11/2020 merger agreement were all-stock with an ownership split, and the filing never says which side was acquired. The agreement was ended by mutual termination on 06/29/2020 (pp. 30–31). C1 excludes a target’s attempt to buy another company.</t>
+          <t>pp. 30-31: 'the Company delivered a non-binding indication of interest letter to Company B proposing a “merger of equals”'; 'the Company submitted a non-binding indication of interest to acquire a publicly-traded software company (“Company D”)'. The D terms were all stock with a 'combined company ownership split'.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#9, #21</t>
+          <t>#9, #20</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Counting B would bridge the 2018–19 gap and support merging P1 and P2 (Q1). Counting D would add a signed-and-terminated deal (Jan–Jun 2020) as its own process, and C’s LOI would stay in P2. The P3 boundary holds either way, because D’s termination is reported.</t>
+          <t>If Company B counts as a sale contact, the P1-P2 gap shrinks to about 3.3-4.4 months (still a break). If the D deal counts as a sale of Synacor, a signed-and-terminated process (Jan-Jun 2020) is added between P2 and P3, and the P3 restart follows its reported end.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -6029,27 +6151,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>How should the partial-company bids and non-per-share values be treated?</t>
+          <t>How should the segment-only bidders (portal: Company E 2019, F, I; software and services: G) and management's portal divestiture outreach be placed?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Record them as Other-scope bids. Whole-company bids do exist: A, C, E and CLP. E’s 35% tender keeps $2.00 in the price cells as the price per share tendered.</t>
+          <t>Keep them as participants with Other-scope bid rows, entries and exits, so live-unit counts include them while whole-company prices exclude them. Put the 2019 portal outreach, E's 2019 NDA and F's IOI in process 2, round 0: they answered a divestiture effort, not Canaccord's whole-company round.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>F’s IOI scope is not restated; it is inferred from F’s interest in the portal business (p. 31). G bid for the software segment and was valued only as a “fraction” of E’s value on an enterprise-value basis (pp. 32–33). I bid for the portal business (pp. 34–35). E’s 12/14 and 12/29 offers were tender offers for 35% at $2.00 per share (pp. 34–35). All prices are in US dollars.</t>
+          <t>pp. 31-36: the Board was 'evaluating divesting its portal and advertising business'; G's and I's bids gave no per-share price, only fractions of rival valuations; segment and whole-company bids therefore sit on mixed bases.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#18, #35, #57, #61</t>
+          <t>#11, #13, #17, #18, #27, #33, #49, #54, #55, #60, #71</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Leaving E’s partial-tender price cells blank would stop anyone reading $2.00 as a whole-company value. Treating F’s IOI as whole-company would make it a Bid.</t>
+          <t>Excluding segment buyers would remove E (2019), F, G and I, leaving process 2 with Company C alone and round 3 of process 3 with CLP and H. Placing F's IOI in process 2, round 1 would give that round one bid.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -6062,27 +6184,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Who is inside the 37 contacts and 14 NDA signers?</t>
+          <t>Which exit labels fit Company C (talks 'mutually agreed' to end, October 2019) and Company F ('unable to agree on terms', undated)?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CLP, G and H are inside the 37. CLP is one of the 14. E is outside both, since its approach and NDA amendment came before the outreach. G and H are not shown to have signed NDAs, so they enter on their own rows. That leaves a residual of 13 NDA signers, and all of them did not submit.</t>
+          <t>Withdrew for both, with Exit reason Not stated (C) and Terms or process (F). The filing names neither side as ending talks, so no target-side exclusion is shown.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The filing says that, other than IOIs “described below”, none of the 37 produced an IOI, which ties CLP and G to the outreach. H’s interest arose from the outreach. The 37 exclude only Companies A–D, so E could technically be a member (p. 32).</t>
+          <t>p. 31: 'the Company and Company C mutually agreed in October 2019 not to pursue a transaction'; 'the parties were ultimately unable to agree on terms for the transaction'.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#23, #27, #29, #35, #40, #44</t>
+          <t>#18, #19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If E is one of the 14, the residual becomes 12. If G or H signed one of the 13 NDAs, their entries duplicate cohort members, round-1 live units fall from 17, and #40 shrinks. The auction screen is Met either way.</t>
+          <t>Dropped by target would attribute the decision to Synacor. Neither label reveals a price; only whose decision ended participation changes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -6095,27 +6217,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>What was the outcome of the only due date, the 09/17/2020 IOI deadline (P3 round 1)?</t>
+          <t>How do the 14 outreach NDA signers relate to CLP, Company G and Company H, and how many failed to submit by 09/17/2020?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Enforced.</t>
+          <t>Treat CLP as possibly one of the 14 (cohort 13-14 besides CLP) and non-submitters as 12-14 (G may be a member). Leave Counts blank with bounds in the Notes. The auction screen is Met either way.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>There was no extension and no late bid was reported. The target acted on the bids it held: a best-offer request to E (09/17), requests to CLP and G to raise their prices (09/21), and exclusivity with E (09/23) (pp. 32–34). The other rounds had no due dates.</t>
+          <t>p. 32: 'Of the parties contacted, 14 parties executed non-disclosure agreements'. The filing never places CLP or G in the outreach, and says H was reached in it but reports no NDA for H.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#30, #39, #40</t>
+          <t>#28, #29, #39</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Passed without action is arguable: Bhise invited H to bid after the due date (09/22), and bidding kept going until exclusivity. That would signal the deadline was not binding.</t>
+          <t>If CLP and G are both members, process-3 NDA entrants are 15 (14 plus Company E) and non-submitters 12. If neither is, entrants are 16 plus G, with 14 non-submitters. Round 1's live count shifts accordingly.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -6128,27 +6250,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Was the 09/17 request for E’s “best offer on purchase price” a best-and-final solicitation?</t>
+          <t>Was the Company's 09/17/2020 request that Company E give its 'best offer on purchase price' a best-and-final solicitation that opens a new round and makes E's 09/18 reply Formal?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>No. E’s 09/18 reaffirmation stays Informal and the round is not final.</t>
+          <t>No. It was a request to one bidder to improve its price inside a counter-LOI. That is bargaining within round 1 (E6), so E's 09/18 $2.00 reply stays Informal.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The request came in a revised non-binding LOI. No markup or binding submission was sought, and diligence had not started; E asked for exclusivity in order to do diligence (p. 33).</t>
+          <t>p. 33: 'the Company submitted a revised letter of intent to Company E, which included a request for Company E to provide its best offer on purchase price'. No other bidder got a comparable request, and bargaining continued with CLP and G.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#37, #41</t>
+          <t>#36, #40</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>If it was best-and-final, it would open a round announced as final and #41 would be Formal with Heavy conditions. Rounds 2–5 would then be renumbered.</t>
+          <t>A new round would open 09/17 with Company E alone, E's 09/18 bid would become Formal (E11 item 2), and later process-3 round numbers would rise by one.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -6161,27 +6283,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Is CLP’s 09/22 verbal statement a Bid?</t>
+          <t>What was the outcome of the 09/17/2020 IOI due date in process 3, round 1?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>No. It is recorded as an Other material event (a price signal).</t>
+          <t>Enforced. The Company acted on the three bids in hand: it asked Company E for its best price (09/17), asked CLP and G to raise (09/21-22) and gave E exclusivity on 09/23.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CLP said it “would consider increasing” its price by 10–25%, subject to further diligence. That is a possible range, not an offer (p. 33).</t>
+          <t>pp. 33-34. On 09/22 Bhise still urged Company H, which had not bid, to submit a proposal. H submitted none.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#43</t>
+          <t>#38, #45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>As a Bid it would be Informal and Heavy with an implied range of $1.485–$1.7625 (10% on $1.35 up to 25% on $1.41), adding a round-1 bid from CLP.</t>
+          <t>Weighting the post-deadline invitation to H would make the outcome 'Passed without action'. No late bid arrived, so 'Late bids accepted' does not apply.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -6194,27 +6316,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Is the tracking of H’s and I’s participation right?</t>
+          <t>Is CLP's 09/22/2020 verbal statement that it 'would consider' raising its price by 10%-25%, subject to diligence, a Bid?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Yes. H entered on 09/22 when invited, was dropped 09/23, returned 10/27, withdrew “at that time” 11/02, returned in Dec, and was dropped by inference 01/06. I withdrew by inference by 01/04.</t>
+          <t>Yes: record it as an Informal Bid with Heavy conditions and blank price cells. It communicated a higher price range relative to #37, but the filing gives no per-share figure.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>On 01/04 Canaccord said only E and H remained as other interested parties (p. 36). On 01/06 the committee chose CLP while H gave no sign it would bid (p. 36).</t>
+          <t>p. 33: 'CLP provided a verbal indication that, subject to further diligence, it would consider increasing its purchase price by 10% to 25% per Share'. Arithmetic on $1.35-$1.41 implies about $1.49-$1.76 (not stated).</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#44, #53, #54, #59, #64, #68</t>
+          <t>#44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>If the 01/04 report meant whole-company interest only, I (a portal bidder) stays live until signing, where it would be Not selected at signing. If H stays live until signing, rounds 4–5 have up to 3 live units instead of 1.</t>
+          <t>As an Other material event (a valuation statement without an offer), CLP would have one round-1 bid ($1.35-$1.41). Filling the implied prices would add a range the filing never states.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -6227,33 +6349,66 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Is the late-reconfirmation row for CLP right?</t>
+          <t>Did Company H and Company I stay live after 12/30/2020, and how did they leave?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Yes. #71 is a Bid reaffirmed by returned draft, dated late January (after 01/27). It is Formal, with conditions Unclear.</t>
+          <t>H enters on 12/30 by admission: the Committee continued with CLP, H and I and sought their LOIs. Both H and I are inferred Dropped by target by 01/06/2021, when only CLP advanced.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The C12 tests hold. (a) The committee decided on 01/06 to negotiate a definitive agreement with CLP at $2.00, and the LOI was signed 01/07. (b) CLP’s last priced bid (#67) was Informal. (c) After Gunderson’s 01/27 draft, drafts were exchanged with CLP and Thompson (p. 37). Thompson’s 01/21 first draft was the buyer’s opening draft and does not count.</t>
+          <t>pp. 35-36. On 01/04/2021 Canaccord listed only E and H as other interested parties (I not named). On 01/06, H still gave 'no indication if or when' it would submit.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>#67, #70, #71, #73</t>
+          <t>#63, #70, #71</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Without this row, CLP’s first Formal bid is the $2.20 bid on 02/10 (#73). Dating it at 01/21 would conflict with C13.</t>
+          <t>If H is not treated as entered (no NDA or bid reported), it has no exit and round 3 admits two units. If I is taken to have left by 01/04, its exit moves earlier and could be Withdrew.</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Does CLP's delivery of its own initial draft Merger Agreement on 01/21/2021 reaffirm its $2.00 offer as Formal (Bid reaffirmed)?</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Yes. CLP's own full proposed agreement, delivered after the target moved to finalize with it, supports its standing $2.00 cash price (E10; E11 item 1). The filing does not state the price in the draft.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>p. 37: 'outside counsel to CLP, Thompson Hine LLP (“Thompson”), delivered an initial draft of the Merger Agreement to Gunderson'. CLP's latest priced row (#67) is Informal.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>#74</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Without #74, CLP's $2.00 stays Informal until the Formal $2.20 bid of 02/10/2021 (#76), and the winner has one formal bid instead of two.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6268,7 +6423,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6291,7 +6446,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Synacor, Inc.</t>
+          <t>Synacor, Inc. (Nasdaq: SYNC), Buffalo, New York; email/collaboration software, identity management, portals and advertising.</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6458,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CLP SY Holding, LLC (Parent), through SY Merger Sub Corporation. Controlled by Centre Lane Partners V, L.P. (CLP Fund V); the bidder in the background is its affiliate Centre Lane Partners, LLC (“CLP”).</t>
+          <t>CLP SY Holding, LLC (Parent) through SY Merger Sub Corporation; Parent's sole member is Centre Lane Partners V, L.P., affiliated with Centre Lane Partners, LLC (CLP).</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6470,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Financial. CLP Fund V is a private investment fund, and Centre Lane Partners, LLC manages private investment funds (p. 28). The deal is funded by an equity commitment from CLP Fund V (p. 29).</t>
+          <t>Financial (private equity fund)</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6482,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$2.20 per share in cash, through a tender offer followed by a DGCL §251(h) merger. About $94.2m needed in total (p. 29).</t>
+          <t>$2.20 per share in cash, by a tender offer followed by a DGCL 251(h) merger; equity commitment from CLP Fund V of up to $87,597,343 plus award payouts; no financing condition; $3.5 million termination fee, no reverse fee.</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6506,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>02/11/2021 (press release and Form 8-K before trading opened)</t>
+          <t>02/11/2021 (press release before market open; Form 8-K)</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6518,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Schedule TO-T, Offer to Purchase (Exhibit (a)(1)(A)), filed by Parent and Purchaser; dated 03/03/2021</t>
+          <t>Schedule TO-T (Offer to Purchase, Exhibit (a)(1)(A)) by SY Merger Sub Corporation, dated 03/03/2021</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6530,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>30–38 (Section 11, “Background of the Offer”)</t>
+          <t>30-38 (Section 11, Background of the Offer)</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6542,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>mixed. Process 3 began when Company E approached through director Rendino (bidder-led), and the target then ran a broad outreach that brought in the winner, CLP. Process 1 was bidder-led (Company A); process 2 was mixed.</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6566,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>No earlier approaches in the C7 sense beyond processes 1–2. Two combinations are excluded as not sales of Synacor (Q2). Company B: Synacor-proposed “merger of equals”; NDA Oct 2018, LOI signed Dec 2018, ended March 2019. Company D: Synacor proposed buying D on 07/01/2019; all-stock LOI 01/01/2020; merger agreement 02/11/2020; mutually terminated 06/29/2020. Company F’s May 2018 NDA came from a commercial relationship.</t>
+          <t>None reported beyond processes 1-3. Two Synacor-initiated combinations are not treated as sale processes (Q2): a proposed 'merger of equals' with Company B (NDA and letter October-December 2018, ended March 2019), and Synacor's proposed acquisition of Company D (IOI 07/01/2019; all-stock merger agreement 02/11/2020; terminated 06/29/2020).</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6578,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Not met (process 1): 1 party (Company A). Uncertain (process 2): 1 whole-company party (Company C); 3 if the portal-only bidders count (E’s 07/30/2019 NDA; F’s May 2018 commercial NDA, reuse implied). Met (process 3): 16 parties. The filing’s 14 counts parties (incl. CLP); add E (amended 2019 NDA) and I (portal only) = 16, or 15 if E is among the 14 (Q4). No post-signing additions, so the pre-signing subtotal is also 16.</t>
+          <t>Not met (process 1): 1 party (Company A); Uncertain (process 2): 1 whole-company acquirer (Company C), 2 counting Company E's NDA for the portal business only; Met (process 3): at least 14 parties (14 outreach NDA signers; up to 17 with Company E's amended NDA, CLP and Company I if outside the 14)</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6590,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Yes: Company A (2018), Company C (2019), Company E ($2.00, 2020) and CLP. Other-scope bids: F and I (portal and advertising business), G (software and services business), and E’s 35% partial tender offers.</t>
+          <t>Yes (also Other-scope bids: Company F and Company I for the portal and advertising business, Company G for the software and services business, and Company E's 35% partial tender offer)</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6602,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share. Exceptions: G was valued only as a fraction of E’s value on an enterprise-value basis; CLP’s 09/22 signal was a 10–25% increase; E’s partial offers were priced per share tendered for 35% (Q3).</t>
+          <t>US dollars per share. Company A's and Company C's prices were not disclosed (C: cash and stock). The segment bids (F, G, I) gave no per-share price, only valuations as fractions of rivals'. Company E's partial tender was $2.00 per share for 35% of shares (Q3).</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6614,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Liontree Advisors LLC (2018). Canaccord Genuity LLC (engaged 08/25/2019, re-engaged 01/02/2020, amended 07/30/2020 and 01/25/2021; primary adviser in process 3; gave the fairness opinion).</t>
+          <t>Liontree Advisors LLC (2018); Canaccord Genuity LLC (2019-2021; fairness opinion 02/10/2021)</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6626,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Gunderson Dettmer (outside corporate counsel). Buyer’s counsel: Thompson Hine LLP.</t>
+          <t>Gunderson Dettmer (outside corporate counsel). Acquirer's counsel: Thompson Hine LLP.</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6638,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Synacor made two earlier sale attempts: with private investment firm Company A in 2018, and with software company Company C plus a portal-business divestiture effort in 2019. Neither produced a deal. In July 2020, Company E’s approach through director Rendino led Canaccord to contact 37 parties; 14 signed NDAs, and E ($2.00), CLP ($1.35–$1.41) and segment bidder G submitted IOIs. The Special Committee gave E exclusivity on 09/23/2020, but E later switched to a 35% partial tender offer that the committee let lapse. Renewed outreach brought CLP back with LOIs at $1.88 and then $2.00, and an LOI was signed 01/07/2021. After the board demanded $2.20, CLP agreed on 02/10/2021, and the merger agreement was signed that day and announced on 02/11/2021.</t>
+          <t>After two attempts in 2018 and 2019 lapsed, a director relayed Company E's interest in July 2020, and Canaccord contacted 37 parties, 14 of which signed NDAs. By the 09/17/2020 IOI date Synacor had Company E at $2.00 cash, CLP at $1.35-$1.41 and a software-only bid from Company G. It granted Company E exclusivity, but E's diligence dragged, and in December E switched to a 35% partial tender at $2.00 with control demands. The Special Committee let E's offer lapse and turned to CLP, H and I; CLP bid $1.88 on 01/04/2021 and $2.00 two days later, and the parties signed a non-binding LOI. After the share price rose, the Board asked for $2.20; CLP agreed on 02/10/2021, conditioned on signing that day, and the merger agreement was signed that evening.</t>
         </is>
       </c>
     </row>

--- a/extraction/synacor.xlsx
+++ b/extraction/synacor.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
-    <numFmt numFmtId="166" formatCode="$0.00"/>
+    <numFmt numFmtId="166" formatCode="0.00##"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -69,10 +69,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,31 +440,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,7 +585,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>before 01/10/2018</t>
+          <t>by 01/10/2018</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -609,8 +609,8 @@
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -621,7 +621,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Company A, a private investment firm, expressed interest in exploring an acquisition of the Company before signing its NDA; bidder-led first contact in process 1. Exact date not given.</t>
+          <t>Company A, a private investment firm, approached expressing interest in a potential acquisition of Synacor before signing the 01/10/2018 NDA; date of the approach not given.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="3" t="n">
+      <c r="T2" s="4" t="n">
         <v>43110</v>
       </c>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="3" t="n">
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n">
         <v>43110</v>
       </c>
     </row>
@@ -669,8 +669,8 @@
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
@@ -681,7 +681,7 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Mutual NDA including a standstill for the Company's benefit; Company A's entry to process 1.</t>
+          <t>Mutual NDA with a standstill for the benefit of Synacor; Company A enters process 1.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -691,13 +691,13 @@
       </c>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
-      <c r="T3" s="3" t="n">
+      <c r="T3" s="4" t="n">
         <v>43110</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="4" t="n">
         <v>43110</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="4" t="n">
         <v>43110</v>
       </c>
     </row>
@@ -731,8 +731,8 @@
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -755,7 +755,7 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>No condition or financing reported; price not disclosed. Non-binding indication of interest to acquire the Company, unsolicited (before any target outreach), so round 0.</t>
+          <t>No conditions reported. Non-binding indication of interest to acquire the whole Company; price, form of consideration and terms not disclosed. Unsolicited (before any outreach).</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -765,13 +765,13 @@
       </c>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
-      <c r="T4" s="3" t="n">
+      <c r="T4" s="4" t="n">
         <v>43137</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="4" t="n">
         <v>43137</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="4" t="n">
         <v>43137</v>
       </c>
     </row>
@@ -805,8 +805,8 @@
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -829,7 +829,7 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>No condition or financing reported; price not disclosed. Updated non-binding IOI after discussion between the parties; revises #3. Its value is what Company A later could not support (#8).</t>
+          <t>No conditions reported. Updated non-binding indication of interest after discussion between the parties; revises #3; price and changed terms not disclosed.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -839,13 +839,13 @@
       </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
-      <c r="T5" s="3" t="n">
+      <c r="T5" s="4" t="n">
         <v>43215</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" s="4" t="n">
         <v>43215</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="4" t="n">
         <v>43215</v>
       </c>
     </row>
@@ -875,8 +875,8 @@
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
@@ -885,23 +885,23 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Target's financial adviser, engaged to evaluate potential strategic opportunities; engagement letter had a stated termination date of 12/31/2018. No other end of the relationship is reported.</t>
+          <t>Synacor’s financial adviser “for purposes of evaluating potential strategic opportunities”; engagement letter had a stated termination date of 12/31/2018. No later Liontree activity reported.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“On May 8, 2018, the Company engaged Liontree Advisors LLC (“Liontree”) to act as the Company’s financial advisor” (p. 30)</t>
+          <t>“On May 8, 2018, the Company engaged Liontree Advisors LLC (“Liontree”) to act as the Company’s financial advisor for purposes of evaluating potential strategic opportunities” (p. 30)</t>
         </is>
       </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
-      <c r="T6" s="3" t="n">
+      <c r="T6" s="4" t="n">
         <v>43228</v>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="4" t="n">
         <v>43228</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="4" t="n">
         <v>43228</v>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
+          <t>Synacor</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -931,8 +931,8 @@
       <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
@@ -941,12 +941,12 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Liontree's outreach to about 12 strategic and financial companies is process 1's first outreach wave; its start is undated, so it is dated from the engagement it carried out (#5). No bid due date stated. Company A carried in from round 0.</t>
+          <t>Round 1 opens with Liontree’s outreach wave, reported only as following its 05/08/2018 engagement; no due date reported. Company A’s April IOI remained outstanding.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“Liontree then reached out to approximately 12 potential strategic and financial companies to evaluate their interest in an acquisition of the Company” (p. 30)</t>
+          <t>“Liontree then reached out to approximately 12 potential strategic and financial companies to evaluate their interest in an acquisition of the Company.” (p. 30)</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="S7" s="2" t="n"/>
-      <c r="T7" s="3" t="n">
+      <c r="T7" s="4" t="n">
         <v>43228</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="4" t="n">
         <v>43228</v>
       </c>
-      <c r="V7" s="2" t="n"/>
+      <c r="V7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -974,7 +974,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Approximately 12 strategic and financial companies (Liontree outreach)</t>
+          <t>Approx. 12 strategic and financial parties (Liontree outreach)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -993,8 +993,8 @@
       <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
@@ -1003,23 +1003,23 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Count: approximately 12. Target-initiated contacts by Liontree; strategic/financial split not given. None is reported to have signed an NDA or submitted an IOI, so none entered.</t>
+          <t>Count: approximately 12. Target-initiated contacts by Liontree, mixed strategic and financial (no split given). None reported signing an NDA or submitting an IOI, so none entered.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“The outreach by Liontree to additional parties did not lead to an indication of interest from any of these parties” (p. 30)</t>
+          <t>“The outreach by Liontree to additional parties did not lead to an indication of interest from any of these parties with respect to a potential strategic transaction” (p. 30)</t>
         </is>
       </c>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
-      <c r="T8" s="3" t="n">
+      <c r="T8" s="4" t="n">
         <v>43228</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="4" t="n">
         <v>43228</v>
       </c>
-      <c r="V8" s="2" t="n"/>
+      <c r="V8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1051,8 +1051,8 @@
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
@@ -1067,23 +1067,23 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Company A told the Company it could not support a deal at the value in its non-binding IOI (#4, price undisclosed): its value is below its earlier offer. No bidder remains live in process 1.</t>
+          <t>Company A told Synacor it could not support a transaction at the value proposed in its own IOI (#4), i.e. its valuation fell below its earlier offer. Leaves process 1.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“Company A informed the Company that they were unable to support the transaction at the proposed value set forth in the non-binding indication of interest” (p. 30)</t>
+          <t>“On June 20, 2018, Company A informed the Company that they were unable to support the transaction at the proposed value set forth in the non-binding indication of interest.” (p. 30)</t>
         </is>
       </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
-      <c r="T9" s="3" t="n">
+      <c r="T9" s="4" t="n">
         <v>43271</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="U9" s="4" t="n">
         <v>43271</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="4" t="n">
         <v>43271</v>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
+          <t>Synacor</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -1113,8 +1113,8 @@
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Inferred restart. Process 1 lapsed after Company A's 06/20/2018 withdrawal (last dated acquirer contact; Liontree outreach undated). Fresh start: NDA with Company C (#10). No participation open from process 1. Company B 'merger of equals' talks not treated as a sale (Q2).</t>
+          <t>Inferred restart at Company C’s NDA. Last acquirer contact in process 1: Company A’s withdrawal 06/20/2018 (Liontree outreach undated). Company B merger-of-equals talks (Oct 2018–Mar 2019) not treated as a sale. Closes no open participation.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
-      <c r="T10" s="3" t="n">
+      <c r="T10" s="4" t="n">
         <v>43540</v>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="U10" s="4" t="n">
         <v>43525</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="4" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -1181,8 +1181,8 @@
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
@@ -1193,23 +1193,23 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Mutual NDA with standstill for the Company's benefit, 'to explore a potential business combination'. Company C is a publicly-traded software company; who initiated contact is not stated. Company C's entry to process 2.</t>
+          <t>Mutual NDA with standstill for Synacor’s benefit, “to explore a potential business combination”; Company C (publicly-traded software company) enters. Which side initiated contact not stated.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“entered into a mutual non-disclosure agreement, which included a standstill provision for the benefit of the Company, to explore a potential business combination” (p. 30)</t>
+          <t>“which included a standstill provision for the benefit of the Company, to explore a potential business combination” (p. 30)</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
-      <c r="T11" s="3" t="n">
+      <c r="T11" s="4" t="n">
         <v>43540</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="U11" s="4" t="n">
         <v>43525</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="4" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -1243,8 +1243,8 @@
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
@@ -1255,27 +1255,23 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Mutual NDA with standstill. Company E (investment subsidiary of a publicly-traded financial services company) had expressed interest in acquiring only the portal and advertising business, within management's divestiture effort. Entry as a segment buyer (Q3).</t>
+          <t>Mutual NDA with standstill with Company E (investment subsidiary of a publicly-traded financial services company), which had expressed interest in buying only the portal and advertising business. Segment-only interest; enters process 2.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“on July 30, 2019, the Company entered into a mutual non-disclosure agreement, which included a standstill provision for the benefit of the Company” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“on July 30, 2019, the Company entered into a mutual non-disclosure agreement, which included a standstill provision for the benefit of the Company, with an investment subsidiary” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
-      <c r="T12" s="3" t="n">
+      <c r="T12" s="4" t="n">
         <v>43676</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="4" t="n">
         <v>43676</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="4" t="n">
         <v>43676</v>
       </c>
     </row>
@@ -1309,8 +1305,8 @@
       <c r="G13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -1333,23 +1329,23 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>No condition or financing reported; price not disclosed. Non-binding LOI to acquire the Company for cash and stock. Arrived before the banker outreach, so round 0; Canaccord was engaged on 08/25/2019 partly to evaluate it.</t>
+          <t>No conditions reported. Non-binding LOI to acquire the whole Company for cash and stock; price not disclosed. Canaccord was engaged 12 days later to evaluate it.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“On August 13, 2019, Company C submitted a non-binding letter of intent proposing an acquisition of the Company with consideration in the form of cash and stock” (p. 30)</t>
+          <t>“On August 13, 2019, Company C submitted a non-binding letter of intent proposing an acquisition of the Company with consideration in the form of cash and stock.” (p. 30)</t>
         </is>
       </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
-      <c r="T13" s="3" t="n">
+      <c r="T13" s="4" t="n">
         <v>43690</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" s="4" t="n">
         <v>43690</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="4" t="n">
         <v>43690</v>
       </c>
     </row>
@@ -1359,12 +1355,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>third quarter of 2019</t>
+          <t>Q3 2019</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Approximately five companies (portal and advertising divestiture outreach)</t>
+          <t>Approx. 5 companies (portal and advertising outreach)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1383,8 +1379,8 @@
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
@@ -1393,7 +1389,7 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Count: approximately 5. Management outreach to sell only the portal and advertising business (segment divestiture, not a whole-company sale). Company E and Company F may be among them; the filing does not say.</t>
+          <t>Count: approximately 5. Management-led outreach while the Board evaluated divesting the portal and advertising business (segment only, not a whole-company solicitation). Whether Companies E or F were among them is not stated.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1401,19 +1397,15 @@
           <t>“The Company’s management engaged in outreach to approximately five companies” (p. 31)</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+      <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
-      <c r="T14" s="3" t="n">
+      <c r="T14" s="4" t="n">
         <v>43692</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="4" t="n">
         <v>43647</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="4" t="n">
         <v>43738</v>
       </c>
     </row>
@@ -1443,8 +1435,8 @@
       <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
@@ -1453,7 +1445,7 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Target's financial adviser, engaged to evaluate Company C's proposal and review other strategic and financial opportunities; stated termination 01/15/2020. Separately engaged 01/02/2020 for the target's own Company D acquisition (not a sale).</t>
+          <t>Synacor’s financial adviser, to evaluate Company C’s proposal and other strategic and financial opportunities (term to 01/15/2020). Re-engaged 01/02/2020 (Company D deal); amended 07/30/2020 and 01/25/2021; acted through process 3 and gave the 02/10/2021 fairness opinion.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1463,13 +1455,13 @@
       </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="4" t="n">
         <v>43702</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="4" t="n">
         <v>43702</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="4" t="n">
         <v>43702</v>
       </c>
     </row>
@@ -1484,7 +1476,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
+          <t>Synacor</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1499,8 +1491,8 @@
       <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
@@ -1509,12 +1501,12 @@
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Canaccord's outreach to 18 additional parties, at the Board's direction under the 08/25/2019 engagement, is the first whole-company outreach wave; start undated. No bid due date stated. Company C carried in from round 0.</t>
+          <t>Round 1 opens with Canaccord’s outreach to 18 additional parties at the Board’s direction under its 08/25/2019 engagement; outreach undated; no due date reported. Company C (bid #12) and Company E (segment NDA) already in.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“Pursuant to this engagement, at the direction of the Company Board, Canaccord Genuity reached out to an additional 18 parties” (p. 31)</t>
+          <t>“at the direction of the Company Board, Canaccord Genuity reached out to an additional 18 parties to determine whether such parties would be interested in exploring a potential strategic transaction” (p. 31)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -1523,13 +1515,13 @@
         </is>
       </c>
       <c r="S16" s="2" t="n"/>
-      <c r="T16" s="3" t="n">
+      <c r="T16" s="4" t="n">
         <v>43702</v>
       </c>
-      <c r="U16" s="3" t="n">
+      <c r="U16" s="4" t="n">
         <v>43702</v>
       </c>
-      <c r="V16" s="2" t="n"/>
+      <c r="V16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1561,8 +1553,8 @@
       <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
@@ -1573,7 +1565,7 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated contacts; types not given. None led to an indication of interest and none is reported to have signed an NDA, so none entered.</t>
+          <t>Target-initiated contacts for strategic and financial opportunities; types not given. None produced an indication of interest and none is reported signing an NDA, so none entered.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -1583,13 +1575,13 @@
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
-      <c r="T17" s="3" t="n">
+      <c r="T17" s="4" t="n">
         <v>43702</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="U17" s="4" t="n">
         <v>43702</v>
       </c>
-      <c r="V17" s="2" t="n"/>
+      <c r="V17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1619,10 +1611,10 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1645,27 +1637,23 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>No condition or financing reported; price not disclosed. Non-binding IOI for the portal and advertising business only. Company F (information and technology services) held a valid May 2018 NDA from a commercial relationship; reuse not stated. Answers management's divestiture outreach (Q3).</t>
+          <t>No conditions reported. Non-binding IOI from an information and technology services company interested in the portal and advertising business (existing May 2018 commercial NDA); price not disclosed. Parties later “unable to agree on terms” (undated); closed by #19.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“Company F submitted a non-binding indication of interest to the Company on September 15, 2019” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“Company F submitted a non-binding indication of interest to the Company on September 15, 2019. However, the parties were ultimately unable to agree on terms for the transaction.” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
-      <c r="T18" s="3" t="n">
+      <c r="T18" s="4" t="n">
         <v>43723</v>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" s="4" t="n">
         <v>43723</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="4" t="n">
         <v>43723</v>
       </c>
     </row>
@@ -1675,12 +1663,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>after 09/15/2019 (undated)</t>
+          <t>October 2019</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Company F</t>
+          <t>Company C</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1697,10 +1685,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
@@ -1709,33 +1697,35 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Terms or process</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>The parties 'were ultimately unable to agree on terms'; who ended talks and when are not stated. Withdrew is a convention for this mutual ending (Q4). No upper date bound is established.</t>
+          <t>Synacor and Company C mutually agreed not to pursue a transaction after further discussion and Canaccord’s review; the filing does not say which side initiated or why.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“Company F submitted a non-binding indication of interest to the Company on September 15, 2019. However, the parties were ultimately unable to agree on terms for the transaction.” (p. 31)</t>
+          <t>“the Company and Company C mutually agreed in October 2019 not to pursue a transaction” (p. 31)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
-      <c r="T19" s="3" t="n">
-        <v>43724</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>43724</v>
-      </c>
-      <c r="V19" s="2" t="n"/>
+      <c r="T19" s="4" t="n">
+        <v>43754</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>43739</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>43769</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1743,68 +1733,64 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>October 2019</t>
+          <t>07/13/2020</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Company C</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Process restarted</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>The Company and Company C 'mutually agreed' not to pursue a transaction, after further discussion and Canaccord's engagement; no reason given. Recorded as Withdrew for a mutual ending (Q4). Leaves only Company E's portal NDA open.</t>
+          <t>Inferred restart when Synacor took up Company E’s approach. Last acquirer contact in process 2: Company C, October 2019 (Company F talks, 18-party outreach undated); Company D deal was Synacor as buyer. Closes Company E (07/30/2019 segment NDA) and Company F.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“the Company and Company C mutually agreed in October 2019 not to pursue a transaction” (p. 31)</t>
+          <t>“As a result of this outreach, the Company directed Canaccord Genuity to reach out to Company E for further information about a potential strategic transaction.” (p. 32)</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S20" s="2" t="n"/>
-      <c r="T20" s="3" t="n">
-        <v>43754</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>43739</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>43769</v>
+      <c r="T20" s="4" t="n">
+        <v>44025</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>44025</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>44025</v>
       </c>
     </row>
     <row r="21">
@@ -1818,13 +1804,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
+          <t>Company E</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Process restarted</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1833,8 +1823,8 @@
       <c r="G21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
@@ -1842,34 +1832,26 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Inferred restart. Last acquirer contact before the gap: Company C talks ended October 2019 (Company F's end undated). Fresh start: Company E's approach taken up and outreach launched. Closes Company E's open process-2 participation (portal NDA, #11).</t>
+          <t>Company E approached via director Kevin Rendino (who had co-invested with E) about acquiring Synacor; Synacor directed Canaccord to contact E. First contact in process 3; no price.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“As a result of this outreach, the Company directed Canaccord Genuity to reach out to Company E for further information about a potential strategic transaction” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q2</t>
-        </is>
-      </c>
+          <t>“informed the Company’s management of potential interest that Company E had in a potential acquisition of the Company.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="4" t="n">
         <v>44025</v>
       </c>
     </row>
@@ -1894,7 +1876,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1903,8 +1885,8 @@
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
@@ -1915,23 +1897,23 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Director Kevin Rendino relayed Company E's interest in acquiring the whole Company; Rendino had invested alongside E through affiliated entities. Bidder-led first contact in process 3; the Company then had Canaccord contact E.</t>
+          <t>Amendment to the 07/30/2019 mutual NDA, extending the standstill to 07/30/2021 (no proposals without invitation); new executed instrument, so Company E enters process 3.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Kevin Rendino, informed the Company’s management of potential interest that Company E had in a potential acquisition of the Company” (p. 32)</t>
+          <t>“Also, on July 13, 2020, the Company and Company E entered into an amendment to their non-disclosure agreement entered into on July 30, 2019” (p. 32)</t>
         </is>
       </c>
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
-      <c r="T22" s="3" t="n">
+      <c r="T22" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="4" t="n">
         <v>44025</v>
       </c>
     </row>
@@ -1941,28 +1923,28 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>07/13/2020</t>
+          <t>mid-July 2020</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Canaccord Genuity LLC</t>
+          <t>Synacor</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
@@ -1971,24 +1953,28 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Target's financial adviser, acting in process 3 from 07/13/2020; engagement letter amended 07/30/2020 (term to 01/31/2021) and 01/25/2021 (to 06/30/2021). Gave the $2.20 fairness opinion on 02/10/2021.</t>
+          <t>Synacor directs Canaccord to solicit buyers for the Company and/or its software and services business; outreach runs mid-July to mid-September 2020. Company E already in (#21). Due date 09/17/2020 set later (#26).</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“the Company directed Canaccord Genuity to reach out to Company E for further information about a potential strategic transaction” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n"/>
+          <t>“The Company also then directed Canaccord Genuity to commence outreach to various parties to consider an acquisition of the Company and/or its software and services business.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="n"/>
-      <c r="T23" s="3" t="n">
+      <c r="T23" s="4" t="n">
+        <v>44028</v>
+      </c>
+      <c r="U23" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="U23" s="3" t="n">
-        <v>44025</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>44025</v>
+      <c r="V23" s="4" t="n">
+        <v>44031</v>
       </c>
     </row>
     <row r="24">
@@ -1997,60 +1983,60 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/13/2020</t>
+          <t>mid-July to mid-September 2020</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>37 parties (Canaccord outreach; other than Companies A–D)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Amendment to E's 07/30/2019 mutual NDA extending the standstill (no proposals without invitation) to 07/30/2021. A newly executed instrument, so E's entry to process 3.</t>
+          <t>Target-initiated contacts; types not given. Company H is established as one of them (its interest arose from this outreach); CLP, Company G and Company E may be. Only the parties described individually produced IOIs.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“on July 13, 2020, the Company and Company E entered into an amendment to their non-disclosure agreement entered into on July 30, 2019” (p. 32)</t>
+          <t>“From the middle of July 2020 to the middle of September 2020, Canaccord Genuity reached out to 37 parties (other than Companies A-D) at the direction of the Company” (p. 32)</t>
         </is>
       </c>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
-      <c r="T24" s="3" t="n">
+      <c r="T24" s="4" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U24" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="U24" s="3" t="n">
-        <v>44025</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>44025</v>
+      <c r="V24" s="4" t="n">
+        <v>44093</v>
       </c>
     </row>
     <row r="25">
@@ -2059,28 +2045,32 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>after 07/13/2020 (undated)</t>
+          <t>mid-July to mid-September 2020 (undated)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
+          <t>NDA signers from Canaccord outreach (remainder of 14)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
@@ -2089,25 +2079,27 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>The Company directed Canaccord to begin outreach on an acquisition of the whole Company and/or its software and services business; no Board meeting is reported. Window: after E's 07/13 approach, before outreach began in mid-July.</t>
+          <t>Count: 12–14. Filing total 14 NDA signers, all given access to confidential information. Remainder excludes CLP (#27) and Company E’s amendment (#21) only if they are among the 14 (likely for CLP, not stated). Company G, Company H may be inside.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“The Company also then directed Canaccord Genuity to commence outreach to various parties to consider an acquisition of the Company and/or its software and services business” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="n"/>
+          <t>“Of the parties contacted, 14 parties executed non-disclosure agreements with the Company and were provided access to confidential information relating to the Company’s business and prospects.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="n"/>
-      <c r="T25" s="3" t="n">
-        <v>44028</v>
-      </c>
-      <c r="U25" s="3" t="n">
+      <c r="T25" s="4" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U25" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="V25" s="3" t="n">
-        <v>44031</v>
-      </c>
+      <c r="V25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2115,18 +2107,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>mid-July 2020</t>
+          <t>mid-July to mid-September 2020</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
+          <t>8 parties (management portal and advertising outreach)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2135,38 +2131,36 @@
       <c r="G26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
+      <c r="M26" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Canaccord's outreach wave from mid-July (#26). Parties still involved were asked for non-binding IOIs by 09/17/2020; when that request was made is not stated, so no separate Deadline set row. Company E carried in from round 0.</t>
+          <t>Management-led contacts, at the same time as Canaccord’s outreach, about buying only the portal and advertising business. None reported signing an NDA or bidding.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“Parties that remained involved in the process were requested to submit a non-binding indication of interest by September 17, 2020” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“the Company’s management reached out to 8 parties to determine whether such parties would be interested in exploring a potential acquisition of the portal and advertising business.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="3" t="n">
-        <v>44028</v>
-      </c>
-      <c r="U26" s="3" t="n">
+      <c r="T26" s="4" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U26" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>44031</v>
+      <c r="V26" s="4" t="n">
+        <v>44093</v>
       </c>
     </row>
     <row r="27">
@@ -2175,22 +2169,18 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>mid-July to mid-September 2020</t>
+          <t>undated, by 09/17/2020</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>37 parties (Canaccord outreach, other than Companies A-D)</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2199,36 +2189,38 @@
       <c r="G27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="n">
-        <v>37</v>
-      </c>
+      <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated contacts about the whole Company and/or its software and services business; types not given. Company H is established as one of them (#35); CLP and Company G may be. Of the 37, 14 signed NDAs (#28).</t>
+          <t>Parties still involved were asked for non-binding indications of interest by 09/17/2020; the day the request was communicated is not stated.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“From the middle of July 2020 to the middle of September 2020, Canaccord Genuity reached out to 37 parties (other than Companies A-D)” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="n"/>
+          <t>“Parties that remained involved in the process were requested to submit a non-binding indication of interest by September 17, 2020.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="n"/>
-      <c r="T27" s="3" t="n">
+      <c r="T27" s="4" t="n">
         <v>44059</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" s="4" t="n">
         <v>44025</v>
       </c>
-      <c r="V27" s="3" t="n">
-        <v>44093</v>
+      <c r="V27" s="4" t="n">
+        <v>44091</v>
       </c>
     </row>
     <row r="28">
@@ -2237,22 +2229,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>mid-July to mid-September 2020</t>
+          <t>09/08/2020</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>8 parties (portal and advertising business, management outreach)</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2261,24 +2253,24 @@
       <c r="G28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>At the same time as #26, management contacted 8 parties about buying only the portal and advertising business (segment). None is reported to have signed an NDA or bid in this window.</t>
+          <t>Confidentiality agreement with standstill (12 months or until a significant event); CLP, a private equity manager, enters. Likely, but not stated to be, one of the 14 NDA signers (#24).</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“the Company’s management reached out to 8 parties to determine whether such parties would be interested in exploring a potential acquisition of the portal and advertising business” (p. 32)</t>
+          <t>“On September 8, 2020, Centre Lane Partners, LLC (“CLP”) entered into the Confidentiality Agreement (as defined herein) with the Company” (p. 32)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -2287,14 +2279,14 @@
         </is>
       </c>
       <c r="S28" s="2" t="n"/>
-      <c r="T28" s="3" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>44025</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>44093</v>
+      <c r="T28" s="4" t="n">
+        <v>44082</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>44082</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>44082</v>
       </c>
     </row>
     <row r="29">
@@ -2303,22 +2295,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>mid-July to mid-September 2020</t>
+          <t>09/10/2020</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>NDA signers from Canaccord outreach (14 stated; 13-14 besides CLP)</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2327,37 +2319,53 @@
       <c r="G29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
+      <c r="H29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Count: 13-14. Filing: 14 of the 37 contacted signed NDAs and received confidential information. CLP's 09/08/2020 agreement (#29) may be one of the 14; Company G and Company H may also be members (Q5). Execution dates not given.</t>
+          <t>No condition stated; diligence later opened under exclusivity. Non-binding LOI, all cash, 100% of equity and awards at $2.00; 180 Degree (Rendino affiliate) to roll over its stake. Ref: Q3 2020 share-price range $1.01–$1.62 (p. 25).</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Of the parties contacted, 14 parties executed non-disclosure agreements with the Company and were provided access to confidential information relating to the Company’s business and prospects” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“for an all-cash transaction to acquire 100% of the Company’s outstanding equity and equity awards at a per Share price of $2.00.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
-      <c r="T29" s="3" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>44025</v>
-      </c>
-      <c r="V29" s="2" t="n"/>
+      <c r="T29" s="4" t="n">
+        <v>44084</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>44084</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>44084</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2365,22 +2373,18 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>09/08/2020</t>
+          <t>09/13/2020</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CLP (Centre Lane Partners, LLC)</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Gunderson Dettmer</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2389,40 +2393,34 @@
       <c r="G30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality Agreement with a standstill (12 months or earlier significant event). CLP is a private-equity manager; Parent is controlled by its fund CLP Fund V. Whether CLP came through Canaccord's outreach and is one of the 14 signers is not stated (Q5).</t>
+          <t>Synacor’s outside corporate counsel, first shown acting at the 09/13/2020 Board meeting that formed the Special Committee (excluding Rendino) to lead negotiations with Company E.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“On September 8, 2020, Centre Lane Partners, LLC (“CLP”) entered into the Confidentiality Agreement (as defined herein) with the Company, which included a standstill provision” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“the Company’s outside corporate counsel, Gunderson Dettmer (“Gunderson”)” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
-      <c r="T30" s="3" t="n">
-        <v>44082</v>
-      </c>
-      <c r="U30" s="3" t="n">
-        <v>44082</v>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v>44082</v>
+      <c r="T30" s="4" t="n">
+        <v>44087</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>44087</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>44087</v>
       </c>
     </row>
     <row r="31">
@@ -2431,12 +2429,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>09/10/2020</t>
+          <t>09/14/2020</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Company G</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2446,7 +2444,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2455,12 +2453,8 @@
       <c r="G31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2483,24 +2477,24 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>No condition or financing source reported; E's diligence began only after 09/23 (#46). Non-binding LOI, all cash, for 100% of equity and equity awards at $2.00; 180 Degree (Rendino affiliate) to roll over its stake. Before the 09/17 due date.</t>
+          <t>Financing: equity plus third-party debt, commitment not reported. Non-binding IOI for the software and services business only; cash; EV-basis value “a fraction” of Company E’s implied value. G’s NDA not reported; enters by this bid.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“for an all-cash transaction to acquire 100% of the Company’s outstanding equity and equity awards at a per Share price of $2.00” (p. 32)</t>
+          <t>“On September 14, 2020, the Company received a non-binding indication of interest from a financial acquirer (“Company G”) who regularly makes investments in enterprise software companies.” (p. 32)</t>
         </is>
       </c>
       <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
-      <c r="T31" s="3" t="n">
-        <v>44084</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>44084</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>44084</v>
+      <c r="T31" s="4" t="n">
+        <v>44088</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>44088</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>44088</v>
       </c>
     </row>
     <row r="32">
@@ -2509,18 +2503,18 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>09/13/2020</t>
+          <t>09/14/2020</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Gunderson Dettmer</t>
+          <t>180 Degree Capital Corp. (shareholder; Rendino affiliate)</t>
         </is>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2529,8 +2523,8 @@
       <c r="G32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
@@ -2539,24 +2533,24 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Target's outside corporate counsel; first shown acting at the 09/13/2020 Board meeting.</t>
+          <t>Rollover support: 180 Degree confirmed to Gunderson it supported rolling its equity into Company E’s proposed deal (#28), subject to due diligence. Supporter only; E remains the bidder.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“the Company’s outside corporate counsel, Gunderson Dettmer (“Gunderson”)” (p. 32)</t>
+          <t>“On September 14, 2020, 180 Degree, an affiliate of Mr. Rendino, confirmed to Gunderson that it was supportive of rolling over its existing equity position in the Company” (p. 33)</t>
         </is>
       </c>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
-      <c r="T32" s="3" t="n">
-        <v>44087</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>44087</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>44087</v>
+      <c r="T32" s="4" t="n">
+        <v>44088</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>44088</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>44088</v>
       </c>
     </row>
     <row r="33">
@@ -2565,15 +2559,19 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>09/13/2020</t>
+          <t>by 09/16/2020</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
+          <t>Company H</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -2585,34 +2583,38 @@
       <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
+      <c r="M33" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Board forms a Special Committee (Bhise, Kau, Donohue, Fawaz, Montgomery) to lead negotiations with Company E because director Rendino had invested alongside E; Rendino recuses from E matters. The Board also reviewed E's LOI and outreach feedback.</t>
+          <t>Canaccord reports that Company H, a public-company software acquirer reached through its outreach, expressed more serious interest in acquiring Synacor but could not yet submit an LOI. No NDA or bid reported for H.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“The Company Special Committee was authorized to lead the negotiations with Company E on behalf of the Company” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="n"/>
+          <t>“had also expressed more serious interest in an acquisition of the Company, but was not yet in a position to submit a letter of intent” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S33" s="2" t="n"/>
-      <c r="T33" s="3" t="n">
-        <v>44087</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>44087</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>44087</v>
+      <c r="T33" s="4" t="n">
+        <v>44090</v>
+      </c>
+      <c r="U33" s="4" t="n"/>
+      <c r="V33" s="4" t="n">
+        <v>44090</v>
       </c>
     </row>
     <row r="34">
@@ -2621,22 +2623,18 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/14/2020</t>
+          <t>09/17/2020</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Company G</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2645,52 +2643,34 @@
       <c r="G34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Financing: equity plus third-party debt, commitment status not stated. Non-binding IOI for only the software and services business; valuation 'a fraction' of E's implied value, no per-share price. G regularly invests in enterprise software. Entry by bid; no NDA reported (Q3).</t>
+          <t>Synacor returns a revised LOI to Company E asking for its best offer on price; Canaccord then relays the same request by phone. A request to improve within round 1.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“Company G proposed paying cash for the purchase price, but Company G indicated that it would utilize equity and third party debt financing to finance the transaction” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“On September 17, 2020, the Company submitted a revised letter of intent to Company E, which included a request for Company E to provide its best offer on purchase price.” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
-      <c r="T34" s="3" t="n">
-        <v>44088</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>44088</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>44088</v>
+      <c r="T34" s="4" t="n">
+        <v>44091</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>44091</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>44091</v>
       </c>
     </row>
     <row r="35">
@@ -2699,18 +2679,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/14/2020</t>
+          <t>09/17/2020</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>180 Degree Capital Corp.</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
+          <t>CLP (Centre Lane Partners, LLC)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2719,34 +2703,52 @@
       <c r="G35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
+      <c r="H35" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Rollover support: 180 Degree (affiliate of director Rendino; later a Tender and Support Agreement signatory) told Gunderson it supported rolling its equity into E's proposed deal, subject to due diligence. Supports E; not a bidding group (E4).</t>
+          <t>Financing from committed private-equity capital, but diligence still open (see #40). Non-binding IOI for 100% of equity and awards at $1.35–$1.41 per share, cash; submitted on the due date.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“180 Degree, an affiliate of Mr. Rendino, confirmed to Gunderson that it was supportive of rolling over its existing equity position in the Company as part of the proposed transaction” (p. 33)</t>
+          <t>“contemplated a purchase price of $1.35 to $1.41 per Share. CLP proposed paying cash for the purchase price by utilizing committed capital from its private equity vehicles” (p. 33)</t>
         </is>
       </c>
       <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
-      <c r="T35" s="3" t="n">
-        <v>44088</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>44088</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>44088</v>
+      <c r="T35" s="4" t="n">
+        <v>44091</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>44091</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>44091</v>
       </c>
     </row>
     <row r="36">
@@ -2755,22 +2757,18 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>09/16/2020</t>
+          <t>09/17/2020</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2779,36 +2777,38 @@
       <c r="G36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Canaccord reports that Company H, a public-company software acquirer reached in its outreach, has 'more serious interest' but cannot yet submit an LOI. No NDA or bid is reported for H, so no entry. Committee also met E's representatives.</t>
+          <t>IOI due date reached. Submissions reported: Company E (#28), Company G (#30, segment only), CLP (#34). Synacor then evaluated these and moved to exclusivity with E.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“had also expressed more serious interest in an acquisition of the Company, but was not yet in a position to submit a letter of intent” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="n"/>
+          <t>“Parties that remained involved in the process were requested to submit a non-binding indication of interest by September 17, 2020.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="n"/>
-      <c r="T36" s="3" t="n">
-        <v>44090</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>44090</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>44090</v>
+      <c r="T36" s="4" t="n">
+        <v>44091</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>44091</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>44091</v>
       </c>
     </row>
     <row r="37">
@@ -2817,18 +2817,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>09/17/2020</t>
+          <t>by 09/17/2020</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n"/>
+          <t>NDA signers that did not submit IOIs</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -2837,37 +2841,43 @@
       <c r="G37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Price request: the Company sent Company E a revised LOI asking for its best offer on price, and Canaccord repeated it by phone. Treated as bargaining within round 1, not a best-and-final round (Q6).</t>
+          <t>Count: 11–14. Inferred: 14 NDA signers; only E, G and CLP reported bidding, “none” other. 14 less those of E, G, CLP inside the 14. H, if a signer, is inside. Some may have left before the request.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“the Company submitted a revised letter of intent to Company E, which included a request for Company E to provide its best offer on purchase price” (p. 33)</t>
+          <t>“Other than as described below, none of the outreach attempts to these 37 parties ultimately led to an indication of interest from any of these parties” (p. 32)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S37" s="2" t="n"/>
-      <c r="T37" s="3" t="n">
+      <c r="T37" s="4" t="n">
         <v>44091</v>
       </c>
-      <c r="U37" s="3" t="n">
-        <v>44091</v>
-      </c>
-      <c r="V37" s="3" t="n">
+      <c r="U37" s="4" t="n"/>
+      <c r="V37" s="4" t="n">
         <v>44091</v>
       </c>
     </row>
@@ -2877,12 +2887,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>09/17/2020</t>
+          <t>09/18/2020</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CLP (Centre Lane Partners, LLC)</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2901,11 +2911,11 @@
       <c r="G38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>1.41</v>
+      <c r="H38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2929,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
@@ -2929,24 +2939,24 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Financing from committed capital of CLP's private equity vehicles, but diligence still open (#44 is 'subject to further diligence'). Non-binding IOI for 100% of equity and equity awards at $1.35-$1.41 cash, on the due date. CLP's first bid.</t>
+          <t>Requested exclusivity to 10/23/2020 (about five weeks) for diligence and documents. Revised LOI answering #33: $2.00 is the only price E will pay (same as #28), all cash, 180 Degree rollover retained.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“contemplated a purchase price of $1.35 to $1.41 per Share. CLP proposed paying cash for the purchase price by utilizing committed capital from its private equity vehicles” (p. 33)</t>
+          <t>“Company E provided a revised letter of intent to the Company, re-affirming that it would only pay $2.00 per Share in connection with its acquisition of the Company” (p. 33)</t>
         </is>
       </c>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
-      <c r="T38" s="3" t="n">
-        <v>44091</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>44091</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>44091</v>
+      <c r="T38" s="4" t="n">
+        <v>44092</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>44092</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>44092</v>
       </c>
     </row>
     <row r="39">
@@ -2955,18 +2965,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>09/17/2020</t>
+          <t>09/18/2020</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
+          <t>Company E</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -2975,38 +2989,36 @@
       <c r="G39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
+      <c r="M39" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Due date for round-1 non-binding IOIs. Received by then: Company E (#30), Company G (#33, segment only) and CLP (#37). The target then acted on these bids (outcome, Q7).</t>
+          <t>Requested: Company E asks Synacor to deal exclusively with it until 10/23/2020, in its revised LOI (#37).</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“requested to submit a non-binding indication of interest by September 17, 2020” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
+          <t>“requesting that the Company enter into exclusivity with it until October 23, 2020” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n"/>
-      <c r="T39" s="3" t="n">
-        <v>44091</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>44091</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>44091</v>
+      <c r="T39" s="4" t="n">
+        <v>44092</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>44092</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>44092</v>
       </c>
     </row>
     <row r="40">
@@ -3015,22 +3027,18 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>by 09/17/2020</t>
+          <t>09/21/2020</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Outreach NDA signers without an IOI</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -3039,44 +3047,34 @@
       <c r="G40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Count: 12-14. 14 NDA signers minus submitters among them (CLP, Company G; membership not stated) = 12-14. Filing: no other outreach party produced an IOI. Some were 'still conducting diligence' on 09/16 and may have lasted until talks ended 09/23 (#47).</t>
+          <t>Price request: Special Committee has Canaccord ask Company G to raise its software-segment price and CLP to raise its whole-company price; E’s revised LOI and all IOIs reviewed.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“Other than as described below, none of the outreach attempts to these 37 parties ultimately led to an indication of interest from any of these parties” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“The Company Special Committee directed Canaccord Genuity to further follow up with Company G to seek to increase the purchase price payable for the software and services segment and CLP” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
-      <c r="T40" s="3" t="n">
-        <v>44091</v>
-      </c>
-      <c r="U40" s="2" t="n"/>
-      <c r="V40" s="3" t="n">
-        <v>44091</v>
+      <c r="T40" s="4" t="n">
+        <v>44095</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>44095</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>44095</v>
       </c>
     </row>
     <row r="41">
@@ -3085,12 +3083,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>09/18/2020</t>
+          <t>09/22/2020</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3100,7 +3098,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -3109,27 +3107,11 @@
       <c r="G41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n">
         <v>1</v>
       </c>
@@ -3137,12 +3119,12 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Heavy: asks for exclusivity until 10/23/2020 (about five weeks) for diligence and documents. Revised LOI answering #36, 're-affirming' E would only pay $2.00 cash for 100%; 180 Degree rollover kept.</t>
+          <t>Valuation statement without an offer: CLP said, subject to further diligence, it would consider raising its price 10%–25% per share above #34 (arithmetic, not stated: about $1.49–$1.76). Company G said the same day it could not increase.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“it would only pay $2.00 per Share in connection with its acquisition of the Company, and requesting that the Company enter into exclusivity with it until October 23, 2020” (p. 33)</t>
+          <t>“CLP provided a verbal indication that, subject to further diligence, it would consider increasing its purchase price by 10% to 25% per Share” (p. 33)</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -3151,14 +3133,14 @@
         </is>
       </c>
       <c r="S41" s="2" t="n"/>
-      <c r="T41" s="3" t="n">
-        <v>44092</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>44092</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>44092</v>
+      <c r="T41" s="4" t="n">
+        <v>44096</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>44096</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>44096</v>
       </c>
     </row>
     <row r="42">
@@ -3167,22 +3149,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>09/18/2020</t>
+          <t>09/22/2020</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -3191,8 +3173,8 @@
       <c r="G42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
@@ -3203,24 +3185,28 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Requested: Company E's revised LOI asks the Company to enter exclusivity with it until 10/23/2020.</t>
+          <t>Solicitation of a named party: CEO Bhise urges Company H to submit a whole-company proposal after the due date; H did not indicate a near-term proposal.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“requesting that the Company enter into exclusivity with it until October 23, 2020” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="n"/>
+          <t>“encourage it to submit a proposal relating to a potential acquisition of 100% of the Company’s outstanding equity and equity awards.” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S42" s="2" t="n"/>
-      <c r="T42" s="3" t="n">
-        <v>44092</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>44092</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>44092</v>
+      <c r="T42" s="4" t="n">
+        <v>44096</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>44096</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>44096</v>
       </c>
     </row>
     <row r="43">
@@ -3229,18 +3215,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>09/21/2020</t>
+          <t>09/22/2020</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n"/>
+          <t>Other portal and advertising prospects (Bhise outreach)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -3249,8 +3239,8 @@
       <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
@@ -3259,24 +3249,24 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Price requests: the Special Committee directs Canaccord to ask Company G to raise its software-and-services price and CLP to raise its whole-company price. It also reviewed E's revised LOI.</t>
+          <t>Count: unknown. CEO Bhise contacts companies thought interested in the portal and advertising business; none indicated a near-term proposal. None entered.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“The Company Special Committee directed Canaccord Genuity to further follow up with Company G to seek to increase the purchase price payable for the software and services segment” (p. 33)</t>
+          <t>“Mr. Bhise also reached out to other companies which the Company believed may have an interest in acquiring the Company’s portal and advertising business.” (p. 34)</t>
         </is>
       </c>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
-      <c r="T43" s="3" t="n">
-        <v>44095</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>44095</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>44095</v>
+      <c r="T43" s="4" t="n">
+        <v>44096</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>44096</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>44096</v>
       </c>
     </row>
     <row r="44">
@@ -3285,60 +3275,58 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>09/22/2020</t>
+          <t>09/23/2020</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Company G</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Asked to improve (#42), Company G says it cannot raise its software-and-services price; its IOI (#33) stands.</t>
+          <t>Round 2: Synacor signs Company E’s LOI (#37, $2.00) with exclusivity to 10/23/2020 and moves to diligence and definitive-agreement negotiation with E alone; all other discussions ended.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“Company G was unable to increase its purchase price” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="n"/>
+          <t>“From September 2020 through December 2020, the Company, Company E and their respective representatives engaged in diligence, and responded to related requests, and negotiated the terms of a definitive agreement” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="n"/>
-      <c r="T44" s="3" t="n">
-        <v>44096</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>44096</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>44096</v>
+      <c r="T44" s="4" t="n">
+        <v>44097</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>44097</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>44097</v>
       </c>
     </row>
     <row r="45">
@@ -3347,12 +3335,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>09/22/2020</t>
+          <t>09/23/2020</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CLP (Centre Lane Partners, LLC)</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3362,32 +3350,20 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n">
         <v>1</v>
       </c>
@@ -3395,28 +3371,24 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Heavy: 'subject to further diligence'. Verbal: CLP 'would consider' raising its $1.35-$1.41 IOI (#37) by 10%-25% per share. No per-share figure stated (arithmetic implies about $1.49-$1.76), so price cells blank (Q8).</t>
+          <t>Executed: Synacor and Company E enter E’s LOI, whose exclusivity runs to 10/23/2020 (about one month).</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“CLP provided a verbal indication that, subject to further diligence, it would consider increasing its purchase price by 10% to 25% per Share” (p. 33)</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
+          <t>“On September 23, 2020, the Company and Company E entered into Company E’s letter of intent” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
-      <c r="T45" s="3" t="n">
-        <v>44096</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>44096</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>44096</v>
+      <c r="T45" s="4" t="n">
+        <v>44097</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>44097</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>44097</v>
       </c>
     </row>
     <row r="46">
@@ -3425,22 +3397,22 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>09/22/2020</t>
+          <t>09/23/2020</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3449,24 +3421,28 @@
       <c r="G46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="2" t="n"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Terms or process</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>After the 09/17 due date, CEO Bhise urged Company H to submit a whole-company proposal and also contacted possible portal buyers. None said it would propose in the near term.</t>
+          <t>Displaced by exclusivity with Company E: Synacor and Canaccord ended other active discussions. CLP’s last position: $1.35–$1.41 (#34) plus a possible 10%–25% increase (#40).</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“None of these parties indicated that they would be submitting a potential proposal in the near term” (p. 34)</t>
+          <t>“As a result of the exclusivity provisions in the letter of intent, the Company and Canaccord Genuity also terminated other active discussions with other parties” (p. 34)</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -3475,14 +3451,14 @@
         </is>
       </c>
       <c r="S46" s="2" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>44096</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>44096</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>44096</v>
+      <c r="T46" s="4" t="n">
+        <v>44097</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>44097</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>44097</v>
       </c>
     </row>
     <row r="47">
@@ -3496,7 +3472,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Company G</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3506,44 +3482,48 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="n"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Would not improve earlier offer</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Executed: the Company entered Company E's LOI, with exclusivity to 10/23/2020, and began diligence and documentation. The Company and Canaccord ended other active discussions.</t>
+          <t>Displaced by exclusivity with Company E. Asked on 09/21–09/22 to raise its software-segment price, G said it could not.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“On September 23, 2020, the Company and Company E entered into Company E’s letter of intent, and began coordination to commence diligence and prepare documentation” (p. 34)</t>
+          <t>“the Company and Canaccord Genuity also terminated other active discussions with other parties relating to a proposed transaction at such time” (p. 34)</t>
         </is>
       </c>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
-      <c r="T47" s="3" t="n">
+      <c r="T47" s="4" t="n">
         <v>44097</v>
       </c>
-      <c r="U47" s="3" t="n">
+      <c r="U47" s="4" t="n">
         <v>44097</v>
       </c>
-      <c r="V47" s="3" t="n">
+      <c r="V47" s="4" t="n">
         <v>44097</v>
       </c>
     </row>
@@ -3553,18 +3533,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/23/2020</t>
+          <t>10/23/2020</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
+          <t>Company E</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3573,38 +3557,36 @@
       <c r="G48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n"/>
+      <c r="M48" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Move to exclusive definitive negotiation with Company E after a non-final round; E (1 financial bidder) admitted and given diligence from September through December. No due date set.</t>
+          <t>Ended: exclusivity with Company E expired under the LOI’s terms; diligence and negotiation with E continued without exclusivity.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“As a result of the exclusivity provisions in the letter of intent, the Company and Canaccord Genuity also terminated other active discussions with other parties” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“On October 23, 2020, the exclusivity period that the Company had agreed upon with Company E expired in accordance with the terms of the executed letter of intent” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
-      <c r="T48" s="3" t="n">
-        <v>44097</v>
-      </c>
-      <c r="U48" s="3" t="n">
-        <v>44097</v>
-      </c>
-      <c r="V48" s="3" t="n">
-        <v>44097</v>
+      <c r="T48" s="4" t="n">
+        <v>44127</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>44127</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>44127</v>
       </c>
     </row>
     <row r="49">
@@ -3613,64 +3595,58 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/23/2020</t>
+          <t>10/27/2020</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CLP (Centre Lane Partners, LLC)</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
       <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Reported: other active discussions ended because of E's exclusivity; CLP was in active price talks (#44). CLP's $1.35-$1.41 was below E's $2.00, but the filing gives exclusivity, not price, as the reason.</t>
+          <t>Round 3: with talks with Company E slowing, the Special Committee has Canaccord re-initiate outreach to parties that had shown interest (unnamed, count unknown); E carried forward in non-exclusive negotiation. No due date set.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“the Company and Canaccord Genuity also terminated other active discussions with other parties relating to a proposed transaction at such time” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="n"/>
+          <t>“considered that the pace of discussions with Company E appeared to be slowing, and requested that Canaccord Genuity re-initiate outreach to various parties which had previously expressed some interest” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="n"/>
-      <c r="T49" s="3" t="n">
-        <v>44097</v>
-      </c>
-      <c r="U49" s="3" t="n">
-        <v>44097</v>
-      </c>
-      <c r="V49" s="3" t="n">
-        <v>44097</v>
+      <c r="T49" s="4" t="n">
+        <v>44131</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>44131</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>44131</v>
       </c>
     </row>
     <row r="50">
@@ -3679,68 +3655,64 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>09/23/2020</t>
+          <t>10/27/2020</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Company G</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
+      <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Other active discussions ended for E's exclusivity. G had just declined to raise its price when asked (#43), so E14 gives 'Would not improve earlier offer'. Segment bidder (Q3).</t>
+          <t>CEO Bhise re-contacts Company H; H says it remains interested and requests updated financial information (whether provided is not stated).</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“the Company and Canaccord Genuity also terminated other active discussions with other parties relating to a proposed transaction at such time” (p. 34)</t>
+          <t>“Company H indicated that it remained interested and requested updated financial information for the Company.” (p. 34)</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S50" s="2" t="n"/>
-      <c r="T50" s="3" t="n">
-        <v>44097</v>
-      </c>
-      <c r="U50" s="3" t="n">
-        <v>44097</v>
-      </c>
-      <c r="V50" s="3" t="n">
-        <v>44097</v>
+      <c r="T50" s="4" t="n">
+        <v>44131</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>44131</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>44131</v>
       </c>
     </row>
     <row r="51">
@@ -3749,32 +3721,32 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>10/23/2020</t>
+          <t>11/02/2020</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
@@ -3785,24 +3757,28 @@
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Ended: Company E's exclusivity expired under the LOI's terms; negotiation with E continued without exclusivity.</t>
+          <t>Company H declines to bid for now: still interested, but cannot submit a proposal while Synacor is pursuing a transaction with another party (Company E).</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“On October 23, 2020, the exclusivity period that the Company had agreed upon with Company E expired in accordance with the terms of the executed letter of intent” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="n"/>
+          <t>“it was unable to submit a proposal at that time given that the Company was separately still pursuing a strategic transaction with another third party.” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="n"/>
-      <c r="T51" s="3" t="n">
-        <v>44127</v>
-      </c>
-      <c r="U51" s="3" t="n">
-        <v>44127</v>
-      </c>
-      <c r="V51" s="3" t="n">
-        <v>44127</v>
+      <c r="T51" s="4" t="n">
+        <v>44137</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>44137</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>44137</v>
       </c>
     </row>
     <row r="52">
@@ -3811,58 +3787,60 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>10/27/2020</t>
+          <t>11/19/2020</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n"/>
+          <t>Company I</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>With talks with Company E slowing, the Special Committee asks Canaccord to re-initiate outreach to parties that had shown interest, while E negotiations continue. Reopens competition inside round 2 (alternative round boundary, Q1).</t>
+          <t>Mutual NDA with mutual standstill with Company I, a publicly-traded media company interested in the portal and advertising business only; I then began diligence. Enters.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“requested that Canaccord Genuity re-initiate outreach to various parties which had previously expressed some interest in a transaction with the Company” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“On November 19, 2020, the Company entered into a mutual non-disclosure agreement with a publicly-traded media company (“Company I”)” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
-      <c r="T52" s="3" t="n">
-        <v>44131</v>
-      </c>
-      <c r="U52" s="3" t="n">
-        <v>44131</v>
-      </c>
-      <c r="V52" s="3" t="n">
-        <v>44131</v>
+      <c r="T52" s="4" t="n">
+        <v>44154</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>44154</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>44154</v>
       </c>
     </row>
     <row r="53">
@@ -3871,12 +3849,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>10/27/2020</t>
+          <t>12/08/2020</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>Company I</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3886,20 +3864,32 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M53" s="2" t="n">
         <v>1</v>
       </c>
@@ -3907,24 +3897,24 @@
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Bhise re-contacts Company H; H remains interested and asks for updated financial information on the Company (whether provided is not stated).</t>
+          <t>No conditions reported. Non-binding LOI to buy only the portal and advertising business; price not disclosed. Reported to the Board the same day.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“Company H indicated that it remained interested and requested updated financial information for the Company” (p. 34)</t>
+          <t>“On December 8, 2020, Company I submitted a non-binding letter of intent to acquire solely the Company’s portal and advertising business.” (p. 34)</t>
         </is>
       </c>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
-      <c r="T53" s="3" t="n">
-        <v>44131</v>
-      </c>
-      <c r="U53" s="3" t="n">
-        <v>44131</v>
-      </c>
-      <c r="V53" s="3" t="n">
-        <v>44131</v>
+      <c r="T53" s="4" t="n">
+        <v>44173</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>44173</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>44173</v>
       </c>
     </row>
     <row r="54">
@@ -3933,61 +3923,57 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/02/2020</t>
+          <t>after 12/08/2020</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>Portal and advertising prospects (Bhise outreach)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Company H will not submit a proposal 'at that time' while the Company is still pursuing another party (E), though still interested. Not an exit: H had not entered.</t>
+          <t>Count: unknown. CEO Bhise again contacts parties possibly interested in the portal and advertising business; none could submit a proposal in the near term. None entered.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>“it was unable to submit a proposal at that time given that the Company was separately still pursuing a strategic transaction with another third party” (p. 34)</t>
+          <t>“Thereafter, Mr. Bhise again commenced outreach with various parties who may have an interest in an acquisition of the Company’s portal and advertising business.” (p. 34)</t>
         </is>
       </c>
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
-      <c r="T54" s="3" t="n">
-        <v>44137</v>
-      </c>
-      <c r="U54" s="3" t="n">
-        <v>44137</v>
-      </c>
-      <c r="V54" s="3" t="n">
-        <v>44137</v>
-      </c>
+      <c r="T54" s="4" t="n">
+        <v>44173</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>44173</v>
+      </c>
+      <c r="V54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3995,35 +3981,51 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/19/2020</t>
+          <t>12/14/2020</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Company I</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="n"/>
-      <c r="L55" s="2" t="n"/>
+      <c r="I55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="n">
         <v>1</v>
       </c>
@@ -4031,28 +4033,28 @@
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Mutual NDA with standstills for both sides with Company I, a publicly-traded media company interested in the portal and advertising business; I then began diligence. Entry as a segment buyer (Q3).</t>
+          <t>Heavy: needs standstill waiver, E-nominated CEO and new CFO, three board seats, poison pill. Tender offer at $2.00 per share for 35% of shares only; E drops interest in the $2.00 whole-company deal.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>“On November 19, 2020, the Company entered into a mutual non-disclosure agreement with a publicly-traded media company” (p. 34)</t>
+          <t>“so that Company E could commence a tender offer at a purchase price of $2.00 per Share for 35% of the outstanding Shares.” (p. 34)</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S55" s="2" t="n"/>
-      <c r="T55" s="3" t="n">
-        <v>44154</v>
-      </c>
-      <c r="U55" s="3" t="n">
-        <v>44154</v>
-      </c>
-      <c r="V55" s="3" t="n">
-        <v>44154</v>
+      <c r="T55" s="4" t="n">
+        <v>44179</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>44179</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>44179</v>
       </c>
     </row>
     <row r="56">
@@ -4061,47 +4063,35 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>12/08/2020</t>
+          <t>12/18/2020–12/21/2020</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Company I</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n">
         <v>1</v>
       </c>
@@ -4109,28 +4099,28 @@
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>No condition, financing or price reported. Non-binding LOI for solely the portal and advertising business. Bhise then re-canvassed other portal buyers; none could propose in the near term.</t>
+          <t>Canaccord re-contacts CLP at Synacor’s direction; CLP indicates it may have continuing interest and would consider re-engaging, then speeds up its diligence through late December and January.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>“On December 8, 2020, Company I submitted a non-binding letter of intent to acquire solely the Company’s portal and advertising business” (p. 34)</t>
+          <t>“Each of CLP and Company H preliminarily indicated they may have continuing interest and would consider re-engaging on a proposed transaction.” (p. 35)</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S56" s="2" t="n"/>
-      <c r="T56" s="3" t="n">
-        <v>44173</v>
-      </c>
-      <c r="U56" s="3" t="n">
-        <v>44173</v>
-      </c>
-      <c r="V56" s="3" t="n">
-        <v>44173</v>
+      <c r="T56" s="4" t="n">
+        <v>44184</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>44183</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>44186</v>
       </c>
     </row>
     <row r="57">
@@ -4139,51 +4129,35 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>12/14/2020</t>
+          <t>12/18/2020–12/21/2020</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n">
         <v>1</v>
       </c>
@@ -4191,24 +4165,28 @@
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Heavy: needs standstill waiver, new CEO (E's nominee) and CFO, three Board seats and a poison pill. Tender offer for 35% of shares at $2.00 per share (minority stake); cash not stated.</t>
+          <t>Canaccord re-contacts Company H at Synacor’s direction; H preliminarily indicates it may have continuing interest and would consider re-engaging. Still no NDA or proposal reported.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>“so that Company E could commence a tender offer at a purchase price of $2.00 per Share for 35% of the outstanding Shares” (p. 34)</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="n"/>
+          <t>“Between December 18 and December 21, 2020, at the direction of the Company, Canaccord Genuity engaged in further outreach to CLP, Company G and Company H” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="n"/>
-      <c r="T57" s="3" t="n">
-        <v>44179</v>
-      </c>
-      <c r="U57" s="3" t="n">
-        <v>44179</v>
-      </c>
-      <c r="V57" s="3" t="n">
-        <v>44179</v>
+      <c r="T57" s="4" t="n">
+        <v>44184</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>44183</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>44186</v>
       </c>
     </row>
     <row r="58">
@@ -4217,12 +4195,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>12/14/2020</t>
+          <t>12/18/2020–12/21/2020</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>Company G</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4239,10 +4217,10 @@
         <v>3</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
@@ -4253,24 +4231,24 @@
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Company E drops its $2.00 whole-company proposal (#40) but stays in with the partial tender (#56). Not an exit: E's participation continues to 01/04/2021 (#66).</t>
+          <t>Company G, re-contacted by Canaccord, says it would not go above its earlier software-segment price (#30); it does not re-enter. Reconfirmed to the Committee on 12/30/2020.</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>“Company E advised the Company that it no longer had interest in its prior proposed transaction structure which included a purchase price of $2.00 per Share for 100%” (p. 35)</t>
+          <t>“Company G indicated it would not be interested at a higher price than it previously communicated for the Company’s software and services business.” (p. 35)</t>
         </is>
       </c>
       <c r="R58" s="2" t="n"/>
       <c r="S58" s="2" t="n"/>
-      <c r="T58" s="3" t="n">
-        <v>44179</v>
-      </c>
-      <c r="U58" s="3" t="n">
-        <v>44179</v>
-      </c>
-      <c r="V58" s="3" t="n">
-        <v>44179</v>
+      <c r="T58" s="4" t="n">
+        <v>44184</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>44183</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>44186</v>
       </c>
     </row>
     <row r="59">
@@ -4279,54 +4257,72 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>12/18/2020-12/21/2020</t>
+          <t>12/29/2020</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
+          <t>Company I</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="n"/>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="n"/>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Canaccord re-contacts CLP, Company G and Company H, which had shown 'more serious interest'. CLP and H may re-engage; G not interested above its earlier software-and-services price, so G does not return.</t>
+          <t>No conditions reported. Company I reaffirms interest in the portal and advertising business at a price “only a fraction” of CLP’s, partly contingent on the business’s recent performance; revises #52 as described.</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>“Each of CLP and Company H preliminarily indicated they may have continuing interest and would consider re-engaging on a proposed transaction” (p. 35)</t>
+          <t>“its pricing reflected only a fraction of that being offered pursuant to CLP’s offer, and a portion of such consideration was contingent upon the business’s recent performance.” (p. 35)</t>
         </is>
       </c>
       <c r="R59" s="2" t="n"/>
       <c r="S59" s="2" t="n"/>
-      <c r="T59" s="3" t="n">
-        <v>44184</v>
-      </c>
-      <c r="U59" s="3" t="n">
-        <v>44183</v>
-      </c>
-      <c r="V59" s="3" t="n">
-        <v>44186</v>
+      <c r="T59" s="4" t="n">
+        <v>44194</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>44194</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>44194</v>
       </c>
     </row>
     <row r="60">
@@ -4335,12 +4331,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/18/2020-12/21/2020</t>
+          <t>12/29/2020</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>CLP (Centre Lane Partners, LLC)</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4350,20 +4346,36 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Other-scope bid</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="n"/>
-      <c r="L60" s="2" t="n"/>
+      <c r="I60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="n">
         <v>1</v>
       </c>
@@ -4371,24 +4383,28 @@
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>CLP returns after its 09/23 drop (#48) and 'increased the pace of its diligence review' into January while E's proposal was pending: diligence access for CLP during E's negotiation.</t>
+          <t>Heavy: adds a 20% minimum tender condition and a required public Board recommendation to #54’s governance terms. Still $2.00 per share for 35%; offer to expire by 01/04/2021.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>“Following such time, CLP increased the pace of its diligence review through the end of December and into January” (p. 35)</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="n"/>
+          <t>“further detailing the terms of its proposed tender offer to specify a minimum tender condition of 20% and to also require that the Company Board publicly recommend” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
       <c r="S60" s="2" t="n"/>
-      <c r="T60" s="3" t="n">
-        <v>44184</v>
-      </c>
-      <c r="U60" s="3" t="n">
-        <v>44183</v>
-      </c>
-      <c r="V60" s="3" t="n">
-        <v>44186</v>
+      <c r="T60" s="4" t="n">
+        <v>44194</v>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>44194</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>44194</v>
       </c>
     </row>
     <row r="61">
@@ -4397,76 +4413,58 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/29/2020</t>
+          <t>12/30/2020</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Company I</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
       <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Contingent pricing: part of the consideration depends on the business's recent performance; no other condition stated. Company I reaffirms interest in the portal business at pricing 'only a fraction' of CLP's; no per-share figure.</t>
+          <t>Special Committee decides to let Company E’s partial-tender offer expire and to keep engaging CLP, Company H and Company I, seeking non-binding LOIs from them; notes G will not raise its price.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>“re-affirmed its interest in a potential acquisition of the Company’s portal and advertising business, but its pricing reflected only a fraction of that being offered pursuant to CLP’s offer” (p. 35)</t>
+          <t>“the Company Special Committee determined to let Company E’s offer expire and to continue to engage with CLP, Company H and Company I” (p. 36)</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S61" s="2" t="n"/>
-      <c r="T61" s="3" t="n">
-        <v>44194</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>44194</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>44194</v>
+      <c r="T61" s="4" t="n">
+        <v>44195</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>44195</v>
+      </c>
+      <c r="V61" s="4" t="n">
+        <v>44195</v>
       </c>
     </row>
     <row r="62">
@@ -4475,12 +4473,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>12/29/2020</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4490,24 +4488,24 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Other-scope bid</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>1.88</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4517,7 +4515,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
@@ -4527,24 +4525,24 @@
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Heavy: adds 20% minimum tender condition and a required public Board recommendation to #56's governance demands. Still a 35% tender at $2.00 per share; E says the proposal expires by 01/04/2021.</t>
+          <t>Not contingent on debt financing; CLP “prepared to” fund via equity commitment; diligence still to come. Non-binding LOI: two-step tender offer and merger for 100% at $1.88 per share in cash.</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>“further detailing the terms of its proposed tender offer to specify a minimum tender condition of 20% and to also require that the Company Board publicly recommend” (p. 35)</t>
+          <t>“with a purchase price of $1.88 per Share in cash. The letter of intent indicated that if necessary, CLP would be prepared to fund the entire acquisition amount” (p. 36)</t>
         </is>
       </c>
       <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
-      <c r="T62" s="3" t="n">
-        <v>44194</v>
-      </c>
-      <c r="U62" s="3" t="n">
-        <v>44194</v>
-      </c>
-      <c r="V62" s="3" t="n">
-        <v>44194</v>
+      <c r="T62" s="4" t="n">
+        <v>44200</v>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>44200</v>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="63">
@@ -4553,54 +4551,68 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>12/30/2020</t>
+          <t>by 01/04/2021</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n"/>
+          <t>Company I</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="3" t="n"/>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="n"/>
+      <c r="M63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Special Committee lets Company E's partial tender offer lapse (control transfer without a premium for all holders) and continues with CLP, Company H and Company I. Rejection, not an exit: E is asked again on 01/04 (#65).</t>
+          <t>Inferred: asked for an LOI on 12/30/2020 (#60) and submitted none; on 01/04/2021 Canaccord listed only Company E and Company H as other parties still interested, so I was out by then.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>“the Company Special Committee determined to let Company E’s offer expire and to continue to engage with CLP, Company H and Company I” (p. 36)</t>
+          <t>“Canaccord Genuity reported that at such time, only Company E (with respect to its proposed partial tender offer proposal) and Company H remained as other parties interested” (p. 36)</t>
         </is>
       </c>
       <c r="R63" s="2" t="n"/>
       <c r="S63" s="2" t="n"/>
-      <c r="T63" s="3" t="n">
+      <c r="T63" s="4" t="n">
+        <v>44200</v>
+      </c>
+      <c r="U63" s="4" t="n">
         <v>44195</v>
       </c>
-      <c r="U63" s="3" t="n">
-        <v>44195</v>
-      </c>
-      <c r="V63" s="3" t="n">
-        <v>44195</v>
+      <c r="V63" s="4" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="64">
@@ -4609,18 +4621,18 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>12/30/2020</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
+          <t>Synacor</t>
         </is>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
@@ -4629,8 +4641,8 @@
       <c r="G64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
+      <c r="H64" s="3" t="n"/>
+      <c r="I64" s="3" t="n"/>
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
@@ -4639,28 +4651,24 @@
       <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Committee selects CLP, Company H and Company I (I for the portal business only) and has Canaccord and management seek non-binding LOIs; no due date. H enters by this admission. E stays outside, still being received.</t>
+          <t>Price request: Special Committee has Canaccord seek to maximize offers from CLP and Company E and obtain a written offer from Company H.</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>“directing Canaccord Genuity and the Company’s management to continue to seek non-binding letters of intent from such parties” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q9</t>
-        </is>
-      </c>
+          <t>“directed Canaccord Genuity to engage in outreach to seek to maximize offers from each of CLP and Company E and to receive a written offer from Company H.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="n"/>
       <c r="S64" s="2" t="n"/>
-      <c r="T64" s="3" t="n">
-        <v>44195</v>
-      </c>
-      <c r="U64" s="3" t="n">
-        <v>44195</v>
-      </c>
-      <c r="V64" s="3" t="n">
-        <v>44195</v>
+      <c r="T64" s="4" t="n">
+        <v>44200</v>
+      </c>
+      <c r="U64" s="4" t="n">
+        <v>44200</v>
+      </c>
+      <c r="V64" s="4" t="n">
+        <v>44200</v>
       </c>
     </row>
     <row r="65">
@@ -4674,7 +4682,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>CLP (Centre Lane Partners, LLC)</t>
+          <t>Company E</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4684,7 +4692,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
@@ -4693,51 +4701,43 @@
       <c r="G65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H65" s="4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N65" s="2" t="n"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Not contingent on third-party debt and CLP would fund it all with equity if needed, but diligence still open (stepped up into January). Non-binding LOI: tender offer then merger for 100% at $1.88 cash; answers #63.</t>
+          <t>Asked by Canaccord to return to a 100% acquisition, Company E declined; its partial tender-offer proposal lapsed after 01/04/2021. It had dropped the $2.00 whole-company structure on 12/14/2020 (#54).</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>“with a purchase price of $1.88 per Share in cash” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="n"/>
+          <t>“Company E declined to do so and indicated that its tender offer proposal would no longer be available following January 4, 2021.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
       <c r="S65" s="2" t="n"/>
-      <c r="T65" s="3" t="n">
+      <c r="T65" s="4" t="n">
         <v>44200</v>
       </c>
-      <c r="U65" s="3" t="n">
+      <c r="U65" s="4" t="n">
         <v>44200</v>
       </c>
-      <c r="V65" s="3" t="n">
+      <c r="V65" s="4" t="n">
         <v>44200</v>
       </c>
     </row>
@@ -4747,12 +4747,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/05/2021</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
+          <t>Synacor</t>
         </is>
       </c>
       <c r="D66" s="2" t="n"/>
@@ -4767,8 +4767,8 @@
       <c r="G66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="n"/>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
@@ -4777,24 +4777,24 @@
       <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Price requests: the Committee has Canaccord seek higher offers from CLP and Company E and a written offer from Company H; Canaccord reports only E (partial offer) and H remain besides CLP. On 01/05 the Company told CLP price was still open.</t>
+          <t>Price request: Canaccord tells CLP the Committee wants a higher price; Synacor sends CLP a revised LOI leaving price open and adding customary public-company deal terms.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>“directed Canaccord Genuity to engage in outreach to seek to maximize offers from each of CLP and Company E and to receive a written offer from Company H” (p. 36)</t>
+          <t>“Later that day, the Company sent a revised letter of intent to CLP, noting that the price per Share to be paid in the transaction was still an open issue” (p. 36)</t>
         </is>
       </c>
       <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
-      <c r="T66" s="3" t="n">
-        <v>44200</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>44200</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>44200</v>
+      <c r="T66" s="4" t="n">
+        <v>44201</v>
+      </c>
+      <c r="U66" s="4" t="n">
+        <v>44201</v>
+      </c>
+      <c r="V66" s="4" t="n">
+        <v>44201</v>
       </c>
     </row>
     <row r="67">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>by 01/06/2021</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Company E</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
@@ -4827,40 +4827,52 @@
       <c r="G67" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="n"/>
+      <c r="H67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>Value below earlier offer</t>
-        </is>
-      </c>
+      <c r="N67" s="2" t="n"/>
       <c r="O67" s="2" t="n"/>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Asked to re-engage on 100% of the Company, E declined and its partial tender offer lapsed after 01/04/2021. Having dropped its $2.00 whole-company price (#57), E values 100% below $2.00.</t>
+          <t>Requested a 30-day exclusivity period for diligence. CLP raises its LOI price from $1.88 (#61) to $2.00 per share, same cash structure; reported by Canaccord to the 01/06/2021 Committee meeting.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>“Company E declined to do so and indicated that its tender offer proposal would no longer be available following January 4, 2021” (p. 36)</t>
+          <t>“Canaccord Genuity reported that CLP agreed to increase its offer to $2.00 per Share and had also requested a 30-day period of exclusivity.” (p. 36)</t>
         </is>
       </c>
       <c r="R67" s="2" t="n"/>
       <c r="S67" s="2" t="n"/>
-      <c r="T67" s="3" t="n">
-        <v>44200</v>
-      </c>
-      <c r="U67" s="3" t="n">
-        <v>44200</v>
-      </c>
-      <c r="V67" s="3" t="n">
-        <v>44200</v>
+      <c r="T67" s="4" t="n">
+        <v>44201</v>
+      </c>
+      <c r="U67" s="4" t="n">
+        <v>44201</v>
+      </c>
+      <c r="V67" s="4" t="n">
+        <v>44202</v>
       </c>
     </row>
     <row r="68">
@@ -4884,7 +4896,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
@@ -4893,27 +4905,11 @@
       <c r="G68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n">
         <v>1</v>
       </c>
@@ -4921,23 +4917,23 @@
       <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Heavy: CLP asks for a 30-day exclusivity period. Raises #64 to $2.00 cash after the 01/05 request for a higher price; reported at the 01/06 Committee meeting. Equity-funded per #64.</t>
+          <t>Requested: CLP asks for 30 days of exclusivity with its $2.00 offer. Whether the LOI executed on 01/07/2021 granted it is not stated.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>“Canaccord Genuity reported that CLP agreed to increase its offer to $2.00 per Share and had also requested a 30-day period of exclusivity” (p. 36)</t>
+          <t>“CLP agreed to increase its offer to $2.00 per Share and had also requested a 30-day period of exclusivity” (p. 36)</t>
         </is>
       </c>
       <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
-      <c r="T68" s="3" t="n">
+      <c r="T68" s="4" t="n">
         <v>44201</v>
       </c>
-      <c r="U68" s="3" t="n">
+      <c r="U68" s="4" t="n">
         <v>44201</v>
       </c>
-      <c r="V68" s="3" t="n">
+      <c r="V68" s="4" t="n">
         <v>44202</v>
       </c>
     </row>
@@ -4947,22 +4943,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>by 01/06/2021</t>
+          <t>01/06/2021</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CLP (Centre Lane Partners, LLC)</t>
+          <t>Company H</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -4971,8 +4967,8 @@
       <c r="G69" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
       <c r="J69" s="2" t="n"/>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
@@ -4983,23 +4979,27 @@
       <c r="O69" s="2" t="n"/>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>Requested: CLP asks for 30 days of exclusivity. Execution is not reported; the LOI signed 01/07 (#72) is not said to include it.</t>
+          <t>Company H still gives no indication whether or when it would submit a formal LOI; the Committee proceeds with CLP alone. Last mention of H.</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>“had also requested a 30-day period of exclusivity” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="n"/>
+          <t>“Company H continued to provide no indication if or when it would be willing to submit a formal letter of intent.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S69" s="2" t="n"/>
-      <c r="T69" s="3" t="n">
-        <v>44201</v>
-      </c>
-      <c r="U69" s="3" t="n">
-        <v>44201</v>
-      </c>
-      <c r="V69" s="3" t="n">
+      <c r="T69" s="4" t="n">
+        <v>44202</v>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>44202</v>
+      </c>
+      <c r="V69" s="4" t="n">
         <v>44202</v>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
+          <t>Synacor</t>
         </is>
       </c>
       <c r="D70" s="2" t="n"/>
@@ -5029,8 +5029,8 @@
       <c r="G70" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
@@ -5039,12 +5039,12 @@
       <c r="O70" s="2" t="n"/>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Committee unanimously decides to sign a non-binding LOI with CLP and begin diligence and definitive-agreement negotiation: definitive negotiation with the selected bidder after a non-final round. CLP (1 financial bidder) admitted.</t>
+          <t>Round 4: Special Committee unanimously decides to enter CLP’s non-binding LOI at $2.00 and begin diligence and definitive-agreement negotiation with CLP alone; Rendino stays recused.</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>“it unanimously determined to enter into the non-binding letter of intent with CLP and commence diligence and negotiation of a definitive agreement” (p. 36)</t>
+          <t>“it unanimously determined to enter into the non-binding letter of intent with CLP and commence diligence and negotiation of a definitive agreement.” (p. 36)</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -5053,13 +5053,13 @@
         </is>
       </c>
       <c r="S70" s="2" t="n"/>
-      <c r="T70" s="3" t="n">
+      <c r="T70" s="4" t="n">
         <v>44202</v>
       </c>
-      <c r="U70" s="3" t="n">
+      <c r="U70" s="4" t="n">
         <v>44202</v>
       </c>
-      <c r="V70" s="3" t="n">
+      <c r="V70" s="4" t="n">
         <v>44202</v>
       </c>
     </row>
@@ -5069,70 +5069,60 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>by 01/06/2021</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Company H</t>
+          <t>CLP (Centre Lane Partners, LLC)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
       <c r="J71" s="2" t="n"/>
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Inferred: the complete advancing set on 01/06 is CLP alone. Company H had given 'no indication if or when' it would submit a formal LOI. H entered by admission on 12/30 (#63).</t>
+          <t>Synacor and CLP execute the non-binding LOI for 100% at $2.00 per share; kick-off diligence call follows. Ref: $1.49 close 01/07/2021 (per p. 37).</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>“Company H continued to provide no indication if or when it would be willing to submit a formal letter of intent” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+          <t>“On January 7, 2021, the Company and CLP executed the non-binding letter of intent.” (p. 36)</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="n"/>
       <c r="S71" s="2" t="n"/>
-      <c r="T71" s="3" t="n">
-        <v>44202</v>
-      </c>
-      <c r="U71" s="2" t="n"/>
-      <c r="V71" s="3" t="n">
-        <v>44202</v>
+      <c r="T71" s="4" t="n">
+        <v>44203</v>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>44203</v>
+      </c>
+      <c r="V71" s="4" t="n">
+        <v>44203</v>
       </c>
     </row>
     <row r="72">
@@ -5141,70 +5131,54 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>by 01/06/2021</t>
+          <t>01/21/2021</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Company I</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Thompson Hine LLP</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
       <c r="J72" s="2" t="n"/>
       <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="n"/>
-      <c r="M72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>Inferred: only CLP advanced on 01/06. Company I (portal only) was last reported interested on 12/30; on 01/04 Canaccord named only E and H as other interested parties, so I may have lapsed earlier or been outside that count.</t>
+          <t>CLP’s outside legal counsel, first shown acting when delivering CLP’s initial draft merger agreement to Gunderson.</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>“only Company E (with respect to its proposed partial tender offer proposal) and Company H remained as other parties interested in engaging on a transaction” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q9</t>
-        </is>
-      </c>
+          <t>“On January 21, 2021, outside counsel to CLP, Thompson Hine LLP (“Thompson”), delivered an initial draft of the Merger Agreement to Gunderson.” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
-      <c r="T72" s="3" t="n">
-        <v>44202</v>
-      </c>
-      <c r="U72" s="2" t="n"/>
-      <c r="V72" s="3" t="n">
-        <v>44202</v>
+      <c r="T72" s="4" t="n">
+        <v>44217</v>
+      </c>
+      <c r="U72" s="4" t="n">
+        <v>44217</v>
+      </c>
+      <c r="V72" s="4" t="n">
+        <v>44217</v>
       </c>
     </row>
     <row r="73">
@@ -5213,7 +5187,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/21/2021</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5228,7 +5202,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid reaffirmed</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
@@ -5237,11 +5211,27 @@
       <c r="G73" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
-      <c r="J73" s="2" t="n"/>
-      <c r="K73" s="2" t="n"/>
-      <c r="L73" s="2" t="n"/>
+      <c r="H73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M73" s="2" t="n">
         <v>1</v>
       </c>
@@ -5249,24 +5239,28 @@
       <c r="O73" s="2" t="n"/>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>The Company and CLP execute the non-binding LOI for 100% at $2.00 per share (confirmed 01/08 to Rendino); exclusivity terms not stated. A kick-off diligence call and weeks of diligence followed; Rendino stayed recused.</t>
+          <t>Heavy: diligence continuing within CLP’s requested 30-day period; equity commitment not yet signed. CLP delivers its own full draft merger agreement for its standing $2.00 offer (carried from #66).</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>“On January 7, 2021, the Company and CLP executed the non-binding letter of intent” (p. 36)</t>
-        </is>
-      </c>
-      <c r="R73" s="2" t="n"/>
+          <t>“On January 21, 2021, outside counsel to CLP, Thompson Hine LLP (“Thompson”), delivered an initial draft of the Merger Agreement to Gunderson.” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
       <c r="S73" s="2" t="n"/>
-      <c r="T73" s="3" t="n">
-        <v>44203</v>
-      </c>
-      <c r="U73" s="3" t="n">
-        <v>44203</v>
-      </c>
-      <c r="V73" s="3" t="n">
-        <v>44203</v>
+      <c r="T73" s="4" t="n">
+        <v>44217</v>
+      </c>
+      <c r="U73" s="4" t="n">
+        <v>44217</v>
+      </c>
+      <c r="V73" s="4" t="n">
+        <v>44217</v>
       </c>
     </row>
     <row r="74">
@@ -5275,18 +5269,18 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/21/2021</t>
+          <t>02/08/2021</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Thompson Hine LLP</t>
+          <t>Synacor</t>
         </is>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
@@ -5295,8 +5289,8 @@
       <c r="G74" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
       <c r="J74" s="2" t="n"/>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
@@ -5305,24 +5299,24 @@
       <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>CLP's outside counsel; delivered CLP's initial draft Merger Agreement to Gunderson.</t>
+          <t>Price requirement: after Synacor’s share price rose in early February, the Board requires $2.20 per share to consider approval; Canaccord relays it and CLP takes it to its investment committee. Ref: $1.49 close 01/07/2021.</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>“On January 21, 2021, outside counsel to CLP, Thompson Hine LLP” (p. 37)</t>
+          <t>“The Company Board discussed and instructed Canaccord Genuity to relay the need for an increase in purchase price to $2.20 per Share to consider approving the proposed Transaction.” (p. 37)</t>
         </is>
       </c>
       <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
-      <c r="T74" s="3" t="n">
-        <v>44217</v>
-      </c>
-      <c r="U74" s="3" t="n">
-        <v>44217</v>
-      </c>
-      <c r="V74" s="3" t="n">
-        <v>44217</v>
+      <c r="T74" s="4" t="n">
+        <v>44235</v>
+      </c>
+      <c r="U74" s="4" t="n">
+        <v>44235</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>44235</v>
       </c>
     </row>
     <row r="75">
@@ -5331,7 +5325,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/21/2021</t>
+          <t>02/09/2021–02/10/2021</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5346,7 +5340,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
@@ -5355,27 +5349,11 @@
       <c r="G75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n">
         <v>1</v>
       </c>
@@ -5383,28 +5361,24 @@
       <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>Diligence still ongoing, no stated condition. CLP's counsel delivers CLP's own initial draft Merger Agreement, supporting its standing $2.00 cash price (carried from #67) after the target moved to finalize with it (Q10).</t>
+          <t>CLP requires Tender and Support Agreements from two significant stockholders (Pacven Walden funds and 180 Degree; about 17.4% of shares) and refuses a reverse termination fee; termination fee negotiated to $3.0 million.</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>“delivered an initial draft of the Merger Agreement to Gunderson” (p. 37)</t>
-        </is>
-      </c>
-      <c r="R75" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
+          <t>“However, CLP was unwilling to agree to a reverse termination fee in favor of the Company, and CLP subsequently required that two significant stockholders enter into Tender” (p. 37)</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="n"/>
       <c r="S75" s="2" t="n"/>
-      <c r="T75" s="3" t="n">
-        <v>44217</v>
-      </c>
-      <c r="U75" s="3" t="n">
-        <v>44217</v>
-      </c>
-      <c r="V75" s="3" t="n">
-        <v>44217</v>
+      <c r="T75" s="4" t="n">
+        <v>44236</v>
+      </c>
+      <c r="U75" s="4" t="n">
+        <v>44236</v>
+      </c>
+      <c r="V75" s="4" t="n">
+        <v>44237</v>
       </c>
     </row>
     <row r="76">
@@ -5413,18 +5387,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>02/08/2021</t>
+          <t>02/10/2021</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n"/>
+          <t>CLP (Centre Lane Partners, LLC)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
@@ -5433,34 +5411,52 @@
       <c r="G76" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="n"/>
-      <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="n"/>
-      <c r="L76" s="2" t="n"/>
-      <c r="M76" s="2" t="n"/>
+      <c r="H76" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N76" s="2" t="n"/>
       <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Price requirement: after the share price rose (Ref: $1.49 close 01/07/2021) and Canaccord's premium advice, the Board requires $2.20 per share to consider approval; Canaccord relays it and CLP will consult its investment committee.</t>
+          <t>Light: conditional only on signing the merger agreement that day and announcing before market open 02/11. Raises $2.00 to $2.20 cash; termination fee up from $3.0m to $3.5m. Ref: $1.95 close 02/10/2021 (p. 26).</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>“instructed Canaccord Genuity to relay the need for an increase in purchase price to $2.20 per Share to consider approving the proposed Transaction” (p. 37)</t>
+          <t>“Later in the day on February 10, 2021, CLP indicated that it would increase the purchase price per Share from $2.00 per Share to $2.20 per Share” (p. 38)</t>
         </is>
       </c>
       <c r="R76" s="2" t="n"/>
       <c r="S76" s="2" t="n"/>
-      <c r="T76" s="3" t="n">
-        <v>44235</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>44235</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>44235</v>
+      <c r="T76" s="4" t="n">
+        <v>44237</v>
+      </c>
+      <c r="U76" s="4" t="n">
+        <v>44237</v>
+      </c>
+      <c r="V76" s="4" t="n">
+        <v>44237</v>
       </c>
     </row>
     <row r="77">
@@ -5484,7 +5480,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
@@ -5493,27 +5489,11 @@
       <c r="G77" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H77" s="4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="n">
         <v>1</v>
       </c>
@@ -5521,23 +5501,23 @@
       <c r="O77" s="2" t="n"/>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Ready to sign: raise conditioned on signing that day and announcing before the 02/11 open; CLP Fund V equity commitment, no financing condition. $2.20 cash; termination fee up from $3.0m to $3.5m; no reverse fee; support agreements required.</t>
+          <t>Merger agreement signed after unanimous Board approval and Canaccord fairness opinion: $2.20 per share in cash by tender offer then §251(h) merger; Tender and Support Agreements and CLP Fund V equity commitment letter executed.</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>“CLP indicated that it would increase the purchase price per Share from $2.00 per Share to $2.20 per Share” (p. 38)</t>
+          <t>“Later that day, the parties executed the Merger Agreement and the Tender and Support Agreements, and CLP Fund V, Parent and Purchaser executed the Equity Commitment Letter.” (p. 38)</t>
         </is>
       </c>
       <c r="R77" s="2" t="n"/>
       <c r="S77" s="2" t="n"/>
-      <c r="T77" s="3" t="n">
+      <c r="T77" s="4" t="n">
         <v>44237</v>
       </c>
-      <c r="U77" s="3" t="n">
+      <c r="U77" s="4" t="n">
         <v>44237</v>
       </c>
-      <c r="V77" s="3" t="n">
+      <c r="V77" s="4" t="n">
         <v>44237</v>
       </c>
     </row>
@@ -5547,122 +5527,60 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>02/10/2021</t>
+          <t>02/11/2021</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CLP (Centre Lane Partners, LLC)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Synacor</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G78" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M78" s="2" t="n"/>
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="2" t="n"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Agreed $2.20 per share in cash: tender offer then DGCL 251(h) merger; $3.5m termination fee; CLP Fund V equity commitment; Tender and Support Agreements with Pacven Walden funds and 180 Degree (about 17.4% of shares). Canaccord fairness opinion.</t>
+          <t>Press release announcing the merger agreement issued before the market opened, with a Form 8-K. No go-shop; no competing proposal reported to the 03/03/2021 filing date.</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>“Later that day, the parties executed the Merger Agreement and the Tender and Support Agreements” (p. 38)</t>
+          <t>“Before the opening of trading on the public markets on February 11, 2021, the Company issued a press release announcing entry into the Merger Agreement” (p. 38)</t>
         </is>
       </c>
       <c r="R78" s="2" t="n"/>
       <c r="S78" s="2" t="n"/>
-      <c r="T78" s="3" t="n">
-        <v>44237</v>
-      </c>
-      <c r="U78" s="3" t="n">
-        <v>44237</v>
-      </c>
-      <c r="V78" s="3" t="n">
-        <v>44237</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/11/2021</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Synacor (target)</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Merger announced</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
-      <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="n"/>
-      <c r="L79" s="2" t="n"/>
-      <c r="M79" s="2" t="n"/>
-      <c r="N79" s="2" t="n"/>
-      <c r="O79" s="2" t="n"/>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>Press release before market open and Form 8-K. Ref: $1.95 close 02/10/2021, last trading day before announcement (p. 4). No go-shop; no-solicitation covenant from signing.</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>“Before the opening of trading on the public markets on February 11, 2021, the Company issued a press release announcing entry into the Merger Agreement” (p. 38)</t>
-        </is>
-      </c>
-      <c r="R79" s="2" t="n"/>
-      <c r="S79" s="2" t="n"/>
-      <c r="T79" s="3" t="n">
+      <c r="T78" s="4" t="n">
         <v>44238</v>
       </c>
-      <c r="U79" s="3" t="n">
+      <c r="U78" s="4" t="n">
         <v>44238</v>
       </c>
-      <c r="V79" s="3" t="n">
+      <c r="V78" s="4" t="n">
         <v>44238</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V79"/>
+  <autoFilter ref="A1:V78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5678,14 +5596,14 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5747,17 +5665,17 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>43228</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Liontree engaged 05/08/2018; outreach to approximately 12 strategic and financial companies (undated start) (#6)</t>
+          <t>Liontree (engaged 05/08/2018) contacts about 12 strategic and financial parties; undated.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1 financial: Company A (carried from round 0, NDA 01/10/2018). About 12 contacted parties, none reported to enter.</t>
+          <t>1 bidder: Company A (Financial), carried from round 0 with its 04/25/2018 IOI outstanding. About 12 contacted parties; none entered.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -5777,12 +5695,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>0 in the round (Company A's two IOIs, #3-#4, preceded the outreach and are round 0)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Company A withdrew 06/20/2018 (#8); outreach produced no IOI; attempt lapsed (Liontree engagement's stated end 12/31/2018).</t>
+          <t>Company A withdrew 06/20/2018; the outreach produced no IOI; process lapsed (restart inferred March 2019).</t>
         </is>
       </c>
     </row>
@@ -5793,17 +5711,17 @@
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>43702</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Canaccord engaged 08/25/2019; outreach to 18 additional parties at the Board's direction (undated start) (#15)</t>
+          <t>Canaccord (engaged 08/25/2019) contacts 18 additional parties at the Board’s direction; undated.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1 strategic: Company C (carried from round 0, NDA March 2019). 18 contacted parties, none entered. Segment buyers in management's portal divestiture, not admitted: Company E (NDA), Company F (IOI, round 0).</t>
+          <t>2 bidders carried from round 0: Company C (Strategic; 08/13/2019 LOI) and Company E (Financial; portal/advertising NDA only); Company F (Strategic) entered by its segment IOI 09/15/2019. 18 contacted parties; none entered.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -5823,12 +5741,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>0 whole-company bids in the round (Company C's LOI #12 preceded it; Company F's portal IOI #17 answered management's divestiture outreach)</t>
+          <t>1: Company F (portal/advertising segment IOI, 09/15/2019). No whole-company bid in the round.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Company C and the Company mutually dropped talks October 2019 (#19); Company F talks failed, undated (#18); lapsed; Company E's NDA closed by process 3 restart (#20).</t>
+          <t>Company C withdrew by mutual agreement October 2019; Company F talks failed (undated); process lapsed, E and F closed at the 07/13/2020 restart.</t>
         </is>
       </c>
     </row>
@@ -5839,17 +5757,17 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>44028</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Canaccord outreach to 37 parties from mid-July 2020, with IOIs requested by 09/17/2020 (#25); management separately contacted 8 portal buyers</t>
+          <t>Synacor directs Canaccord to solicit buyers for the Company and/or software business (37 parties, mid-July–mid-September 2020); management contacts 8 portal parties.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15-17 bidder units entered: Company E (financial, NDA amendment 07/13/2020); CLP (financial, NDA 09/08/2020); 13-14 other outreach NDA signers (type unknown; CLP may be one of the 14); Company G (financial) by its segment bid, possibly also an NDA signer. Company H contacted, not entered.</t>
+          <t>Company E (Financial; entered 07/13/2020); 12–14 other NDA signers (types unknown); CLP (Financial; NDA 09/08/2020); Company G (Financial; entered by segment IOI 09/14/2020). Company H (Strategic) contacted, not entered.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -5869,12 +5787,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3 bidders: Company E ($2.00, #30; revised #40), CLP ($1.35-$1.41, #37; verbal #44), Company G (software and services only, #33)</t>
+          <t>3: Company E ($2.00 09/10; $2.00 revised LOI 09/18), CLP ($1.35–$1.41, 09/17), Company G (software and services segment only, 09/14).</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Company E selected for exclusive negotiation 09/23/2020; CLP and Company G dropped 09/23 (#48-#49); 12-14 NDA signers did not submit (#39).</t>
+          <t>One advanced: exclusivity with Company E 09/23/2020; CLP and G dropped; 11–14 NDA signers did not submit.</t>
         </is>
       </c>
     </row>
@@ -5885,17 +5803,17 @@
       <c r="B5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>44097</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Company E's LOI with exclusivity to 10/23/2020 executed; definitive negotiation with E (#47)</t>
+          <t>Synacor signs Company E’s LOI with exclusivity to 10/23/2020; diligence and definitive-agreement negotiation.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1 financial: Company E. Still being received, not admitted: Company I (portal only; NDA 11/19/2020, LOIs #55, #60); CLP (re-entered 12/18-12/21/2020, #59). Company H contacted, not entered.</t>
+          <t>1 bidder: Company E (Financial).</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5915,12 +5833,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2 bidders: Company E (35% partial tender at $2.00, #56, revised #61; dropped whole-company $2.00, #57); Company I (portal only, #55, #60)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity lapsed 10/23/2020; outreach reopened 10/27; E dropped its whole-company offer 12/14; on 12/30 the Committee let E's partial offer lapse and turned to CLP, H and I (#62).</t>
+          <t>Exclusivity expired 10/23/2020; talks slowed and Synacor re-opened outreach 10/27/2020, carrying E into round 3.</t>
         </is>
       </c>
     </row>
@@ -5931,17 +5849,17 @@
       <c r="B6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>44195</v>
+      <c r="C6" s="4" t="n">
+        <v>44131</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Special Committee selects CLP, Company H and Company I and seeks non-binding LOIs (#63)</t>
+          <t>Special Committee has Canaccord re-initiate outreach to parties that had shown interest, while E talks continue.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3 admitted: CLP (financial), Company H (strategic), Company I (strategic, portal only). Still being received, not admitted: Company E (asked 01/04/2021 to re-engage on 100%).</t>
+          <t>3 bidders: Company E (Financial; carried), Company I (Strategic; portal segment; NDA 11/19/2020), CLP (Financial; re-entered 12/18–12/21/2020). Solicited, not entered: Company H (Strategic). Company G re-contacted, declined to raise.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5961,12 +5879,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1 bidder: CLP ($1.88 on 01/04/2021, #64; $2.00 by 01/06/2021, #67). Company E declined (#66); H and I did not bid.</t>
+          <t>3: CLP ($1.88 01/04/2021; $2.00 by 01/06/2021); Company E (35% tender offer at $2.00, 12/14 and 12/29/2020, other scope); Company I (portal segment, 12/08 and 12/29/2020, other scope).</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>CLP selected 01/06/2021 for LOI and definitive negotiation; Company E withdrew 01/04 (#66); Company H and Company I dropped, inferred, by 01/06 (#70-#71).</t>
+          <t>CLP selected 01/06/2021 for LOI and definitive negotiation; E withdrew 01/04/2021; I did not submit (inferred); H never bid.</t>
         </is>
       </c>
     </row>
@@ -5977,17 +5895,17 @@
       <c r="B7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>44202</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Committee decides to sign an LOI with CLP and begin diligence and definitive negotiation (#69); LOI executed 01/07/2021</t>
+          <t>Special Committee decides to sign CLP’s $2.00 LOI (executed 01/07/2021) and negotiate a definitive agreement.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1 financial: CLP.</t>
+          <t>1 bidder: CLP (Financial).</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -6007,12 +5925,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1 bidder: CLP ($2.00 reaffirmed with its draft Merger Agreement 01/21/2021, #74; $2.20 on 02/10/2021, #76)</t>
+          <t>1: CLP ($2.00 reaffirmed with its draft merger agreement 01/21/2021; $2.20 on 02/10/2021).</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Signing 02/10/2021 at $2.20 per share in cash (#77); announced 02/11/2021.</t>
+          <t>Signing 02/10/2021.</t>
         </is>
       </c>
     </row>
@@ -6028,15 +5946,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -6085,27 +6003,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Is the map right: three processes (2018, 2019, 2020-21), one round in each of processes 1-2, and four rounds in process 3?</t>
+          <t>Process and round map: three processes; process 3 has four rounds (R1 outreach, IOIs due 09/17/2020; R2 exclusive talks with Company E from 09/23/2020; R3 re-opened outreach from 10/27/2020; R4 definitive negotiation with CLP from 01/06/2021). Is this right?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. P3: R1 IOI outreach due 09/17/2020; R2 exclusive negotiation with Company E from 09/23; R3 LOI requests to CLP, H and I from 12/30; R4 definitive negotiation with CLP from 01/06/2021.</t>
+          <t>Keep. Alternatives: merge processes 1 and 2 if the Company B merger-of-equals talks (Oct 2018–Mar 2019) count as sale contacts; open R3 at the 12/18–12/21/2020 outreach or the 12/30/2020 selection; treat the 09/17/2020 best-offer request to E as a new round.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>E5 tests (pp. 30-32). P1 to P2: (a) met, no offer open after Company A withdrew 06/20/2018 (Liontree outreach undated); (b) met; (c) met, Company C NDA March 2019. P2 to P3: (a) met, but Company F's end undated; (b) met, about 8.5-9.5 months with no reported sale contact (October 2019 to 07/13/2020); (c) met, E approach taken up. Gaps of two months or more with no dated acquirer contact: 02/06/2018-04/25/2018 (undated discussions between); 06/20/2018-October 2018 (Company B) or March 2019 (Company C); March 2019-07/30/2019; October 2019-07/13/2020.</t>
+          <t>pp. 30–37. Gaps of two months or more with no reported acquirer contact: 06/20/2018 (Liontree outreach undated) to March 2019; March 2019 to Q3 2019 (07/30/2019 NDA); October 2019 to 07/13/2020. E5, P1→P2: (a) met, A withdrew, no IOI outstanding; (b) met on reading, about 8–9 months but Liontree end undated; (c) met, Company C NDA. P2→P3: (a) met; (b) met, about 8.5–9.5 months; (c) met, E approach taken up plus new outreach.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#6, #9, #15, #20, #25, #47, #51, #63, #69</t>
+          <t>#6, #9, #15, #19, #22, #43, #48, #69</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Most plausible alternative: round 3 opens 10/27/2020, when outreach is re-initiated (#51), moving #52-#62 (H contacts, Company I's NDA and LOIs, E's partial offers, CLP's re-entry) from round 2 to round 3. Merging processes has no supported basis given the gaps.</t>
+          <t>Merging P1/P2 deletes #9 and renumbers process 2 rows; a later R3 start moves #48, #49, #50, #51, #52 into R2; a best-offer round would move #37, #38, #39, #40 into a new R2 and make #37 Formal.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -6118,27 +6036,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Should the Company B 'merger of equals' (Oct 2018-Mar 2019) and the Company D deal (IOI 07/01/2019; merger agreement 02/11/2020; terminated 06/29/2020) be treated as sale processes?</t>
+          <t>Company C’s October 2019 exit was “mutually agreed”. Withdrew or Dropped by target?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>No. Synacor was the proposer in both: it delivered the MOE letter to Company B and proposed to acquire Company D. E1 excludes a target's attempt to buy another company. Both are recorded only in Deal facts.</t>
+          <t>Withdrew, reason Not stated: C agreed it would not pursue a transaction.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>pp. 30-31: 'the Company delivered a non-binding indication of interest letter to Company B proposing a “merger of equals”'; 'the Company submitted a non-binding indication of interest to acquire a publicly-traded software company (“Company D”)'. The D terms were all stock with a 'combined company ownership split'.</t>
+          <t>p. 31. Neither side is said to have initiated, and no reason is given beyond “further discussion” and Canaccord’s review.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#9, #20</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If Company B counts as a sale contact, the P1-P2 gap shrinks to about 3.3-4.4 months (still a break). If the D deal counts as a sale of Synacor, a signed-and-terminated process (Jan-Jun 2020) is added between P2 and P3, and the P3 restart follows its reported end.</t>
+          <t>Dropped by target would say Synacor, not C, ended the only whole-company bid in process 2.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -6151,27 +6069,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>How should the segment-only bidders (portal: Company E 2019, F, I; software and services: G) and management's portal divestiture outreach be placed?</t>
+          <t>How many of the 14 stated NDA signers are recorded in the cohort, and how many did not submit IOIs?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Keep them as participants with Other-scope bid rows, entries and exits, so live-unit counts include them while whole-company prices exclude them. Put the 2019 portal outreach, E's 2019 NDA and F's IOI in process 2, round 0: they answered a divestiture effort, not Canaccord's whole-company round.</t>
+          <t>Cohort Count 12–14 and non-submitters 11–14, left blank. CLP (NDA 09/08/2020, inside the outreach window) is very likely one of the 14, which would make it 13 and 12–13.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>pp. 31-36: the Board was 'evaluating divesting its portal and advertising business'; G's and I's bids gave no per-share price, only fractions of rival valuations; segment and whole-company bids therefore sit on mixed bases.</t>
+          <t>p. 32. The filing gives 14 NDAs “of the parties contacted” (37, other than Companies A–D) but never says CLP, Company E (amended NDA) or Company G (no NDA reported) were among them; Company H, established as contacted, may be a signer.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#11, #13, #17, #18, #27, #33, #49, #54, #55, #60, #71</t>
+          <t>#24, #27, #36</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Excluding segment buyers would remove E (2019), F, G and I, leaving process 2 with Company C alone and round 3 of process 3 with CLP and H. Placing F's IOI in process 2, round 1 would give that round one bid.</t>
+          <t>Exact counts would change the live-bidder count in round 1 by up to three and the size of the Did not submit exit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -6184,27 +6102,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Which exit labels fit Company C (talks 'mutually agreed' to end, October 2019) and Company F ('unable to agree on terms', undated)?</t>
+          <t>Deadline outcome, process 3 round 1 (IOIs due 09/17/2020): Enforced, or Passed without action?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Withdrew for both, with Exit reason Not stated (C) and Terms or process (F). The filing names neither side as ending talks, so no target-side exclusion is shown.</t>
+          <t>Enforced: the Special Committee evaluated the three submissions in hand (E, G, CLP) on 09/21, pressed G and CLP to improve, and signed exclusivity with E on 09/23.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>p. 31: 'the Company and Company C mutually agreed in October 2019 not to pursue a transaction'; 'the parties were ultimately unable to agree on terms for the transaction'.</t>
+          <t>pp. 32–34. After the due date CEO Bhise still urged Company H (09/22) to submit, which could read as bidding simply continuing; but no new date was set and no late bid arrived.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#18, #19</t>
+          <t>#26, #35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target would attribute the decision to Synacor. Neither label reveals a price; only whose decision ended participation changes.</t>
+          <t>Passed without action would signal a soft deadline; no row changes, only the Rounds sheet outcome.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -6217,27 +6135,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>How do the 14 outreach NDA signers relate to CLP, Company G and Company H, and how many failed to submit by 09/17/2020?</t>
+          <t>Did Company H ever enter?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Treat CLP as possibly one of the 14 (cohort 13-14 besides CLP) and non-submitters as 12-14 (G may be a member). Leave Counts blank with bounds in the Notes. The auction screen is Met either way.</t>
+          <t>No: record H only through Other material event rows. No NDA or bid is reported, and being courted is contact, not admission.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>p. 32: 'Of the parties contacted, 14 parties executed non-disclosure agreements'. The filing never places CLP or G in the outreach, and says H was reached in it but reports no NDA for H.</t>
+          <t>pp. 33–36. H was reached through Canaccord’s outreach and may be one of the 14 NDA signers. The 12/30/2020 decision to “continue to engage with CLP, Company H and Company I” could be read as admitting H to an LOI stage.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#28, #29, #39</t>
+          <t>#32, #41, #49, #50, #56, #60, #68</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>If CLP and G are both members, process-3 NDA entrants are 15 (14 plus Company E) and non-submitters 12. If neither is, entrants are 16 plus G, with 14 non-submitters. Round 1's live count shifts accordingly.</t>
+          <t>If H entered on 12/30, round 3 had one more live strategic bidder, and H needs an exit, Did not submit (inferred) by 01/06/2021.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -6250,27 +6168,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Was the Company's 09/17/2020 request that Company E give its 'best offer on purchase price' a best-and-final solicitation that opens a new round and makes E's 09/18 reply Formal?</t>
+          <t>Is CLP’s 09/22/2020 verbal statement (would consider raising its price 10%–25%, subject to further diligence) a Bid?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>No. It was a request to one bidder to improve its price inside a counter-LOI. That is bargaining within round 1 (E6), so E's 09/18 $2.00 reply stays Informal.</t>
+          <t>No: record it as a valuation statement without an offer (Other material event), price cells blank.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>p. 33: 'the Company submitted a revised letter of intent to Company E, which included a request for Company E to provide its best offer on purchase price'. No other bidder got a comparable request, and bargaining continued with CLP and G.</t>
+          <t>p. 33. “Would consider” is not a proposal, and the base of the percentage (low or high end of $1.35–$1.41) is unstated; the implied $1.49–$1.76 is only arithmetic.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#36, #40</t>
+          <t>#40</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>A new round would open 09/17 with Company E alone, E's 09/18 bid would become Formal (E11 item 2), and later process-3 round numbers would rise by one.</t>
+          <t>As a Bid it would add an Informal, Heavy CLP bid at about $1.49–$1.76 in round 1, raising CLP’s last price before its exit.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -6283,27 +6201,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>What was the outcome of the 09/17/2020 IOI due date in process 3, round 1?</t>
+          <t>Did CLP really leave on 09/23/2020 and re-enter on 12/18–12/21/2020?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Enforced. The Company acted on the three bids in hand: it asked Company E for its best price (09/17), asked CLP and G to raise (09/21-22) and gave E exclusivity on 09/23.</t>
+          <t>Keep the drop and the re-entry. The filing says Synacor ended “other active discussions” because of E’s exclusivity, and CLP was re-contacted and said it “would consider re-engaging”.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>pp. 33-34. On 09/22 Bhise still urged Company H, which had not bid, to submit a proposal. H submitted none.</t>
+          <t>pp. 34–35. That CLP afterwards “increased the pace of its diligence review” could suggest it kept doing diligence throughout.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#38, #45</t>
+          <t>#45, #55</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Weighting the post-deadline invitation to H would make the outcome 'Passed without action'. No late bid arrived, so 'Late bids accepted' does not apply.</t>
+          <t>If CLP never left, it was live alongside E through rounds 2–3 and the drop and re-entry rows go.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -6316,27 +6234,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Is CLP's 09/22/2020 verbal statement that it 'would consider' raising its price by 10%-25%, subject to diligence, a Bid?</t>
+          <t>When did Company E leave: 12/14/2020, when it dropped the $2.00 whole-company deal for a 35% tender offer, or 01/04/2021, when it declined to return to 100% and its partial offer lapsed?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Yes: record it as an Informal Bid with Heavy conditions and blank price cells. It communicated a higher price range relative to #37, but the filing gives no per-share figure.</t>
+          <t>Use 01/04/2021 (Withdrew, reason Not stated): E stayed in negotiation with a live, if partial, proposal, and Synacor still asked it to re-engage on 100% on 01/04.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>p. 33: 'CLP provided a verbal indication that, subject to further diligence, it would consider increasing its purchase price by 10% to 25% per Share'. Arithmetic on $1.35-$1.41 implies about $1.49-$1.76 (not stated).</t>
+          <t>pp. 34–36. On 12/14 E “no longer had interest in its prior proposed transaction structure”; on 12/30 the Committee decided to let E’s offer expire.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#44</t>
+          <t>#54, #59, #64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>As an Other material event (a valuation statement without an offer), CLP would have one round-1 bid ($1.35-$1.41). Filling the implied prices would add a range the filing never states.</t>
+          <t>A 12/14 exit would remove E as a whole-company rival for all of round 3, leaving its later rows as proposals from a party that had left.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -6349,66 +6267,33 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Did Company H and Company I stay live after 12/30/2020, and how did they leave?</t>
+          <t>Bid reaffirmed: does CLP’s 01/21/2021 delivery of its own draft merger agreement confirm its $2.00 offer as Formal?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>H enters on 12/30 by admission: the Committee continued with CLP, H and I and sought their LOIs. Both H and I are inferred Dropped by target by 01/06/2021, when only CLP advanced.</t>
+          <t>Yes: record a Bid reaffirmed at $2.00 carried from the 01/06 bid, Formal, Heavy. It is the bidder’s own full proposed agreement after Synacor moved to finalize with it.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>pp. 35-36. On 01/04/2021 Canaccord listed only E and H as other interested parties (I not named). On 01/06, H still gave 'no indication if or when' it would submit.</t>
+          <t>p. 37. The filing does not quote the draft’s price. Diligence was still under way inside CLP’s requested 30-day exclusivity, and the equity commitment letter was not signed until 02/10.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>#63, #70, #71</t>
+          <t>#72</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>If H is not treated as entered (no NDA or bid reported), it has no exit and round 3 admits two units. If I is taken to have left by 01/04, its exit moves earlier and could be Withdrew.</t>
+          <t>Without it, CLP’s only Formal bid is $2.20 on 02/10/2021 and its $2.00 stays Informal.</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Does CLP's delivery of its own initial draft Merger Agreement on 01/21/2021 reaffirm its $2.00 offer as Formal (Bid reaffirmed)?</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Yes. CLP's own full proposed agreement, delivered after the target moved to finalize with it, supports its standing $2.00 cash price (E10; E11 item 1). The filing does not state the price in the draft.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>p. 37: 'outside counsel to CLP, Thompson Hine LLP (“Thompson”), delivered an initial draft of the Merger Agreement to Gunderson'. CLP's latest priced row (#67) is Informal.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>#74</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Without #74, CLP's $2.00 stays Informal until the Formal $2.20 bid of 02/10/2021 (#76), and the winner has one formal bid instead of two.</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6446,7 +6331,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Synacor, Inc. (Nasdaq: SYNC), Buffalo, New York; email/collaboration software, identity management, portals and advertising.</t>
+          <t>Synacor, Inc. (Nasdaq: SYNC), Buffalo, New York; digital technology company (email and collaboration software, identity management, portals, advertising).</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6343,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CLP SY Holding, LLC (Parent) through SY Merger Sub Corporation; Parent's sole member is Centre Lane Partners V, L.P., affiliated with Centre Lane Partners, LLC (CLP).</t>
+          <t>CLP SY Holding, LLC (Parent) through SY Merger Sub Corporation; Parent’s sole member is Centre Lane Partners V, L.P., a fund managed by Centre Lane Partners, LLC (“CLP”).</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6355,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Financial (private equity fund)</t>
+          <t>Financial (private equity fund; equity commitment from CLP Fund V).</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6367,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$2.20 per share in cash, by a tender offer followed by a DGCL 251(h) merger; equity commitment from CLP Fund V of up to $87,597,343 plus award payouts; no financing condition; $3.5 million termination fee, no reverse fee.</t>
+          <t>$2.20 per share in cash, by tender offer followed by a §251(h) merger. Equity commitment up to $87,597,343 plus award payouts; no financing condition. Termination fee $3.5 million; no reverse fee. Tender and Support Agreements cover about 17.4% of shares.</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6403,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Schedule TO-T (Offer to Purchase, Exhibit (a)(1)(A)) by SY Merger Sub Corporation, dated 03/03/2021</t>
+          <t>SC TO-T, Offer to Purchase (Exhibit (a)(1)(A)), 03/03/2021</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6415,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>30-38 (Section 11, Background of the Offer)</t>
+          <t>30–38 (Section 11, Background of the Offer)</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6427,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>mixed: process 3 began with Company E’s approach through director Kevin Rendino (bidder-led), which Synacor took up with a banker-run outreach (target-led)</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6439,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (2018; 2019; July 2020–February 2021)</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6451,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>None reported beyond processes 1-3. Two Synacor-initiated combinations are not treated as sale processes (Q2): a proposed 'merger of equals' with Company B (NDA and letter October-December 2018, ended March 2019), and Synacor's proposed acquisition of Company D (IOI 07/01/2019; all-stock merger agreement 02/11/2020; terminated 06/29/2020).</t>
+          <t>None reported beyond the ledgered processes. Not treated as sales of Synacor: the Company-proposed merger of equals with Company B (Oct 2018–Mar 2019); Synacor’s own bid for Company D (07/01/2019), all-stock merger agreement 02/11/2020, terminated 06/29/2020.</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6463,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Not met (process 1): 1 party (Company A); Uncertain (process 2): 1 whole-company acquirer (Company C), 2 counting Company E's NDA for the portal business only; Met (process 3): at least 14 parties (14 outreach NDA signers; up to 17 with Company E's amended NDA, CLP and Company I if outside the 14)</t>
+          <t>Not met (process 1): 1 party (Company A); Uncertain (process 2): 1 whole-company party (Company C) plus 2 segment-only parties (Company E, Company F’s existing May 2018 NDA), Met if segment buyers count; Met (process 3): at least 14 parties (14 stated; with CLP, E and I at most 17)</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6475,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Yes (also Other-scope bids: Company F and Company I for the portal and advertising business, Company G for the software and services business, and Company E's 35% partial tender offer)</t>
+          <t>Yes. Also other-scope bids: Company F and Company I (portal and advertising business), Company G (software and services business), Company E (35% tender offer).</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6487,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share. Company A's and Company C's prices were not disclosed (C: cash and stock). The segment bids (F, G, I) gave no per-share price, only valuations as fractions of rivals'. Company E's partial tender was $2.00 per share for 35% of shares (Q3).</t>
+          <t>US dollars per share. Several bids have undisclosed prices (A, C, F, I); Company G’s was stated only on an enterprise-value basis as a fraction of E’s.</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6499,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Liontree Advisors LLC (2018); Canaccord Genuity LLC (2019-2021; fairness opinion 02/10/2021)</t>
+          <t>Liontree Advisors LLC (engaged 05/08/2018); Canaccord Genuity LLC (engaged 08/25/2019, re-engaged 01/02/2020, amended 07/30/2020 and 01/25/2021; fairness opinion 02/10/2021)</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6511,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Gunderson Dettmer (outside corporate counsel). Acquirer's counsel: Thompson Hine LLP.</t>
+          <t>Gunderson Dettmer (outside corporate counsel). CLP’s counsel: Thompson Hine LLP.</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6523,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>After two attempts in 2018 and 2019 lapsed, a director relayed Company E's interest in July 2020, and Canaccord contacted 37 parties, 14 of which signed NDAs. By the 09/17/2020 IOI date Synacor had Company E at $2.00 cash, CLP at $1.35-$1.41 and a software-only bid from Company G. It granted Company E exclusivity, but E's diligence dragged, and in December E switched to a 35% partial tender at $2.00 with control demands. The Special Committee let E's offer lapse and turned to CLP, H and I; CLP bid $1.88 on 01/04/2021 and $2.00 two days later, and the parties signed a non-binding LOI. After the share price rose, the Board asked for $2.20; CLP agreed on 02/10/2021, conditioned on signing that day, and the merger agreement was signed that evening.</t>
+          <t>Synacor made two unsuccessful sale attempts first. In 2018 private investment firm Company A bid and then withdrew while Liontree canvassed about 12 parties. In 2019 Company C’s cash-and-stock LOI was dropped by mutual agreement after Canaccord contacted 18 parties. In July 2020 Company E approached through director Rendino, and Canaccord contacted 37 parties, 14 of which signed NDAs; E ($2.00), CLP ($1.35–$1.41) and segment bidder G submitted by 09/17/2020, and Synacor granted E exclusivity. E later switched to a 35% tender offer, so Synacor revived CLP, which rose from $1.88 to $2.00 under an LOI signed 01/07/2021. After the Board demanded $2.20, CLP agreed and the merger agreement was signed on 02/10/2021.</t>
         </is>
       </c>
     </row>
